--- a/research/traditional_assets/database/data/finland/finland_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_telecom_equipment.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0321</v>
+        <v>-0.05515</v>
       </c>
       <c r="F2">
         <v>0.04190000000000001</v>
       </c>
       <c r="G2">
-        <v>0.3734593373903737</v>
+        <v>0.3719888706152703</v>
       </c>
       <c r="H2">
-        <v>0.1455591732344165</v>
+        <v>0.1446385202874716</v>
       </c>
       <c r="I2">
-        <v>0.1029239713044503</v>
+        <v>0.1021767634667808</v>
       </c>
       <c r="J2">
-        <v>0.05774295301303943</v>
+        <v>0.07975025698514557</v>
       </c>
       <c r="K2">
-        <v>461.7</v>
+        <v>457.69</v>
       </c>
       <c r="L2">
-        <v>0.02093668658909315</v>
+        <v>0.02062270484601347</v>
       </c>
       <c r="M2">
         <v>1178.9</v>
       </c>
       <c r="N2">
-        <v>0.04945714189824138</v>
+        <v>0.04935382451322284</v>
       </c>
       <c r="O2">
-        <v>2.553389646956899</v>
+        <v>2.575760886189342</v>
       </c>
       <c r="P2">
         <v>800.8</v>
       </c>
       <c r="Q2">
-        <v>0.03359511343804537</v>
+        <v>0.03352493228449304</v>
       </c>
       <c r="R2">
-        <v>1.734459605804635</v>
+        <v>1.749655880617885</v>
       </c>
       <c r="S2">
         <v>378.1000000000001</v>
@@ -638,73 +638,73 @@
         <v>0.320722707608788</v>
       </c>
       <c r="U2">
-        <v>7855.2</v>
+        <v>7872.9</v>
       </c>
       <c r="V2">
-        <v>0.3295408779701973</v>
+        <v>0.3295934557724591</v>
       </c>
       <c r="W2">
-        <v>0.02051325341887557</v>
+        <v>-0.01949114777127438</v>
       </c>
       <c r="X2">
-        <v>0.1127016413613526</v>
+        <v>0.1291858547375864</v>
       </c>
       <c r="Y2">
-        <v>-0.09218838794247707</v>
+        <v>-0.1486770025088608</v>
       </c>
       <c r="Z2">
-        <v>1.290961245755766</v>
+        <v>1.29435333364438</v>
       </c>
       <c r="AA2">
-        <v>0.07454391455533006</v>
+        <v>0.02143344796089485</v>
       </c>
       <c r="AB2">
-        <v>0.1017550982752465</v>
+        <v>0.09990262367832425</v>
       </c>
       <c r="AC2">
-        <v>-0.02721118371991642</v>
+        <v>-0.07846917571742942</v>
       </c>
       <c r="AD2">
-        <v>5141.6</v>
+        <v>5188.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5141.6</v>
+        <v>5188.5</v>
       </c>
       <c r="AG2">
-        <v>-2713.599999999999</v>
+        <v>-2684.4</v>
       </c>
       <c r="AH2">
-        <v>0.1774287055185932</v>
+        <v>0.1784510510675765</v>
       </c>
       <c r="AI2">
-        <v>0.1839281114958647</v>
+        <v>0.1848539801411567</v>
       </c>
       <c r="AJ2">
-        <v>-0.1284653840327223</v>
+        <v>-0.1266089056375959</v>
       </c>
       <c r="AK2">
-        <v>-0.1350103486705938</v>
+        <v>-0.132922674694977</v>
       </c>
       <c r="AL2">
-        <v>284.4</v>
+        <v>286.29</v>
       </c>
       <c r="AM2">
-        <v>-59.10000000000002</v>
+        <v>-57.21000000000004</v>
       </c>
       <c r="AN2">
-        <v>1.606248047485161</v>
+        <v>1.621329743502729</v>
       </c>
       <c r="AO2">
-        <v>7.980661040787624</v>
+        <v>7.920849488281114</v>
       </c>
       <c r="AP2">
-        <v>-0.847735082786629</v>
+        <v>-0.8388354174537388</v>
       </c>
       <c r="AQ2">
-        <v>-38.40439932318103</v>
+        <v>-39.63747596574023</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.02051325341887557</v>
       </c>
       <c r="X3">
-        <v>0.1127016413613526</v>
+        <v>0.1126669048540224</v>
       </c>
       <c r="Y3">
-        <v>-0.09218838794247707</v>
+        <v>-0.09215365143514685</v>
       </c>
       <c r="Z3">
         <v>1.290961245755766</v>
@@ -793,10 +793,10 @@
         <v>0.07454391455533006</v>
       </c>
       <c r="AB3">
-        <v>0.1017550982752465</v>
+        <v>0.1017265250214461</v>
       </c>
       <c r="AC3">
-        <v>-0.02721118371991642</v>
+        <v>-0.02718261046611604</v>
       </c>
       <c r="AD3">
         <v>5141.6</v>
@@ -839,6 +839,134 @@
       </c>
       <c r="AQ3">
         <v>-38.40439932318103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Teleste Oyj (HLSE:TLT1V)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.07820000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.1424982307147912</v>
+      </c>
+      <c r="H4">
+        <v>0.0009554140127388535</v>
+      </c>
+      <c r="I4">
+        <v>-0.01443736730360934</v>
+      </c>
+      <c r="J4">
+        <v>-0.01443736730360934</v>
+      </c>
+      <c r="K4">
+        <v>-4.01</v>
+      </c>
+      <c r="L4">
+        <v>-0.0283793347487615</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>17.7</v>
+      </c>
+      <c r="V4">
+        <v>0.3547094188376754</v>
+      </c>
+      <c r="W4">
+        <v>-0.05949554896142432</v>
+      </c>
+      <c r="X4">
+        <v>0.1457048046211505</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2052003535825748</v>
+      </c>
+      <c r="Z4">
+        <v>2.194099378881988</v>
+      </c>
+      <c r="AA4">
+        <v>-0.03167701863354037</v>
+      </c>
+      <c r="AB4">
+        <v>0.09807872233520241</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1297557409687428</v>
+      </c>
+      <c r="AD4">
+        <v>46.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>46.9</v>
+      </c>
+      <c r="AG4">
+        <v>29.2</v>
+      </c>
+      <c r="AH4">
+        <v>0.484504132231405</v>
+      </c>
+      <c r="AI4">
+        <v>0.4124890061565524</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3691529709228825</v>
+      </c>
+      <c r="AK4">
+        <v>0.3041666666666666</v>
+      </c>
+      <c r="AL4">
+        <v>1.89</v>
+      </c>
+      <c r="AM4">
+        <v>1.89</v>
+      </c>
+      <c r="AN4">
+        <v>-55.2414605418139</v>
+      </c>
+      <c r="AO4">
+        <v>-1.07936507936508</v>
+      </c>
+      <c r="AP4">
+        <v>-34.39340400471143</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.07936507936508</v>
       </c>
     </row>
   </sheetData>
@@ -1133,49 +1261,49 @@
         <v>7.98066104078762</v>
       </c>
       <c r="F2">
-        <v>3.0147457000381</v>
+        <v>3.00397463760739</v>
       </c>
       <c r="G2">
         <v>1.60624804748516</v>
       </c>
       <c r="H2">
-        <v>3.80222680412371</v>
+        <v>3.9832852233677</v>
       </c>
       <c r="I2">
         <v>0.177428705518593</v>
       </c>
       <c r="J2">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="K2">
         <v>23836.8</v>
       </c>
       <c r="L2">
-        <v>17558.281603818</v>
+        <v>17373.1607815927</v>
       </c>
       <c r="M2">
         <v>21123.2</v>
       </c>
       <c r="N2">
-        <v>21874.009603818</v>
+        <v>22268.4567815927</v>
       </c>
       <c r="O2">
         <v>5141.6</v>
       </c>
       <c r="P2">
-        <v>12170.928</v>
+        <v>12750.496</v>
       </c>
       <c r="Q2">
-        <v>0.101755098275246</v>
+        <v>0.101726525021446</v>
       </c>
       <c r="R2">
-        <v>0.0996115400920449</v>
+        <v>0.0985148222748063</v>
       </c>
       <c r="S2">
         <v>0.0510061955533515</v>
       </c>
       <c r="T2">
-        <v>0.0494861955533515</v>
+        <v>0.0474061955533515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1316,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.112701641361353</v>
+        <v>0.112666904854022</v>
       </c>
       <c r="X2">
-        <v>0.135909203378685</v>
+        <v>0.138671600413092</v>
       </c>
       <c r="Y2">
         <v>1.37485394243548</v>
       </c>
       <c r="Z2">
-        <v>1.85177808786126</v>
+        <v>1.90953785354627</v>
       </c>
       <c r="AA2">
         <v>5141.6</v>
@@ -1230,7 +1358,7 @@
         <v>23836.8</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.04863564251455781</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1028560458074643</v>
+        <v>0.1028264213062847</v>
       </c>
       <c r="C2">
-        <v>28612.46587193535</v>
+        <v>28612.7999216799</v>
       </c>
       <c r="D2">
-        <v>20757.26587193535</v>
+        <v>20757.5999216799</v>
       </c>
       <c r="E2">
         <v>-5141.6</v>
@@ -1469,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1028560458074643</v>
+        <v>0.1028264213062847</v>
       </c>
       <c r="T2">
         <v>1.172523243405601</v>
       </c>
       <c r="U2">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1628,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1027291956713829</v>
+        <v>0.1026884304192056</v>
       </c>
       <c r="C3">
-        <v>28364.19690604443</v>
+        <v>28368.18762236318</v>
       </c>
       <c r="D3">
-        <v>20798.78090604443</v>
+        <v>20802.77162236318</v>
       </c>
       <c r="E3">
         <v>-4851.816000000001</v>
@@ -1533,37 +1661,37 @@
         <v>2269.7</v>
       </c>
       <c r="M3">
-        <v>16.12872381529052</v>
+        <v>15.72302621529052</v>
       </c>
       <c r="N3">
-        <v>2253.571276184709</v>
+        <v>2253.976973784709</v>
       </c>
       <c r="O3">
-        <v>450.7142552369419</v>
+        <v>450.7953947569418</v>
       </c>
       <c r="P3">
-        <v>1802.857020947768</v>
+        <v>1803.181579027767</v>
       </c>
       <c r="Q3">
-        <v>2734.157020947768</v>
+        <v>2734.481579027768</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1033171047634842</v>
+        <v>0.1032872408723961</v>
       </c>
       <c r="T3">
         <v>1.181998178705849</v>
       </c>
       <c r="U3">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.7240911304002</v>
+        <v>144.3551622265142</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1710,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1026023455353014</v>
+        <v>0.1025504395321266</v>
       </c>
       <c r="C4">
-        <v>28116.09433509334</v>
+        <v>28123.7723528221</v>
       </c>
       <c r="D4">
-        <v>20840.46233509334</v>
+        <v>20848.14035282209</v>
       </c>
       <c r="E4">
         <v>-4562.032</v>
@@ -1615,37 +1743,37 @@
         <v>2269.7</v>
       </c>
       <c r="M4">
-        <v>32.25744763058105</v>
+        <v>31.44605243058105</v>
       </c>
       <c r="N4">
-        <v>2237.442552369419</v>
+        <v>2238.253947569419</v>
       </c>
       <c r="O4">
-        <v>447.4885104738838</v>
+        <v>447.6507895138838</v>
       </c>
       <c r="P4">
-        <v>1789.954041895535</v>
+        <v>1790.603158055535</v>
       </c>
       <c r="Q4">
-        <v>2721.254041895535</v>
+        <v>2721.903158055535</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1037875730859535</v>
+        <v>0.1037574649194485</v>
       </c>
       <c r="T4">
         <v>1.191666480032632</v>
       </c>
       <c r="U4">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.36204556520011</v>
+        <v>72.17758111325712</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1792,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.10247549539922</v>
+        <v>0.1024124486450475</v>
       </c>
       <c r="C5">
-        <v>27868.15916147341</v>
+        <v>27879.55540497994</v>
       </c>
       <c r="D5">
-        <v>20882.3111614734</v>
+        <v>20893.70740497993</v>
       </c>
       <c r="E5">
         <v>-4272.248000000001</v>
@@ -1697,37 +1825,37 @@
         <v>2269.7</v>
       </c>
       <c r="M5">
-        <v>48.38617144587156</v>
+        <v>47.16907864587156</v>
       </c>
       <c r="N5">
-        <v>2221.313828554128</v>
+        <v>2222.530921354128</v>
       </c>
       <c r="O5">
-        <v>444.2627657108256</v>
+        <v>444.5061842708257</v>
       </c>
       <c r="P5">
-        <v>1777.051062843303</v>
+        <v>1778.024737083303</v>
       </c>
       <c r="Q5">
-        <v>2708.351062843303</v>
+        <v>2709.324737083303</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1042677417862056</v>
+        <v>0.1042373843076773</v>
       </c>
       <c r="T5">
         <v>1.201534127778523</v>
       </c>
       <c r="U5">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.90803037680008</v>
+        <v>48.11838740883809</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1874,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1023486452631386</v>
+        <v>0.1022744577579685</v>
       </c>
       <c r="C6">
-        <v>27620.3923956436</v>
+        <v>27635.53808207958</v>
       </c>
       <c r="D6">
-        <v>20924.3283956436</v>
+        <v>20939.47408207957</v>
       </c>
       <c r="E6">
         <v>-3982.464</v>
@@ -1779,37 +1907,37 @@
         <v>2269.7</v>
       </c>
       <c r="M6">
-        <v>64.5148952611621</v>
+        <v>62.8921048611621</v>
       </c>
       <c r="N6">
-        <v>2205.185104738838</v>
+        <v>2206.807895138838</v>
       </c>
       <c r="O6">
-        <v>441.0370209477676</v>
+        <v>441.3615790277676</v>
       </c>
       <c r="P6">
-        <v>1764.14808379107</v>
+        <v>1765.44631611107</v>
       </c>
       <c r="Q6">
-        <v>2695.448083791071</v>
+        <v>2696.74631611107</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1047579140010464</v>
+        <v>0.1047273020164942</v>
       </c>
       <c r="T6">
         <v>1.211607351519122</v>
       </c>
       <c r="U6">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.18102278260005</v>
+        <v>36.08879055662857</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1022217951270572</v>
+        <v>0.1021364668708894</v>
       </c>
       <c r="C7">
-        <v>27372.79505621186</v>
+        <v>27391.72169880776</v>
       </c>
       <c r="D7">
-        <v>20966.51505621186</v>
+        <v>20985.44169880776</v>
       </c>
       <c r="E7">
         <v>-3692.68</v>
@@ -1861,37 +1989,37 @@
         <v>2269.7</v>
       </c>
       <c r="M7">
-        <v>80.64361907645261</v>
+        <v>78.61513107645261</v>
       </c>
       <c r="N7">
-        <v>2189.056380923547</v>
+        <v>2191.084868923547</v>
       </c>
       <c r="O7">
-        <v>437.8112761847095</v>
+        <v>438.2169737847095</v>
       </c>
       <c r="P7">
-        <v>1751.245104738838</v>
+        <v>1752.867895138838</v>
       </c>
       <c r="Q7">
-        <v>2682.545104738838</v>
+        <v>2684.167895138838</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1052584056309364</v>
+        <v>0.1052275337823388</v>
       </c>
       <c r="T7">
         <v>1.221892643127942</v>
       </c>
       <c r="U7">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.14481822608005</v>
+        <v>28.87103244530285</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2038,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1020949449909758</v>
+        <v>0.1019984759838104</v>
       </c>
       <c r="C8">
-        <v>27125.36817001738</v>
+        <v>27148.10758142091</v>
       </c>
       <c r="D8">
-        <v>21008.87217001738</v>
+        <v>21031.61158142091</v>
       </c>
       <c r="E8">
         <v>-3402.896000000001</v>
@@ -1943,37 +2071,37 @@
         <v>2269.7</v>
       </c>
       <c r="M8">
-        <v>96.77234289174312</v>
+        <v>94.33815729174313</v>
       </c>
       <c r="N8">
-        <v>2172.927657108257</v>
+        <v>2175.361842708257</v>
       </c>
       <c r="O8">
-        <v>434.5855314216514</v>
+        <v>435.0723685416513</v>
       </c>
       <c r="P8">
-        <v>1738.342125686605</v>
+        <v>1740.289474166605</v>
       </c>
       <c r="Q8">
-        <v>2669.642125686606</v>
+        <v>2671.589474166605</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1057695460189093</v>
+        <v>0.1057384087772439</v>
       </c>
       <c r="T8">
         <v>1.232396770728441</v>
       </c>
       <c r="U8">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.45401518840004</v>
+        <v>24.05919370441904</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2120,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1019680948548944</v>
+        <v>0.1018604850967313</v>
       </c>
       <c r="C9">
-        <v>26878.11277221397</v>
+        <v>26904.69706787275</v>
       </c>
       <c r="D9">
-        <v>21051.40077221397</v>
+        <v>21077.98506787275</v>
       </c>
       <c r="E9">
         <v>-3113.112</v>
@@ -2025,37 +2153,37 @@
         <v>2269.7</v>
       </c>
       <c r="M9">
-        <v>112.9010667070337</v>
+        <v>110.0611835070337</v>
       </c>
       <c r="N9">
-        <v>2156.798933292966</v>
+        <v>2159.638816492966</v>
       </c>
       <c r="O9">
-        <v>431.3597866585932</v>
+        <v>431.9277632985933</v>
       </c>
       <c r="P9">
-        <v>1725.439146634373</v>
+        <v>1727.711053194373</v>
       </c>
       <c r="Q9">
-        <v>2656.739146634373</v>
+        <v>2659.011053194373</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1062916786732901</v>
+        <v>0.1062602703311793</v>
       </c>
       <c r="T9">
         <v>1.243126793546154</v>
       </c>
       <c r="U9">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.10344159005717</v>
+        <v>20.62216603235918</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2202,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.101841244718813</v>
+        <v>0.1017224942096523</v>
       </c>
       <c r="C10">
-        <v>26631.02990635432</v>
+        <v>26661.4915079435</v>
       </c>
       <c r="D10">
-        <v>21094.10190635432</v>
+        <v>21124.56350794351</v>
       </c>
       <c r="E10">
         <v>-2823.328</v>
@@ -2107,37 +2235,37 @@
         <v>2269.7</v>
       </c>
       <c r="M10">
-        <v>129.0297905223242</v>
+        <v>125.7842097223242</v>
       </c>
       <c r="N10">
-        <v>2140.670209477676</v>
+        <v>2143.915790277676</v>
       </c>
       <c r="O10">
-        <v>428.1340418955351</v>
+        <v>428.7831580555351</v>
       </c>
       <c r="P10">
-        <v>1712.53616758214</v>
+        <v>1715.132632222141</v>
       </c>
       <c r="Q10">
-        <v>2643.836167582141</v>
+        <v>2646.43263222214</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1068251620375487</v>
+        <v>0.1067934767015045</v>
       </c>
       <c r="T10">
         <v>1.254090077729469</v>
       </c>
       <c r="U10">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.59051139130003</v>
+        <v>18.04439527831428</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2284,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1017143945827316</v>
+        <v>0.1015845033225732</v>
       </c>
       <c r="C11">
-        <v>26384.12062447544</v>
+        <v>26418.49226337089</v>
       </c>
       <c r="D11">
-        <v>21136.97662447544</v>
+        <v>21171.34826337089</v>
       </c>
       <c r="E11">
         <v>-2533.544</v>
@@ -2189,37 +2317,37 @@
         <v>2269.7</v>
       </c>
       <c r="M11">
-        <v>145.1585143376147</v>
+        <v>141.5072359376147</v>
       </c>
       <c r="N11">
-        <v>2124.541485662385</v>
+        <v>2128.192764062385</v>
       </c>
       <c r="O11">
-        <v>424.9082971324771</v>
+        <v>425.6385528124771</v>
       </c>
       <c r="P11">
-        <v>1699.633188529908</v>
+        <v>1702.554211249908</v>
       </c>
       <c r="Q11">
-        <v>2630.933188529908</v>
+        <v>2633.854211249909</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.107370370310912</v>
+        <v>0.1073384018931555</v>
       </c>
       <c r="T11">
         <v>1.265294313213517</v>
       </c>
       <c r="U11">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.63601012560003</v>
+        <v>16.0394624696127</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2366,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1015875444466501</v>
+        <v>0.1014465124354942</v>
       </c>
       <c r="C12">
-        <v>26137.38598718497</v>
+        <v>26175.7007079828</v>
       </c>
       <c r="D12">
-        <v>21180.02598718497</v>
+        <v>21218.3407079828</v>
       </c>
       <c r="E12">
         <v>-2243.76</v>
@@ -2271,37 +2399,37 @@
         <v>2269.7</v>
       </c>
       <c r="M12">
-        <v>161.2872381529052</v>
+        <v>157.2302621529052</v>
       </c>
       <c r="N12">
-        <v>2108.412761847095</v>
+        <v>2112.469737847095</v>
       </c>
       <c r="O12">
-        <v>421.682552369419</v>
+        <v>422.4939475694189</v>
       </c>
       <c r="P12">
-        <v>1686.730209477676</v>
+        <v>1689.975790277676</v>
       </c>
       <c r="Q12">
-        <v>2618.030209477676</v>
+        <v>2621.275790277676</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1079276943236833</v>
+        <v>0.10789543653351</v>
       </c>
       <c r="T12">
         <v>1.276747531708322</v>
       </c>
       <c r="U12">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.07240911304002</v>
+        <v>14.43551622265143</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2448,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1014606943105687</v>
+        <v>0.1013085215484151</v>
       </c>
       <c r="C13">
-        <v>25890.82706374871</v>
+        <v>25933.1182278318</v>
       </c>
       <c r="D13">
-        <v>21223.25106374871</v>
+        <v>21265.5422278318</v>
       </c>
       <c r="E13">
         <v>-1953.976</v>
@@ -2353,37 +2481,37 @@
         <v>2269.7</v>
       </c>
       <c r="M13">
-        <v>177.4159619681957</v>
+        <v>172.9532883681958</v>
       </c>
       <c r="N13">
-        <v>2092.284038031804</v>
+        <v>2096.746711631804</v>
       </c>
       <c r="O13">
-        <v>418.4568076063608</v>
+        <v>419.3493423263608</v>
       </c>
       <c r="P13">
-        <v>1673.827230425443</v>
+        <v>1677.397369305443</v>
       </c>
       <c r="Q13">
-        <v>2605.127230425443</v>
+        <v>2608.697369305443</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1084975424715731</v>
+        <v>0.1084649888062319</v>
       </c>
       <c r="T13">
         <v>1.288458125899638</v>
       </c>
       <c r="U13">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.79309919367275</v>
+        <v>13.12319656604675</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2530,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1013338441744873</v>
+        <v>0.101170530661336</v>
       </c>
       <c r="C14">
-        <v>25644.44493217909</v>
+        <v>25690.7462213314</v>
       </c>
       <c r="D14">
-        <v>21266.65293217909</v>
+        <v>21312.9542213314</v>
       </c>
       <c r="E14">
         <v>-1664.192</v>
@@ -2435,37 +2563,37 @@
         <v>2269.7</v>
       </c>
       <c r="M14">
-        <v>193.5446857834862</v>
+        <v>188.6763145834863</v>
       </c>
       <c r="N14">
-        <v>2076.155314216513</v>
+        <v>2081.023685416514</v>
       </c>
       <c r="O14">
-        <v>415.2310628433027</v>
+        <v>416.2047370833027</v>
       </c>
       <c r="P14">
-        <v>1660.924251373211</v>
+        <v>1664.818948333211</v>
       </c>
       <c r="Q14">
-        <v>2592.224251373211</v>
+        <v>2596.118948333211</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1090803417137331</v>
+        <v>0.1090474854487885</v>
       </c>
       <c r="T14">
         <v>1.30043486995894</v>
       </c>
       <c r="U14">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.72700759420002</v>
+        <v>12.02959685220952</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2612,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1012069940384059</v>
+        <v>0.101032539774257</v>
       </c>
       <c r="C15">
-        <v>25398.24067932484</v>
+        <v>25448.58609939413</v>
       </c>
       <c r="D15">
-        <v>21310.23267932484</v>
+        <v>21360.57809939413</v>
       </c>
       <c r="E15">
         <v>-1374.408</v>
@@ -2517,37 +2645,37 @@
         <v>2269.7</v>
       </c>
       <c r="M15">
-        <v>209.6734095987768</v>
+        <v>204.3993407987768</v>
       </c>
       <c r="N15">
-        <v>2060.026590401223</v>
+        <v>2065.300659201223</v>
       </c>
       <c r="O15">
-        <v>412.0053180802446</v>
+        <v>413.0601318402446</v>
       </c>
       <c r="P15">
-        <v>1648.021272320978</v>
+        <v>1652.240527360978</v>
       </c>
       <c r="Q15">
-        <v>2579.321272320979</v>
+        <v>2583.540527360979</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1096765386396209</v>
+        <v>0.1096433728187601</v>
       </c>
       <c r="T15">
         <v>1.31268694146788</v>
       </c>
       <c r="U15">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.82493008695386</v>
+        <v>11.1042432481934</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2694,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1010801439023245</v>
+        <v>0.1008945488871779</v>
       </c>
       <c r="C16">
-        <v>25152.21540096167</v>
+        <v>25206.63928557155</v>
       </c>
       <c r="D16">
-        <v>21353.99140096167</v>
+        <v>21408.41528557154</v>
       </c>
       <c r="E16">
         <v>-1084.624</v>
@@ -2599,37 +2727,37 @@
         <v>2269.7</v>
       </c>
       <c r="M16">
-        <v>225.8021334140673</v>
+        <v>220.1223670140674</v>
       </c>
       <c r="N16">
-        <v>2043.897866585932</v>
+        <v>2049.577632985932</v>
       </c>
       <c r="O16">
-        <v>408.7795733171865</v>
+        <v>409.9155265971865</v>
       </c>
       <c r="P16">
-        <v>1635.118293268746</v>
+        <v>1639.662106388746</v>
       </c>
       <c r="Q16">
-        <v>2566.418293268746</v>
+        <v>2570.962106388746</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1102866006102968</v>
+        <v>0.110253118034545</v>
       </c>
       <c r="T16">
         <v>1.325223944872377</v>
       </c>
       <c r="U16">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.05172079502859</v>
+        <v>10.31108301617959</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2776,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1009532937662431</v>
+        <v>0.1007565580000989</v>
       </c>
       <c r="C17">
-        <v>24906.37020188416</v>
+        <v>24964.907216196</v>
       </c>
       <c r="D17">
-        <v>21397.93020188416</v>
+        <v>21456.467216196</v>
       </c>
       <c r="E17">
         <v>-794.8400000000001</v>
@@ -2681,37 +2809,37 @@
         <v>2269.7</v>
       </c>
       <c r="M17">
-        <v>241.9308572293578</v>
+        <v>235.8453932293579</v>
       </c>
       <c r="N17">
-        <v>2027.769142770642</v>
+        <v>2033.854606770642</v>
       </c>
       <c r="O17">
-        <v>405.5538285541284</v>
+        <v>406.7709213541284</v>
       </c>
       <c r="P17">
-        <v>1622.215314216514</v>
+        <v>1627.083685416514</v>
       </c>
       <c r="Q17">
-        <v>2553.515314216514</v>
+        <v>2558.383685416514</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1109110169802827</v>
+        <v>0.1108772101965837</v>
       </c>
       <c r="T17">
         <v>1.338055936592275</v>
       </c>
       <c r="U17">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.381606075360015</v>
+        <v>9.623677481767617</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2858,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1008264436301616</v>
+        <v>0.1006185671130198</v>
       </c>
       <c r="C18">
-        <v>24660.70619599866</v>
+        <v>24723.39134052452</v>
       </c>
       <c r="D18">
-        <v>21442.05019599867</v>
+        <v>21504.73534052452</v>
       </c>
       <c r="E18">
         <v>-505.0559999999996</v>
@@ -2763,37 +2891,37 @@
         <v>2269.7</v>
       </c>
       <c r="M18">
-        <v>258.0595810446484</v>
+        <v>251.5684194446484</v>
       </c>
       <c r="N18">
-        <v>2011.640418955351</v>
+        <v>2018.131580555351</v>
       </c>
       <c r="O18">
-        <v>402.3280837910703</v>
+        <v>403.6263161110703</v>
       </c>
       <c r="P18">
-        <v>1609.312335164281</v>
+        <v>1614.505264444281</v>
       </c>
       <c r="Q18">
-        <v>2540.612335164281</v>
+        <v>2545.805264444281</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1115503004066969</v>
+        <v>0.1115161616958138</v>
       </c>
       <c r="T18">
         <v>1.35119345192455</v>
       </c>
       <c r="U18">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.795255695650013</v>
+        <v>9.02219763915714</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2940,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1008491934940802</v>
+        <v>0.1006845762259408</v>
       </c>
       <c r="C19">
-        <v>24362.99613725691</v>
+        <v>24410.49080744701</v>
       </c>
       <c r="D19">
-        <v>21434.12413725691</v>
+        <v>21481.61880744701</v>
       </c>
       <c r="E19">
         <v>-215.2719999999999</v>
@@ -2845,37 +2973,37 @@
         <v>2269.7</v>
       </c>
       <c r="M19">
-        <v>279.6072656599389</v>
+        <v>274.6809376599389</v>
       </c>
       <c r="N19">
-        <v>1990.092734340061</v>
+        <v>1995.019062340061</v>
       </c>
       <c r="O19">
-        <v>398.0185468680122</v>
+        <v>399.0038124680122</v>
       </c>
       <c r="P19">
-        <v>1592.074187472049</v>
+        <v>1596.015249872049</v>
       </c>
       <c r="Q19">
-        <v>2523.374187472049</v>
+        <v>2527.315249872049</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1122049882530247</v>
+        <v>0.112170509616712</v>
       </c>
       <c r="T19">
         <v>1.364647533891338</v>
       </c>
       <c r="U19">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.117457157785132</v>
+        <v>8.263041546807077</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3022,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1007311433579988</v>
+        <v>0.1005585853388617</v>
       </c>
       <c r="C20">
-        <v>24114.40464606171</v>
+        <v>24164.87227371399</v>
       </c>
       <c r="D20">
-        <v>21475.31664606171</v>
+        <v>21525.78427371399</v>
       </c>
       <c r="E20">
         <v>74.51199999999972</v>
@@ -2927,37 +3055,37 @@
         <v>2269.7</v>
       </c>
       <c r="M20">
-        <v>296.0547518752294</v>
+        <v>290.8386398752294</v>
       </c>
       <c r="N20">
-        <v>1973.64524812477</v>
+        <v>1978.86136012477</v>
       </c>
       <c r="O20">
-        <v>394.7290496249541</v>
+        <v>395.7722720249541</v>
       </c>
       <c r="P20">
-        <v>1578.916198499816</v>
+        <v>1583.089088099816</v>
       </c>
       <c r="Q20">
-        <v>2510.216198499817</v>
+        <v>2514.389088099816</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1128756440956043</v>
+        <v>0.1128408172429981</v>
       </c>
       <c r="T20">
         <v>1.37842976419878</v>
       </c>
       <c r="U20">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.666487315685958</v>
+        <v>7.803983683095574</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3104,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1006130932219174</v>
+        <v>0.1004325944517827</v>
       </c>
       <c r="C21">
-        <v>23865.97178883131</v>
+        <v>23919.43571947074</v>
       </c>
       <c r="D21">
-        <v>21516.66778883131</v>
+        <v>21570.13171947074</v>
       </c>
       <c r="E21">
         <v>364.2960000000003</v>
@@ -3009,37 +3137,37 @@
         <v>2269.7</v>
       </c>
       <c r="M21">
-        <v>312.5022380905199</v>
+        <v>306.9963420905199</v>
       </c>
       <c r="N21">
-        <v>1957.19776190948</v>
+        <v>1962.70365790948</v>
       </c>
       <c r="O21">
-        <v>391.439552381896</v>
+        <v>392.540731581896</v>
       </c>
       <c r="P21">
-        <v>1565.758209527584</v>
+        <v>1570.162926327584</v>
       </c>
       <c r="Q21">
-        <v>2497.058209527584</v>
+        <v>2501.462926327584</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1135628593417045</v>
+        <v>0.1135276756748715</v>
       </c>
       <c r="T21">
         <v>1.392552296489122</v>
       </c>
       <c r="U21">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.262987983281433</v>
+        <v>7.393247699774753</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3186,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.100495043085836</v>
+        <v>0.1003066035647036</v>
       </c>
       <c r="C22">
-        <v>23617.69848369203</v>
+        <v>23674.18227178235</v>
       </c>
       <c r="D22">
-        <v>21558.17848369203</v>
+        <v>21614.66227178235</v>
       </c>
       <c r="E22">
         <v>654.0799999999999</v>
@@ -3091,37 +3219,37 @@
         <v>2269.7</v>
       </c>
       <c r="M22">
-        <v>328.9497243058104</v>
+        <v>323.1540443058104</v>
       </c>
       <c r="N22">
-        <v>1940.750275694189</v>
+        <v>1946.545955694189</v>
       </c>
       <c r="O22">
-        <v>388.1500551388379</v>
+        <v>389.3091911388379</v>
       </c>
       <c r="P22">
-        <v>1552.600220555352</v>
+        <v>1557.236764555352</v>
       </c>
       <c r="Q22">
-        <v>2483.900220555352</v>
+        <v>2488.536764555352</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1142672549689571</v>
+        <v>0.1142317055675416</v>
       </c>
       <c r="T22">
         <v>1.407027892086722</v>
       </c>
       <c r="U22">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.899838584117362</v>
+        <v>7.023585314786017</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3268,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1007465929497546</v>
+        <v>0.1004662126776246</v>
       </c>
       <c r="C23">
-        <v>23239.65265083448</v>
+        <v>23328.01659922634</v>
       </c>
       <c r="D23">
-        <v>21469.91665083448</v>
+        <v>21558.28059922634</v>
       </c>
       <c r="E23">
         <v>943.8639999999996</v>
@@ -3173,37 +3301,37 @@
         <v>2269.7</v>
       </c>
       <c r="M23">
-        <v>358.7852313211009</v>
+        <v>349.6570353211009</v>
       </c>
       <c r="N23">
-        <v>1910.914768678899</v>
+        <v>1920.042964678899</v>
       </c>
       <c r="O23">
-        <v>382.1829537357798</v>
+        <v>384.0085929357798</v>
       </c>
       <c r="P23">
-        <v>1528.731814943119</v>
+        <v>1536.034371743119</v>
       </c>
       <c r="Q23">
-        <v>2460.031814943119</v>
+        <v>2467.334371743119</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1149894833968997</v>
+        <v>0.1149535590017984</v>
       </c>
       <c r="T23">
         <v>1.421869958458944</v>
       </c>
       <c r="U23">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.326068639008982</v>
+        <v>6.491217881303786</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3350,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1006461428136732</v>
+        <v>0.1003538217905455</v>
       </c>
       <c r="C24">
-        <v>22985.02698442712</v>
+        <v>23077.90381260678</v>
       </c>
       <c r="D24">
-        <v>21505.07498442712</v>
+        <v>21597.95181260678</v>
       </c>
       <c r="E24">
         <v>1233.648</v>
@@ -3255,37 +3383,37 @@
         <v>2269.7</v>
       </c>
       <c r="M24">
-        <v>375.8702423363915</v>
+        <v>366.3073703363915</v>
       </c>
       <c r="N24">
-        <v>1893.829757663608</v>
+        <v>1903.392629663608</v>
       </c>
       <c r="O24">
-        <v>378.7659515327217</v>
+        <v>380.6785259327216</v>
       </c>
       <c r="P24">
-        <v>1515.063806130887</v>
+        <v>1522.714103730887</v>
       </c>
       <c r="Q24">
-        <v>2446.363806130887</v>
+        <v>2454.014103730887</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1157302305024819</v>
+        <v>0.115693921498472</v>
       </c>
       <c r="T24">
         <v>1.437092590635583</v>
       </c>
       <c r="U24">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.038520064508574</v>
+        <v>6.196162523062704</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3432,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1005456926775918</v>
+        <v>0.1002414309034664</v>
       </c>
       <c r="C25">
-        <v>22730.51665483887</v>
+        <v>22827.93729986049</v>
       </c>
       <c r="D25">
-        <v>21540.34865483887</v>
+        <v>21637.76929986049</v>
       </c>
       <c r="E25">
         <v>1523.432000000001</v>
@@ -3337,37 +3465,37 @@
         <v>2269.7</v>
       </c>
       <c r="M25">
-        <v>392.9552533516821</v>
+        <v>382.957705351682</v>
       </c>
       <c r="N25">
-        <v>1876.744746648318</v>
+        <v>1886.742294648318</v>
       </c>
       <c r="O25">
-        <v>375.3489493296636</v>
+        <v>377.3484589296636</v>
       </c>
       <c r="P25">
-        <v>1501.395797318654</v>
+        <v>1509.393835718654</v>
       </c>
       <c r="Q25">
-        <v>2432.695797318655</v>
+        <v>2440.693835718655</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1164902177926246</v>
+        <v>0.1164535141898644</v>
       </c>
       <c r="T25">
         <v>1.452710615855771</v>
       </c>
       <c r="U25">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.775975713877765</v>
+        <v>5.92676415249476</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3514,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1007332425415103</v>
+        <v>0.1001290400163874</v>
       </c>
       <c r="C26">
-        <v>22374.96677265466</v>
+        <v>22578.11787148312</v>
       </c>
       <c r="D26">
-        <v>21474.58277265466</v>
+        <v>21677.73387148312</v>
       </c>
       <c r="E26">
         <v>1813.215999999999</v>
@@ -3419,45 +3547,45 @@
         <v>2269.7</v>
       </c>
       <c r="M26">
-        <v>420.4724883669725</v>
+        <v>399.6080403669725</v>
       </c>
       <c r="N26">
-        <v>1849.227511633027</v>
+        <v>1870.091959633027</v>
       </c>
       <c r="O26">
-        <v>369.8455023266055</v>
+        <v>374.0183919266055</v>
       </c>
       <c r="P26">
-        <v>1479.382009306422</v>
+        <v>1496.073567706422</v>
       </c>
       <c r="Q26">
-        <v>2410.682009306422</v>
+        <v>2427.373567706422</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1172702047482973</v>
+        <v>0.1172330961626092</v>
       </c>
       <c r="T26">
         <v>1.468739641739648</v>
       </c>
       <c r="U26">
-        <v>0.0604577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04836619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.397975046631568</v>
+        <v>5.679815646140812</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3596,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1006447924054289</v>
+        <v>0.1001766491293083</v>
       </c>
       <c r="C27">
-        <v>22116.14842230101</v>
+        <v>22271.38675192198</v>
       </c>
       <c r="D27">
-        <v>21505.54842230101</v>
+        <v>21660.78675192198</v>
       </c>
       <c r="E27">
         <v>2103</v>
@@ -3501,37 +3629,37 @@
         <v>2269.7</v>
       </c>
       <c r="M27">
-        <v>437.992175382263</v>
+        <v>422.0540553822631</v>
       </c>
       <c r="N27">
-        <v>1831.707824617737</v>
+        <v>1847.645944617737</v>
       </c>
       <c r="O27">
-        <v>366.3415649235474</v>
+        <v>369.5291889235474</v>
       </c>
       <c r="P27">
-        <v>1465.366259694189</v>
+        <v>1478.11675569419</v>
       </c>
       <c r="Q27">
-        <v>2396.66625969419</v>
+        <v>2409.41675569419</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1180709913561214</v>
+        <v>0.1180334669879606</v>
       </c>
       <c r="T27">
         <v>1.485196108313762</v>
       </c>
       <c r="U27">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.182056044766306</v>
+        <v>5.377747165453216</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3678,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1005563422693475</v>
+        <v>0.1000706582422293</v>
       </c>
       <c r="C28">
-        <v>21857.41950382375</v>
+        <v>22019.36790085273</v>
       </c>
       <c r="D28">
-        <v>21536.60350382375</v>
+        <v>21698.55190085273</v>
       </c>
       <c r="E28">
         <v>2392.784000000001</v>
@@ -3583,37 +3711,37 @@
         <v>2269.7</v>
       </c>
       <c r="M28">
-        <v>455.5118623975536</v>
+        <v>438.9362175975536</v>
       </c>
       <c r="N28">
-        <v>1814.188137602446</v>
+        <v>1830.763782402446</v>
       </c>
       <c r="O28">
-        <v>362.8376275204893</v>
+        <v>366.1527564804892</v>
       </c>
       <c r="P28">
-        <v>1451.350510081957</v>
+        <v>1464.611025921957</v>
       </c>
       <c r="Q28">
-        <v>2382.650510081957</v>
+        <v>2395.911025921957</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.118893420845238</v>
+        <v>0.1188554694572404</v>
       </c>
       <c r="T28">
         <v>1.502097344254743</v>
       </c>
       <c r="U28">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.982746196890677</v>
+        <v>5.170910736012708</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3760,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1004678921332661</v>
+        <v>0.09996466735515024</v>
       </c>
       <c r="C29">
-        <v>21598.7804052154</v>
+        <v>21767.48096534086</v>
       </c>
       <c r="D29">
-        <v>21567.7484052154</v>
+        <v>21736.44896534086</v>
       </c>
       <c r="E29">
         <v>2682.568</v>
@@ -3665,37 +3793,37 @@
         <v>2269.7</v>
       </c>
       <c r="M29">
-        <v>473.0315494128441</v>
+        <v>455.8183798128441</v>
       </c>
       <c r="N29">
-        <v>1796.668450587156</v>
+        <v>1813.881620187156</v>
       </c>
       <c r="O29">
-        <v>359.3336901174312</v>
+        <v>362.7763240374312</v>
       </c>
       <c r="P29">
-        <v>1437.334760469725</v>
+        <v>1451.105296149725</v>
       </c>
       <c r="Q29">
-        <v>2368.634760469725</v>
+        <v>2382.405296149725</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1197383826491249</v>
+        <v>0.1196999925421169</v>
       </c>
       <c r="T29">
         <v>1.519461627755752</v>
       </c>
       <c r="U29">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.798200041450283</v>
+        <v>4.979395523567792</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3842,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1003794419971847</v>
+        <v>0.09985867646807117</v>
       </c>
       <c r="C30">
-        <v>21340.23151671609</v>
+        <v>21515.72663777717</v>
       </c>
       <c r="D30">
-        <v>21598.98351671609</v>
+        <v>21774.47863777717</v>
       </c>
       <c r="E30">
         <v>2972.352000000001</v>
@@ -3747,37 +3875,37 @@
         <v>2269.7</v>
       </c>
       <c r="M30">
-        <v>490.5512364281346</v>
+        <v>472.7005420281346</v>
       </c>
       <c r="N30">
-        <v>1779.148763571865</v>
+        <v>1796.999457971865</v>
       </c>
       <c r="O30">
-        <v>355.8297527143731</v>
+        <v>359.3998915943731</v>
       </c>
       <c r="P30">
-        <v>1423.319010857492</v>
+        <v>1437.599566377492</v>
       </c>
       <c r="Q30">
-        <v>2354.619010857492</v>
+        <v>2368.899566377492</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1206068156142309</v>
+        <v>0.1205679746015733</v>
       </c>
       <c r="T30">
         <v>1.537308252465122</v>
       </c>
       <c r="U30">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.626835754255629</v>
+        <v>4.801559969154657</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3924,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1002909918611033</v>
+        <v>0.09975268558099211</v>
       </c>
       <c r="C31">
-        <v>21081.77323082987</v>
+        <v>21264.10561540646</v>
       </c>
       <c r="D31">
-        <v>21630.30923082986</v>
+        <v>21812.64161540646</v>
       </c>
       <c r="E31">
         <v>3262.135999999999</v>
@@ -3829,37 +3957,37 @@
         <v>2269.7</v>
       </c>
       <c r="M31">
-        <v>508.070923443425</v>
+        <v>489.582704243425</v>
       </c>
       <c r="N31">
-        <v>1761.629076556575</v>
+        <v>1780.117295756575</v>
       </c>
       <c r="O31">
-        <v>352.325815311315</v>
+        <v>356.023459151315</v>
       </c>
       <c r="P31">
-        <v>1409.30326124526</v>
+        <v>1424.09383660526</v>
       </c>
       <c r="Q31">
-        <v>2340.60326124526</v>
+        <v>2355.39383660526</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1214997114797624</v>
+        <v>0.1214604068598876</v>
       </c>
       <c r="T31">
         <v>1.555657598997291</v>
       </c>
       <c r="U31">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.467289693764057</v>
+        <v>4.635988935735532</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1002025417250219</v>
+        <v>0.09964669469391306</v>
       </c>
       <c r="C32">
-        <v>20823.40594234108</v>
+        <v>21012.61860037023</v>
       </c>
       <c r="D32">
-        <v>21661.72594234108</v>
+        <v>21850.93860037023</v>
       </c>
       <c r="E32">
         <v>3551.92</v>
@@ -3911,37 +4039,37 @@
         <v>2269.7</v>
       </c>
       <c r="M32">
-        <v>525.5906104587157</v>
+        <v>506.4648664587157</v>
       </c>
       <c r="N32">
-        <v>1744.109389541284</v>
+        <v>1763.235133541284</v>
       </c>
       <c r="O32">
-        <v>348.8218779082569</v>
+        <v>352.6470267082568</v>
       </c>
       <c r="P32">
-        <v>1395.287511633027</v>
+        <v>1410.588106833027</v>
       </c>
       <c r="Q32">
-        <v>2326.587511633028</v>
+        <v>2341.888106833027</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1224181186557377</v>
+        <v>0.1223783371827251</v>
       </c>
       <c r="T32">
         <v>1.574531212573236</v>
       </c>
       <c r="U32">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.318380037305253</v>
+        <v>4.481455971211013</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4088,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1004612915889404</v>
+        <v>0.09954070380683401</v>
       </c>
       <c r="C33">
-        <v>20441.97218918542</v>
+        <v>20761.26629974971</v>
       </c>
       <c r="D33">
-        <v>21570.07618918542</v>
+        <v>21889.37029974971</v>
       </c>
       <c r="E33">
         <v>3841.704</v>
@@ -3993,45 +4121,45 @@
         <v>2269.7</v>
       </c>
       <c r="M33">
-        <v>555.6869230740061</v>
+        <v>523.3470286740062</v>
       </c>
       <c r="N33">
-        <v>1714.013076925994</v>
+        <v>1746.352971325994</v>
       </c>
       <c r="O33">
-        <v>342.8026153851987</v>
+        <v>349.2705942651987</v>
       </c>
       <c r="P33">
-        <v>1371.210461540795</v>
+        <v>1397.082377060795</v>
       </c>
       <c r="Q33">
-        <v>2302.510461540795</v>
+        <v>2328.382377060795</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1233631463295674</v>
+        <v>0.123322874181587</v>
       </c>
       <c r="T33">
         <v>1.593951887412252</v>
       </c>
       <c r="U33">
-        <v>0.0618577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04948619555335152</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.084494174245165</v>
+        <v>4.336892875365496</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4170,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.100384041452859</v>
+        <v>0.09969071291975494</v>
       </c>
       <c r="C34">
-        <v>20179.46904396281</v>
+        <v>20417.129470994</v>
       </c>
       <c r="D34">
-        <v>21597.35704396281</v>
+        <v>21835.017470994</v>
       </c>
       <c r="E34">
         <v>4131.488000000001</v>
@@ -4075,37 +4203,37 @@
         <v>2269.7</v>
       </c>
       <c r="M34">
-        <v>573.6123076892968</v>
+        <v>549.5022788892968</v>
       </c>
       <c r="N34">
-        <v>1696.087692310703</v>
+        <v>1720.197721110703</v>
       </c>
       <c r="O34">
-        <v>339.2175384621406</v>
+        <v>344.0395442221406</v>
       </c>
       <c r="P34">
-        <v>1356.870153848562</v>
+        <v>1376.158176888562</v>
       </c>
       <c r="Q34">
-        <v>2288.170153848563</v>
+        <v>2307.458176888563</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1243359689349802</v>
+        <v>0.1242951916804154</v>
       </c>
       <c r="T34">
         <v>1.613943758570063</v>
       </c>
       <c r="U34">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.956853731300003</v>
+        <v>4.130465126710158</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4252,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1003067913167776</v>
+        <v>0.09959272203267591</v>
       </c>
       <c r="C35">
-        <v>19917.03499330531</v>
+        <v>20162.81990547823</v>
       </c>
       <c r="D35">
-        <v>21624.70699330531</v>
+        <v>21870.49190547823</v>
       </c>
       <c r="E35">
         <v>4421.272000000001</v>
@@ -4157,37 +4285,37 @@
         <v>2269.7</v>
       </c>
       <c r="M35">
-        <v>591.5376923045873</v>
+        <v>566.6742251045873</v>
       </c>
       <c r="N35">
-        <v>1678.162307695412</v>
+        <v>1703.025774895412</v>
       </c>
       <c r="O35">
-        <v>335.6324615390825</v>
+        <v>340.6051549790825</v>
       </c>
       <c r="P35">
-        <v>1342.52984615633</v>
+        <v>1362.42061991633</v>
       </c>
       <c r="Q35">
-        <v>2273.82984615633</v>
+        <v>2293.72061991633</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1253378310211517</v>
+        <v>0.1252965335821939</v>
       </c>
       <c r="T35">
         <v>1.634532402001242</v>
       </c>
       <c r="U35">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.836949072775761</v>
+        <v>4.00529951680985</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4334,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1002295411806962</v>
+        <v>0.09949473114559684</v>
       </c>
       <c r="C36">
-        <v>19654.67030004075</v>
+        <v>19908.62579518095</v>
       </c>
       <c r="D36">
-        <v>21652.12630004075</v>
+        <v>21906.08179518095</v>
       </c>
       <c r="E36">
         <v>4711.056</v>
@@ -4239,37 +4367,37 @@
         <v>2269.7</v>
       </c>
       <c r="M36">
-        <v>609.4630769198777</v>
+        <v>583.8461713198777</v>
       </c>
       <c r="N36">
-        <v>1660.236923080122</v>
+        <v>1685.853828680122</v>
       </c>
       <c r="O36">
-        <v>332.0473846160244</v>
+        <v>337.1707657360245</v>
       </c>
       <c r="P36">
-        <v>1328.189538464098</v>
+        <v>1348.683062944098</v>
       </c>
       <c r="Q36">
-        <v>2259.489538464098</v>
+        <v>2279.983062944098</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1263700525644798</v>
+        <v>0.1263282191779657</v>
       </c>
       <c r="T36">
         <v>1.655744943718213</v>
       </c>
       <c r="U36">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.724097629458828</v>
+        <v>3.887496589844856</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4416,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1001522910446148</v>
+        <v>0.09939674025851777</v>
       </c>
       <c r="C37">
-        <v>19392.37522833172</v>
+        <v>19654.5477046623</v>
       </c>
       <c r="D37">
-        <v>21679.61522833172</v>
+        <v>21941.7877046623</v>
       </c>
       <c r="E37">
         <v>5000.840000000002</v>
@@ -4321,37 +4449,37 @@
         <v>2269.7</v>
       </c>
       <c r="M37">
-        <v>627.3884615351684</v>
+        <v>601.0181175351684</v>
       </c>
       <c r="N37">
-        <v>1642.311538464831</v>
+        <v>1668.681882464831</v>
       </c>
       <c r="O37">
-        <v>328.4623076929663</v>
+        <v>333.7363764929663</v>
       </c>
       <c r="P37">
-        <v>1313.849230771865</v>
+        <v>1334.945505971865</v>
       </c>
       <c r="Q37">
-        <v>2245.149230771865</v>
+        <v>2266.245505971865</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1274340347706796</v>
+        <v>0.127391648945915</v>
       </c>
       <c r="T37">
         <v>1.677610179026476</v>
       </c>
       <c r="U37">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.617694840045717</v>
+        <v>3.77642525870643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4498,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1000750409085334</v>
+        <v>0.09929874937143875</v>
       </c>
       <c r="C38">
-        <v>19130.15004368396</v>
+        <v>19400.58620216923</v>
       </c>
       <c r="D38">
-        <v>21707.17404368396</v>
+        <v>21977.61020216923</v>
       </c>
       <c r="E38">
         <v>5290.624</v>
@@ -4403,37 +4531,37 @@
         <v>2269.7</v>
       </c>
       <c r="M38">
-        <v>645.3138461504587</v>
+        <v>618.1900637504588</v>
       </c>
       <c r="N38">
-        <v>1624.386153849541</v>
+        <v>1651.509936249541</v>
       </c>
       <c r="O38">
-        <v>324.8772307699082</v>
+        <v>330.3019872499083</v>
       </c>
       <c r="P38">
-        <v>1299.508923079633</v>
+        <v>1321.207948999633</v>
       </c>
       <c r="Q38">
-        <v>2230.808923079633</v>
+        <v>2252.507948999633</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1285312664208232</v>
+        <v>0.1284883108941128</v>
       </c>
       <c r="T38">
         <v>1.700158702938122</v>
       </c>
       <c r="U38">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.517203316711115</v>
+        <v>3.671524557075697</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4580,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09999779077245198</v>
+        <v>0.09920075848435969</v>
       </c>
       <c r="C39">
-        <v>18867.995012955</v>
+        <v>19146.74185966575</v>
       </c>
       <c r="D39">
-        <v>21734.803012955</v>
+        <v>22013.54985966575</v>
       </c>
       <c r="E39">
         <v>5580.407999999999</v>
@@ -4485,37 +4613,37 @@
         <v>2269.7</v>
       </c>
       <c r="M39">
-        <v>663.2392307657493</v>
+        <v>635.3620099657493</v>
       </c>
       <c r="N39">
-        <v>1606.460769234251</v>
+        <v>1634.337990034251</v>
       </c>
       <c r="O39">
-        <v>321.2921538468502</v>
+        <v>326.8675980068501</v>
       </c>
       <c r="P39">
-        <v>1285.1686153874</v>
+        <v>1307.470392027401</v>
       </c>
       <c r="Q39">
-        <v>2216.468615387401</v>
+        <v>2238.770392027401</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.129663330821765</v>
+        <v>0.1296197875073327</v>
       </c>
       <c r="T39">
         <v>1.723423053005694</v>
       </c>
       <c r="U39">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.422143767610815</v>
+        <v>3.572294163641219</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4662,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09992054063637056</v>
+        <v>0.09910276759728062</v>
       </c>
       <c r="C40">
-        <v>18605.9104043627</v>
+        <v>18893.01525286324</v>
       </c>
       <c r="D40">
-        <v>21762.5024043627</v>
+        <v>22049.60725286324</v>
       </c>
       <c r="E40">
         <v>5870.192000000001</v>
@@ -4567,37 +4695,37 @@
         <v>2269.7</v>
       </c>
       <c r="M40">
-        <v>681.1646153810399</v>
+        <v>652.5339561810399</v>
       </c>
       <c r="N40">
-        <v>1588.53538461896</v>
+        <v>1617.16604381896</v>
       </c>
       <c r="O40">
-        <v>317.707076923792</v>
+        <v>323.433208763792</v>
       </c>
       <c r="P40">
-        <v>1270.828307695168</v>
+        <v>1293.732835055168</v>
       </c>
       <c r="Q40">
-        <v>2202.128307695168</v>
+        <v>2225.032835055168</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1308319134291887</v>
+        <v>0.1307877633661404</v>
       </c>
       <c r="T40">
         <v>1.74743786597867</v>
       </c>
       <c r="U40">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.332087352673688</v>
+        <v>3.478286422492765</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4744,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09984329050028914</v>
+        <v>0.09900477671020157</v>
       </c>
       <c r="C41">
-        <v>18343.89648749397</v>
+        <v>18639.40696125125</v>
       </c>
       <c r="D41">
-        <v>21790.27248749397</v>
+        <v>22085.78296125125</v>
       </c>
       <c r="E41">
         <v>6159.976000000001</v>
@@ -4649,37 +4777,37 @@
         <v>2269.7</v>
       </c>
       <c r="M41">
-        <v>699.0899999963303</v>
+        <v>669.7059023963304</v>
       </c>
       <c r="N41">
-        <v>1570.610000003669</v>
+        <v>1599.994097603669</v>
       </c>
       <c r="O41">
-        <v>314.1220000007339</v>
+        <v>319.9988195207339</v>
       </c>
       <c r="P41">
-        <v>1256.488000002936</v>
+        <v>1279.995278082936</v>
       </c>
       <c r="Q41">
-        <v>2187.788000002936</v>
+        <v>2211.295278082936</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1320388102204624</v>
+        <v>0.1319940335154008</v>
       </c>
       <c r="T41">
         <v>1.772240049868794</v>
       </c>
       <c r="U41">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.246649215425645</v>
+        <v>3.389099591146796</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4826,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09976604036420775</v>
+        <v>0.09890678582312251</v>
       </c>
       <c r="C42">
-        <v>18081.95353331349</v>
+        <v>18385.91756812855</v>
       </c>
       <c r="D42">
-        <v>21818.11353331349</v>
+        <v>22122.07756812854</v>
       </c>
       <c r="E42">
         <v>6449.76</v>
@@ -4731,37 +4859,37 @@
         <v>2269.7</v>
       </c>
       <c r="M42">
-        <v>717.0153846116209</v>
+        <v>686.8778486116209</v>
       </c>
       <c r="N42">
-        <v>1552.684615388379</v>
+        <v>1582.822151388379</v>
       </c>
       <c r="O42">
-        <v>310.5369230776758</v>
+        <v>316.5644302776758</v>
       </c>
       <c r="P42">
-        <v>1242.147692310703</v>
+        <v>1266.257721110703</v>
       </c>
       <c r="Q42">
-        <v>2173.447692310703</v>
+        <v>2197.557721110703</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1332859369047786</v>
+        <v>0.1332405126696365</v>
       </c>
       <c r="T42">
         <v>1.797868973221922</v>
       </c>
       <c r="U42">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.165482985040003</v>
+        <v>3.304372101368127</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4908,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09968879022812632</v>
+        <v>0.09880879493604347</v>
       </c>
       <c r="C43">
-        <v>17820.08181417258</v>
+        <v>18132.54766063445</v>
       </c>
       <c r="D43">
-        <v>21846.02581417259</v>
+        <v>22158.49166063446</v>
       </c>
       <c r="E43">
         <v>6739.544000000002</v>
@@ -4813,37 +4941,37 @@
         <v>2269.7</v>
       </c>
       <c r="M43">
-        <v>734.9407692269115</v>
+        <v>704.0497948269115</v>
       </c>
       <c r="N43">
-        <v>1534.759230773088</v>
+        <v>1565.650205173088</v>
       </c>
       <c r="O43">
-        <v>306.9518461546177</v>
+        <v>313.1300410346177</v>
       </c>
       <c r="P43">
-        <v>1227.807384618471</v>
+        <v>1252.520164138471</v>
       </c>
       <c r="Q43">
-        <v>2159.107384618471</v>
+        <v>2183.820164138471</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.134575339069919</v>
+        <v>0.1345292453545243</v>
       </c>
       <c r="T43">
         <v>1.824366673637868</v>
       </c>
       <c r="U43">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.088276082965857</v>
+        <v>3.223777659871343</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4990,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09961154009204491</v>
+        <v>0.09871080404896443</v>
       </c>
       <c r="C44">
-        <v>17558.28160381801</v>
+        <v>17879.29782978054</v>
       </c>
       <c r="D44">
-        <v>21874.00960381801</v>
+        <v>22195.02582978054</v>
       </c>
       <c r="E44">
         <v>7029.328</v>
@@ -4895,37 +5023,37 @@
         <v>2269.7</v>
       </c>
       <c r="M44">
-        <v>752.8661538422019</v>
+        <v>721.2217410422019</v>
       </c>
       <c r="N44">
-        <v>1516.833846157798</v>
+        <v>1548.478258957798</v>
       </c>
       <c r="O44">
-        <v>303.3667692315595</v>
+        <v>309.6956517915596</v>
       </c>
       <c r="P44">
-        <v>1213.467076926238</v>
+        <v>1238.782607166238</v>
       </c>
       <c r="Q44">
-        <v>2144.767076926239</v>
+        <v>2170.082607166239</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1359092033786849</v>
+        <v>0.1358624170975117</v>
       </c>
       <c r="T44">
         <v>1.85177808786126</v>
       </c>
       <c r="U44">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.014745700038098</v>
+        <v>3.147021048922026</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5072,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1004286899559635</v>
+        <v>0.09861281316188536</v>
       </c>
       <c r="C45">
-        <v>16976.06903290705</v>
+        <v>17626.16867048254</v>
       </c>
       <c r="D45">
-        <v>21581.58103290705</v>
+        <v>22231.68067048254</v>
       </c>
       <c r="E45">
         <v>7319.111999999999</v>
@@ -4977,45 +5105,45 @@
         <v>2269.7</v>
       </c>
       <c r="M45">
-        <v>803.1893896574923</v>
+        <v>738.3936872574924</v>
       </c>
       <c r="N45">
-        <v>1466.510610342508</v>
+        <v>1531.306312742508</v>
       </c>
       <c r="O45">
-        <v>293.3021220685015</v>
+        <v>306.2612625485015</v>
       </c>
       <c r="P45">
-        <v>1173.208488274006</v>
+        <v>1225.045050194006</v>
       </c>
       <c r="Q45">
-        <v>2104.508488274006</v>
+        <v>2156.345050194006</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1372898699438988</v>
+        <v>0.1372423667963933</v>
       </c>
       <c r="T45">
         <v>1.880151306092491</v>
       </c>
       <c r="U45">
-        <v>0.06445774444168939</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.825859042993432</v>
+        <v>3.073834512900584</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5154,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1003722398198821</v>
+        <v>0.09851482227480632</v>
       </c>
       <c r="C46">
-        <v>16706.2348635775</v>
+        <v>17373.16078159269</v>
       </c>
       <c r="D46">
-        <v>21601.5308635775</v>
+        <v>22268.45678159269</v>
       </c>
       <c r="E46">
         <v>7608.896000000001</v>
@@ -5059,45 +5187,45 @@
         <v>2269.7</v>
       </c>
       <c r="M46">
-        <v>821.8682126727829</v>
+        <v>755.565633472783</v>
       </c>
       <c r="N46">
-        <v>1447.831787327217</v>
+        <v>1514.134366527217</v>
       </c>
       <c r="O46">
-        <v>289.5663574654434</v>
+        <v>302.8268733054434</v>
       </c>
       <c r="P46">
-        <v>1158.265429861774</v>
+        <v>1211.307493221773</v>
       </c>
       <c r="Q46">
-        <v>2089.565429861774</v>
+        <v>2142.607493221773</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1387198460292989</v>
+        <v>0.1386716004130922</v>
       </c>
       <c r="T46">
         <v>1.909537853546265</v>
       </c>
       <c r="U46">
-        <v>0.06445774444168939</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.76163497383449</v>
+        <v>3.003974637607388</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5236,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1003157896838007</v>
+        <v>0.09931683138772725</v>
       </c>
       <c r="C47">
-        <v>16436.43761128266</v>
+        <v>16785.91116730321</v>
       </c>
       <c r="D47">
-        <v>21621.51761128266</v>
+        <v>21970.99116730321</v>
       </c>
       <c r="E47">
         <v>7898.68</v>
@@ -5141,37 +5269,37 @@
         <v>2269.7</v>
       </c>
       <c r="M47">
-        <v>840.5470356880734</v>
+        <v>805.3382796880735</v>
       </c>
       <c r="N47">
-        <v>1429.152964311927</v>
+        <v>1464.361720311926</v>
       </c>
       <c r="O47">
-        <v>285.8305928623853</v>
+        <v>292.8723440623853</v>
       </c>
       <c r="P47">
-        <v>1143.322371449541</v>
+        <v>1171.489376249541</v>
       </c>
       <c r="Q47">
-        <v>2074.622371449541</v>
+        <v>2102.789376249541</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1402018212450772</v>
+        <v>0.1401528061613074</v>
       </c>
       <c r="T47">
         <v>1.939993002725631</v>
       </c>
       <c r="U47">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.700265307749279</v>
+        <v>2.818318782610344</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5318,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1002593395477193</v>
+        <v>0.09923884050064821</v>
       </c>
       <c r="C48">
-        <v>16166.67737858954</v>
+        <v>16524.70474233881</v>
       </c>
       <c r="D48">
-        <v>21641.54137858954</v>
+        <v>21999.56874233881</v>
       </c>
       <c r="E48">
         <v>8188.464000000002</v>
@@ -5223,37 +5351,37 @@
         <v>2269.7</v>
       </c>
       <c r="M48">
-        <v>859.225858703364</v>
+        <v>823.234685903364</v>
       </c>
       <c r="N48">
-        <v>1410.474141296636</v>
+        <v>1446.465314096636</v>
       </c>
       <c r="O48">
-        <v>282.0948282593272</v>
+        <v>289.2930628193271</v>
       </c>
       <c r="P48">
-        <v>1128.379313037309</v>
+        <v>1157.172251277309</v>
       </c>
       <c r="Q48">
-        <v>2059.679313037309</v>
+        <v>2088.472251277309</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1417386844318103</v>
+        <v>0.1416888713816787</v>
       </c>
       <c r="T48">
         <v>1.971576120393123</v>
       </c>
       <c r="U48">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.641563888015599</v>
+        <v>2.75705098298838</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5400,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1002028894116378</v>
+        <v>0.09916084961356914</v>
       </c>
       <c r="C49">
-        <v>15896.95426844546</v>
+        <v>16263.5727556573</v>
       </c>
       <c r="D49">
-        <v>21661.60226844546</v>
+        <v>22028.2207556573</v>
       </c>
       <c r="E49">
         <v>8478.248000000001</v>
@@ -5305,37 +5433,37 @@
         <v>2269.7</v>
       </c>
       <c r="M49">
-        <v>877.9046817186545</v>
+        <v>841.1310921186546</v>
       </c>
       <c r="N49">
-        <v>1391.795318281345</v>
+        <v>1428.568907881345</v>
       </c>
       <c r="O49">
-        <v>278.3590636562691</v>
+        <v>285.7137815762691</v>
       </c>
       <c r="P49">
-        <v>1113.436254625076</v>
+        <v>1142.855126305076</v>
       </c>
       <c r="Q49">
-        <v>2044.736254625077</v>
+        <v>2074.155126305076</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1433335424557785</v>
+        <v>0.143282901327347</v>
       </c>
       <c r="T49">
         <v>2.004351053821651</v>
       </c>
       <c r="U49">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.585360401036544</v>
+        <v>2.698390323775861</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5482,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1001464392755564</v>
+        <v>0.09908285872649009</v>
       </c>
       <c r="C50">
-        <v>15627.26838417978</v>
+        <v>16002.5154984809</v>
       </c>
       <c r="D50">
-        <v>21681.70038417977</v>
+        <v>22056.9474984809</v>
       </c>
       <c r="E50">
         <v>8768.031999999999</v>
@@ -5387,37 +5515,37 @@
         <v>2269.7</v>
       </c>
       <c r="M50">
-        <v>896.5835047339449</v>
+        <v>859.0274983339449</v>
       </c>
       <c r="N50">
-        <v>1373.116495266055</v>
+        <v>1410.672501666055</v>
       </c>
       <c r="O50">
-        <v>274.623299053211</v>
+        <v>282.134500333211</v>
       </c>
       <c r="P50">
-        <v>1098.493196212844</v>
+        <v>1128.538001332844</v>
       </c>
       <c r="Q50">
-        <v>2029.793196212844</v>
+        <v>2059.838001332844</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1449897411729763</v>
+        <v>0.1449382401170795</v>
       </c>
       <c r="T50">
         <v>2.038386561612815</v>
       </c>
       <c r="U50">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.53149872601495</v>
+        <v>2.642173858697197</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5564,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.101148389139475</v>
+        <v>0.09900486783941102</v>
       </c>
       <c r="C51">
-        <v>14986.21094635753</v>
+        <v>15741.533263553</v>
       </c>
       <c r="D51">
-        <v>21330.42694635753</v>
+        <v>22085.749263553</v>
       </c>
       <c r="E51">
         <v>9057.816000000001</v>
@@ -5469,45 +5597,45 @@
         <v>2269.7</v>
       </c>
       <c r="M51">
-        <v>953.6007509492356</v>
+        <v>876.9239045492355</v>
       </c>
       <c r="N51">
-        <v>1316.099249050764</v>
+        <v>1392.776095450764</v>
       </c>
       <c r="O51">
-        <v>263.2198498101529</v>
+        <v>278.5552190901529</v>
       </c>
       <c r="P51">
-        <v>1052.879399240611</v>
+        <v>1114.220876360612</v>
       </c>
       <c r="Q51">
-        <v>1984.179399240611</v>
+        <v>2045.520876360612</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.146710888859476</v>
+        <v>0.1466584941534682</v>
       </c>
       <c r="T51">
         <v>2.073756795199711</v>
       </c>
       <c r="U51">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.380136548488127</v>
+        <v>2.588251943213582</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5646,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1011135390033936</v>
+        <v>0.09892687695233197</v>
       </c>
       <c r="C52">
-        <v>14708.45387714112</v>
+        <v>15480.626345148</v>
       </c>
       <c r="D52">
-        <v>21342.45387714112</v>
+        <v>22114.626345148</v>
       </c>
       <c r="E52">
         <v>9347.6</v>
@@ -5551,45 +5679,45 @@
         <v>2269.7</v>
       </c>
       <c r="M52">
-        <v>973.0619907645261</v>
+        <v>894.8203107645261</v>
       </c>
       <c r="N52">
-        <v>1296.638009235474</v>
+        <v>1374.879689235474</v>
       </c>
       <c r="O52">
-        <v>259.3276018470948</v>
+        <v>274.9759378470948</v>
       </c>
       <c r="P52">
-        <v>1037.310407388379</v>
+        <v>1099.903751388379</v>
       </c>
       <c r="Q52">
-        <v>1968.610407388379</v>
+        <v>2031.203751388379</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1485008824534357</v>
+        <v>0.1484475583513124</v>
       </c>
       <c r="T52">
         <v>2.110541838130083</v>
       </c>
       <c r="U52">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.332533817518365</v>
+        <v>2.536486904349309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5728,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1010786888673122</v>
+        <v>0.1002768860652529</v>
       </c>
       <c r="C53">
-        <v>14430.71037808608</v>
+        <v>14701.40851486261</v>
       </c>
       <c r="D53">
-        <v>21354.49437808608</v>
+        <v>21625.19251486261</v>
       </c>
       <c r="E53">
         <v>9637.384</v>
@@ -5633,37 +5761,37 @@
         <v>2269.7</v>
       </c>
       <c r="M53">
-        <v>992.5232305798165</v>
+        <v>964.4431609798166</v>
       </c>
       <c r="N53">
-        <v>1277.176769420183</v>
+        <v>1305.256839020183</v>
       </c>
       <c r="O53">
-        <v>255.4353538840367</v>
+        <v>261.0513678040367</v>
       </c>
       <c r="P53">
-        <v>1021.741415536147</v>
+        <v>1044.205471216147</v>
       </c>
       <c r="Q53">
-        <v>1953.041415536147</v>
+        <v>1975.505471216147</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1503639370104141</v>
+        <v>0.1503096455776401</v>
       </c>
       <c r="T53">
         <v>2.148828311384143</v>
       </c>
       <c r="U53">
-        <v>0.0671577444416894</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05372619555335152</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.286797860312122</v>
+        <v>2.353378707869233</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5810,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1029990387312308</v>
+        <v>0.1002268951781739</v>
       </c>
       <c r="C54">
-        <v>13497.0979497389</v>
+        <v>14429.36169477083</v>
       </c>
       <c r="D54">
-        <v>20710.6659497389</v>
+        <v>21642.92969477083</v>
       </c>
       <c r="E54">
         <v>9927.168000000001</v>
@@ -5715,45 +5843,45 @@
         <v>2269.7</v>
       </c>
       <c r="M54">
-        <v>1082.807679995107</v>
+        <v>983.3538111951073</v>
       </c>
       <c r="N54">
-        <v>1186.892320004893</v>
+        <v>1286.346188804893</v>
       </c>
       <c r="O54">
-        <v>237.3784640009785</v>
+        <v>257.2692377609785</v>
       </c>
       <c r="P54">
-        <v>949.513856003914</v>
+        <v>1029.076951043914</v>
       </c>
       <c r="Q54">
-        <v>1880.813856003914</v>
+        <v>1960.376951043914</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1523046188406</v>
+        <v>0.1522493197717314</v>
       </c>
       <c r="T54">
         <v>2.188710054357123</v>
       </c>
       <c r="U54">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.096124770753617</v>
+        <v>2.308121425025594</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5892,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1030017885951494</v>
+        <v>0.1001769042910948</v>
       </c>
       <c r="C55">
-        <v>13206.41984784597</v>
+        <v>14157.34399495687</v>
       </c>
       <c r="D55">
-        <v>20709.77184784597</v>
+        <v>21660.69599495687</v>
       </c>
       <c r="E55">
         <v>10216.952</v>
@@ -5797,45 +5925,45 @@
         <v>2269.7</v>
       </c>
       <c r="M55">
-        <v>1103.630904610398</v>
+        <v>1002.264461410398</v>
       </c>
       <c r="N55">
-        <v>1166.069095389602</v>
+        <v>1267.435538589602</v>
       </c>
       <c r="O55">
-        <v>233.2138190779204</v>
+        <v>253.4871077179204</v>
       </c>
       <c r="P55">
-        <v>932.8552763116816</v>
+        <v>1013.948430871682</v>
       </c>
       <c r="Q55">
-        <v>1864.155276311682</v>
+        <v>1945.248430871682</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1543278828763257</v>
+        <v>0.1542715332932309</v>
       </c>
       <c r="T55">
         <v>2.230288892775761</v>
       </c>
       <c r="U55">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.056575246777133</v>
+        <v>2.264571964176055</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5974,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1030045384590679</v>
+        <v>0.1013365134040158</v>
       </c>
       <c r="C56">
-        <v>12915.74182314841</v>
+        <v>13462.81428962252</v>
       </c>
       <c r="D56">
-        <v>20708.87782314841</v>
+        <v>21255.95028962252</v>
       </c>
       <c r="E56">
         <v>10506.736</v>
@@ -5879,37 +6007,37 @@
         <v>2269.7</v>
       </c>
       <c r="M56">
-        <v>1124.454129225688</v>
+        <v>1064.990452425688</v>
       </c>
       <c r="N56">
-        <v>1145.245870774311</v>
+        <v>1204.709547574312</v>
       </c>
       <c r="O56">
-        <v>229.0491741548623</v>
+        <v>240.9419095148623</v>
       </c>
       <c r="P56">
-        <v>916.1966966194492</v>
+        <v>963.7676380594494</v>
       </c>
       <c r="Q56">
-        <v>1847.496696619449</v>
+        <v>1895.06763805945</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1564391149136046</v>
+        <v>0.1563816691417521</v>
       </c>
       <c r="T56">
         <v>2.273675506777819</v>
       </c>
       <c r="U56">
-        <v>0.07185774444168941</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.05748619555335153</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.018490519984964</v>
+        <v>2.131192814762227</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6056,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1070992883229865</v>
+        <v>0.1013089225169367</v>
       </c>
       <c r="C57">
-        <v>11375.15122030104</v>
+        <v>13182.48476727766</v>
       </c>
       <c r="D57">
-        <v>19458.07122030104</v>
+        <v>21265.40476727766</v>
       </c>
       <c r="E57">
         <v>10796.52</v>
@@ -5961,45 +6089,45 @@
         <v>2269.7</v>
       </c>
       <c r="M57">
-        <v>1293.501869840979</v>
+        <v>1084.712497840979</v>
       </c>
       <c r="N57">
-        <v>976.198130159021</v>
+        <v>1184.987502159021</v>
       </c>
       <c r="O57">
-        <v>195.2396260318042</v>
+        <v>236.9975004318042</v>
       </c>
       <c r="P57">
-        <v>780.9585041272169</v>
+        <v>947.9900017272168</v>
       </c>
       <c r="Q57">
-        <v>1712.258504127217</v>
+        <v>1879.290001727217</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1586441794858738</v>
+        <v>0.1585855888057631</v>
       </c>
       <c r="T57">
         <v>2.318990414735523</v>
       </c>
       <c r="U57">
-        <v>0.0811577444416894</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.06492619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.754694023193823</v>
+        <v>2.092443854493823</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6138,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1092820381869051</v>
+        <v>0.1012813316298577</v>
       </c>
       <c r="C58">
-        <v>10478.4247180818</v>
+        <v>12902.16365922835</v>
       </c>
       <c r="D58">
-        <v>18851.1287180818</v>
+        <v>21274.86765922836</v>
       </c>
       <c r="E58">
         <v>11086.304</v>
@@ -6043,45 +6171,45 @@
         <v>2269.7</v>
       </c>
       <c r="M58">
-        <v>1393.291234456269</v>
+        <v>1104.434543256269</v>
       </c>
       <c r="N58">
-        <v>876.4087655437306</v>
+        <v>1165.265456743731</v>
       </c>
       <c r="O58">
-        <v>175.2817531087461</v>
+        <v>233.0530913487461</v>
       </c>
       <c r="P58">
-        <v>701.1270124349845</v>
+        <v>932.2123653949844</v>
       </c>
       <c r="Q58">
-        <v>1632.427012434985</v>
+        <v>1863.512365394984</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1609494742659733</v>
+        <v>0.16088968663632</v>
       </c>
       <c r="T58">
         <v>2.36636509123676</v>
       </c>
       <c r="U58">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.629020511914545</v>
+        <v>2.055078785663576</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6220,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1093967880508237</v>
+        <v>0.1012537407427786</v>
       </c>
       <c r="C59">
-        <v>10157.77888278514</v>
+        <v>12621.85097671245</v>
       </c>
       <c r="D59">
-        <v>18820.26688278514</v>
+        <v>21284.33897671245</v>
       </c>
       <c r="E59">
         <v>11376.088</v>
@@ -6125,45 +6253,45 @@
         <v>2269.7</v>
       </c>
       <c r="M59">
-        <v>1418.17143507156</v>
+        <v>1124.15658867156</v>
       </c>
       <c r="N59">
-        <v>851.5285649284401</v>
+        <v>1145.54341132844</v>
       </c>
       <c r="O59">
-        <v>170.305712985688</v>
+        <v>229.108682265688</v>
       </c>
       <c r="P59">
-        <v>681.2228519427521</v>
+        <v>916.434729062752</v>
       </c>
       <c r="Q59">
-        <v>1612.522851942752</v>
+        <v>1847.734729062752</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1633619920591008</v>
+        <v>0.1633009518078331</v>
       </c>
       <c r="T59">
         <v>2.415943241063635</v>
       </c>
       <c r="U59">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.600441204687974</v>
+        <v>2.019024771880004</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6302,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1095115379147423</v>
+        <v>0.1048453498556995</v>
       </c>
       <c r="C60">
-        <v>9837.233932284005</v>
+        <v>11166.16721465491</v>
       </c>
       <c r="D60">
-        <v>18789.505932284</v>
+        <v>20118.43921465491</v>
       </c>
       <c r="E60">
         <v>11665.872</v>
@@ -6207,45 +6335,45 @@
         <v>2269.7</v>
       </c>
       <c r="M60">
-        <v>1443.05163568685</v>
+        <v>1274.97691568685</v>
       </c>
       <c r="N60">
-        <v>826.6483643131498</v>
+        <v>994.7230843131497</v>
       </c>
       <c r="O60">
-        <v>165.32967286263</v>
+        <v>198.9446168626299</v>
       </c>
       <c r="P60">
-        <v>661.3186914505199</v>
+        <v>795.7784674505198</v>
       </c>
       <c r="Q60">
-        <v>1592.61869145052</v>
+        <v>1727.07846745052</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1658893916519009</v>
+        <v>0.1658270391303706</v>
       </c>
       <c r="T60">
         <v>2.46788225516798</v>
       </c>
       <c r="U60">
-        <v>0.08585774444168939</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.572847390814044</v>
+        <v>1.780189093680395</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6384,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1096262877786609</v>
+        <v>0.1048801589686205</v>
       </c>
       <c r="C61">
-        <v>9516.789372709452</v>
+        <v>10865.7081940663</v>
       </c>
       <c r="D61">
-        <v>18758.84537270945</v>
+        <v>20107.76419406631</v>
       </c>
       <c r="E61">
         <v>11955.656</v>
@@ -6289,45 +6417,45 @@
         <v>2269.7</v>
       </c>
       <c r="M61">
-        <v>1467.931836302141</v>
+        <v>1296.959276302141</v>
       </c>
       <c r="N61">
-        <v>801.7681636978591</v>
+        <v>972.740723697859</v>
       </c>
       <c r="O61">
-        <v>160.3536327395718</v>
+        <v>194.5481447395718</v>
       </c>
       <c r="P61">
-        <v>641.4145309582873</v>
+        <v>778.1925789582872</v>
       </c>
       <c r="Q61">
-        <v>1572.714530958287</v>
+        <v>1709.492578958287</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1685400790297158</v>
+        <v>0.1684763502247393</v>
       </c>
       <c r="T61">
         <v>2.52235487971644</v>
       </c>
       <c r="U61">
-        <v>0.08585774444168939</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.546188960461263</v>
+        <v>1.750016397177338</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6466,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1097410376425795</v>
+        <v>0.1067869680815415</v>
       </c>
       <c r="C62">
-        <v>9196.444713410896</v>
+        <v>10007.97543325157</v>
       </c>
       <c r="D62">
-        <v>18728.2847134109</v>
+        <v>19539.81543325157</v>
       </c>
       <c r="E62">
         <v>12245.44</v>
@@ -6371,37 +6499,37 @@
         <v>2269.7</v>
       </c>
       <c r="M62">
-        <v>1492.812036917431</v>
+        <v>1386.751092917431</v>
       </c>
       <c r="N62">
-        <v>776.8879630825686</v>
+        <v>882.9489070825684</v>
       </c>
       <c r="O62">
-        <v>155.3775926165137</v>
+        <v>176.5897814165137</v>
       </c>
       <c r="P62">
-        <v>621.5103704660548</v>
+        <v>706.3591256660548</v>
       </c>
       <c r="Q62">
-        <v>1552.810370466055</v>
+        <v>1637.659125666055</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1713233007764214</v>
+        <v>0.1712581268738263</v>
       </c>
       <c r="T62">
         <v>2.579551135492324</v>
       </c>
       <c r="U62">
-        <v>0.08585774444168939</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.520419144453575</v>
+        <v>1.636703235059314</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6548,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.117810187506498</v>
+        <v>0.1068529771944624</v>
       </c>
       <c r="C63">
-        <v>6981.677932479302</v>
+        <v>9699.104415840018</v>
       </c>
       <c r="D63">
-        <v>16803.3019324793</v>
+        <v>19520.72841584002</v>
       </c>
       <c r="E63">
         <v>12535.224</v>
@@ -6453,45 +6581,45 @@
         <v>2269.7</v>
       </c>
       <c r="M63">
-        <v>1805.824468732722</v>
+        <v>1409.863611132722</v>
       </c>
       <c r="N63">
-        <v>463.8755312672779</v>
+        <v>859.8363888672779</v>
       </c>
       <c r="O63">
-        <v>92.77510625345559</v>
+        <v>171.9672777734556</v>
       </c>
       <c r="P63">
-        <v>371.1004250138223</v>
+        <v>687.8691110938223</v>
       </c>
       <c r="Q63">
-        <v>1302.400425013823</v>
+        <v>1619.169111093822</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1742492518434708</v>
+        <v>0.1741825587356871</v>
       </c>
       <c r="T63">
         <v>2.639680532590046</v>
       </c>
       <c r="U63">
-        <v>0.1021577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.08172619555335153</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.256877420424374</v>
+        <v>1.609872034484572</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6630,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1357795749464348</v>
+        <v>0.1069189863073833</v>
       </c>
       <c r="C64">
-        <v>3562.108549896027</v>
+        <v>9390.270651462935</v>
       </c>
       <c r="D64">
-        <v>13673.51654989603</v>
+        <v>19501.67865146293</v>
       </c>
       <c r="E64">
         <v>12825.008</v>
@@ -6535,45 +6663,45 @@
         <v>2269.7</v>
       </c>
       <c r="M64">
-        <v>2422.936230148012</v>
+        <v>1432.976129348012</v>
       </c>
       <c r="N64">
-        <v>-153.2362301480125</v>
+        <v>836.7238706519875</v>
       </c>
       <c r="O64">
-        <v>-30.6472460296025</v>
+        <v>167.3447741303975</v>
       </c>
       <c r="P64">
-        <v>-122.58898411841</v>
+        <v>669.37909652159</v>
       </c>
       <c r="Q64">
-        <v>808.7110158815901</v>
+        <v>1600.67909652159</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1785066957748341</v>
+        <v>0.1772609080639616</v>
       </c>
       <c r="T64">
-        <v>2.727172609833971</v>
+        <v>2.702974634798176</v>
       </c>
       <c r="U64">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V64">
-        <v>0.1873511957730186</v>
+        <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.1095919847612867</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.9367559788650931</v>
+        <v>1.583906356509014</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6712,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1366701523908516</v>
+        <v>0.1069849954203043</v>
       </c>
       <c r="C65">
-        <v>3147.256062766872</v>
+        <v>9081.4740311639</v>
       </c>
       <c r="D65">
-        <v>13548.44806276687</v>
+        <v>19482.6660311639</v>
       </c>
       <c r="E65">
         <v>13114.792</v>
@@ -6617,45 +6745,45 @@
         <v>2269.7</v>
       </c>
       <c r="M65">
-        <v>2462.015846763303</v>
+        <v>1456.088647563303</v>
       </c>
       <c r="N65">
-        <v>-192.3158467633029</v>
+        <v>813.611352436697</v>
       </c>
       <c r="O65">
-        <v>-38.46316935266059</v>
+        <v>162.7222704873394</v>
       </c>
       <c r="P65">
-        <v>-153.8526774106423</v>
+        <v>650.8890819493575</v>
       </c>
       <c r="Q65">
-        <v>777.4473225893578</v>
+        <v>1582.189081949358</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.182093363228208</v>
+        <v>0.1805056546532239</v>
       </c>
       <c r="T65">
-        <v>2.800879977667321</v>
+        <v>2.769690039828367</v>
       </c>
       <c r="U65">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V65">
-        <v>0.184377367268685</v>
+        <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.1099930285657376</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.9218868363434249</v>
+        <v>1.558764985770776</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6794,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1375607298352685</v>
+        <v>0.1070510045332252</v>
       </c>
       <c r="C66">
-        <v>2734.670782953646</v>
+        <v>8772.714446410948</v>
       </c>
       <c r="D66">
-        <v>13425.64678295365</v>
+        <v>19463.69044641095</v>
       </c>
       <c r="E66">
         <v>13404.576</v>
@@ -6699,45 +6827,45 @@
         <v>2269.7</v>
       </c>
       <c r="M66">
-        <v>2501.095463378594</v>
+        <v>1479.201165778594</v>
       </c>
       <c r="N66">
-        <v>-231.3954633785943</v>
+        <v>790.4988342214062</v>
       </c>
       <c r="O66">
-        <v>-46.27909267571886</v>
+        <v>158.0997668442812</v>
       </c>
       <c r="P66">
-        <v>-185.1163707028754</v>
+        <v>632.399067377125</v>
       </c>
       <c r="Q66">
-        <v>746.1836292971248</v>
+        <v>1563.699067377125</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1858792899845471</v>
+        <v>0.1839306649418896</v>
       </c>
       <c r="T66">
-        <v>2.878682199269192</v>
+        <v>2.840111856249124</v>
       </c>
       <c r="U66">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V66">
-        <v>0.1814964709051118</v>
+        <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.1103815397512993</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.9074823545255587</v>
+        <v>1.534409282868107</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6876,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1384513072796854</v>
+        <v>0.1071170136461462</v>
       </c>
       <c r="C67">
-        <v>2324.291615244143</v>
+        <v>8463.991789094554</v>
       </c>
       <c r="D67">
-        <v>13305.05161524415</v>
+        <v>19444.75178909456</v>
       </c>
       <c r="E67">
         <v>13694.36</v>
@@ -6781,45 +6909,45 @@
         <v>2269.7</v>
       </c>
       <c r="M67">
-        <v>2540.175079993885</v>
+        <v>1502.313683993884</v>
       </c>
       <c r="N67">
-        <v>-270.4750799938847</v>
+        <v>767.3863160061157</v>
       </c>
       <c r="O67">
-        <v>-54.09501599877694</v>
+        <v>153.4772632012232</v>
       </c>
       <c r="P67">
-        <v>-216.3800639951078</v>
+        <v>613.9090528048926</v>
       </c>
       <c r="Q67">
-        <v>714.9199360048924</v>
+        <v>1545.209052804893</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.189881555412677</v>
+        <v>0.1875513901041934</v>
       </c>
       <c r="T67">
-        <v>2.960930262105455</v>
+        <v>2.914557776465352</v>
       </c>
       <c r="U67">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V67">
-        <v>0.1787042175065716</v>
+        <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.1107580967465361</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8935210875328579</v>
+        <v>1.510802986208598</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6958,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1393418847241023</v>
+        <v>0.1146806227590671</v>
       </c>
       <c r="C68">
-        <v>1916.059640022093</v>
+        <v>6223.713465504814</v>
       </c>
       <c r="D68">
-        <v>13186.6036400221</v>
+        <v>17494.25746550482</v>
       </c>
       <c r="E68">
         <v>13984.144</v>
@@ -6863,45 +6991,45 @@
         <v>2269.7</v>
       </c>
       <c r="M68">
-        <v>2579.254696609175</v>
+        <v>1797.011767009175</v>
       </c>
       <c r="N68">
-        <v>-309.5546966091752</v>
+        <v>472.6882329908251</v>
       </c>
       <c r="O68">
-        <v>-61.91093932183503</v>
+        <v>94.53764659816503</v>
       </c>
       <c r="P68">
-        <v>-247.6437572873401</v>
+        <v>378.1505863926601</v>
       </c>
       <c r="Q68">
-        <v>683.6562427126601</v>
+        <v>1309.45058639266</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1941192482189322</v>
+        <v>0.1913850990995739</v>
       </c>
       <c r="T68">
-        <v>3.048016446285026</v>
+        <v>2.993382868459006</v>
       </c>
       <c r="U68">
-        <v>0.1348577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V68">
-        <v>0.1759965778473811</v>
+        <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.1111232429237354</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8799828892369055</v>
+        <v>1.263041256417333</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7040,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1402324621685192</v>
+        <v>0.1313004824284483</v>
       </c>
       <c r="C69">
-        <v>1509.918017280732</v>
+        <v>2774.354636552747</v>
       </c>
       <c r="D69">
-        <v>13070.24601728074</v>
+        <v>14334.68263655275</v>
       </c>
       <c r="E69">
         <v>14273.928</v>
@@ -6945,37 +7073,37 @@
         <v>2269.7</v>
       </c>
       <c r="M69">
-        <v>2618.334313224465</v>
+        <v>2379.523318824465</v>
       </c>
       <c r="N69">
-        <v>-348.6343132244656</v>
+        <v>-109.8233188244653</v>
       </c>
       <c r="O69">
-        <v>-69.72686264489312</v>
+        <v>-21.96466376489307</v>
       </c>
       <c r="P69">
-        <v>-278.9074505795725</v>
+        <v>-87.85865505957227</v>
       </c>
       <c r="Q69">
-        <v>652.3925494204277</v>
+        <v>843.4413449404279</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1986137708922332</v>
+        <v>0.1965198928920184</v>
       </c>
       <c r="T69">
-        <v>3.140380581020937</v>
+        <v>3.098959633295773</v>
       </c>
       <c r="U69">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1733697632526441</v>
+        <v>0.1907693008968939</v>
       </c>
       <c r="W69">
-        <v>0.1114774892150481</v>
+        <v>0.09917748921504813</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8668488162632203</v>
+        <v>0.9538465044844695</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7122,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1411230396129361</v>
+        <v>0.1320680598728652</v>
       </c>
       <c r="C70">
-        <v>1105.811895673673</v>
+        <v>2365.991425161246</v>
       </c>
       <c r="D70">
-        <v>12955.92389567368</v>
+        <v>14216.10342516125</v>
       </c>
       <c r="E70">
         <v>14563.712</v>
@@ -7027,37 +7155,37 @@
         <v>2269.7</v>
       </c>
       <c r="M70">
-        <v>2657.413929839756</v>
+        <v>2415.038592239756</v>
       </c>
       <c r="N70">
-        <v>-387.713929839756</v>
+        <v>-145.3385922397561</v>
       </c>
       <c r="O70">
-        <v>-77.5427859679512</v>
+        <v>-29.06771844795121</v>
       </c>
       <c r="P70">
-        <v>-310.1711438718048</v>
+        <v>-116.2708737918048</v>
       </c>
       <c r="Q70">
-        <v>621.1288561281954</v>
+        <v>815.0291262081953</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2033892012326156</v>
+        <v>0.201229889544894</v>
       </c>
       <c r="T70">
-        <v>3.238517474177841</v>
+        <v>3.195802121836267</v>
       </c>
       <c r="U70">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V70">
-        <v>0.1708202079106934</v>
+        <v>0.1879638700013513</v>
       </c>
       <c r="W70">
-        <v>0.1118213164977929</v>
+        <v>0.09952131649779286</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8541010395534672</v>
+        <v>0.9398193500067565</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7204,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.142013617057353</v>
+        <v>0.1328356373172821</v>
       </c>
       <c r="C71">
-        <v>703.6883262975462</v>
+        <v>1959.573937789999</v>
       </c>
       <c r="D71">
-        <v>12843.58432629755</v>
+        <v>14099.46993779</v>
       </c>
       <c r="E71">
         <v>14853.496</v>
@@ -7109,37 +7237,37 @@
         <v>2269.7</v>
       </c>
       <c r="M71">
-        <v>2696.493546455046</v>
+        <v>2450.553865655046</v>
       </c>
       <c r="N71">
-        <v>-426.7935464550465</v>
+        <v>-180.8538656550463</v>
       </c>
       <c r="O71">
-        <v>-85.35870929100929</v>
+        <v>-36.17077313100926</v>
       </c>
       <c r="P71">
-        <v>-341.4348371640372</v>
+        <v>-144.6830925240371</v>
       </c>
       <c r="Q71">
-        <v>589.865162835963</v>
+        <v>786.6169074759631</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2084727238530225</v>
+        <v>0.206243756949568</v>
       </c>
       <c r="T71">
-        <v>3.342985779796481</v>
+        <v>3.298892512863243</v>
       </c>
       <c r="U71">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V71">
-        <v>0.168344552723582</v>
+        <v>0.1852397559433607</v>
       </c>
       <c r="W71">
-        <v>0.1121551777723421</v>
+        <v>0.09985517777234208</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8417227636179097</v>
+        <v>0.9261987797168036</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7286,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1429041945017699</v>
+        <v>0.133603214761699</v>
       </c>
       <c r="C72">
-        <v>303.496180921451</v>
+        <v>1555.054674108942</v>
       </c>
       <c r="D72">
-        <v>12733.17618092145</v>
+        <v>13984.73467410895</v>
       </c>
       <c r="E72">
         <v>15143.28</v>
@@ -7191,37 +7319,37 @@
         <v>2269.7</v>
       </c>
       <c r="M72">
-        <v>2735.573163070337</v>
+        <v>2486.069139070337</v>
       </c>
       <c r="N72">
-        <v>-465.8731630703373</v>
+        <v>-216.3691390703375</v>
       </c>
       <c r="O72">
-        <v>-93.17463261406748</v>
+        <v>-43.2738278140675</v>
       </c>
       <c r="P72">
-        <v>-372.6985304562699</v>
+        <v>-173.09531125627</v>
       </c>
       <c r="Q72">
-        <v>558.6014695437303</v>
+        <v>758.2046887437302</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2138951479814566</v>
+        <v>0.2115918821812203</v>
       </c>
       <c r="T72">
-        <v>3.45441863912303</v>
+        <v>3.408855596625351</v>
       </c>
       <c r="U72">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V72">
-        <v>0.1659396305418165</v>
+        <v>0.1825934737155984</v>
       </c>
       <c r="W72">
-        <v>0.1124795001533328</v>
+        <v>0.1001795001533328</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8296981527090823</v>
+        <v>0.912967368577992</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7368,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1437947719461868</v>
+        <v>0.1343707922061159</v>
       </c>
       <c r="C73">
-        <v>-94.81392560182576</v>
+        <v>1152.387667454626</v>
       </c>
       <c r="D73">
-        <v>12624.65007439818</v>
+        <v>13871.85166745463</v>
       </c>
       <c r="E73">
         <v>15433.064</v>
@@ -7273,37 +7401,37 @@
         <v>2269.7</v>
       </c>
       <c r="M73">
-        <v>2774.652779685627</v>
+        <v>2521.584412485627</v>
       </c>
       <c r="N73">
-        <v>-504.9527796856273</v>
+        <v>-251.8844124856273</v>
       </c>
       <c r="O73">
-        <v>-100.9905559371255</v>
+        <v>-50.37688249712546</v>
       </c>
       <c r="P73">
-        <v>-403.9622237485019</v>
+        <v>-201.5075299885019</v>
       </c>
       <c r="Q73">
-        <v>527.3377762514983</v>
+        <v>729.7924700114984</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2196915323946102</v>
+        <v>0.2173088436357451</v>
       </c>
       <c r="T73">
-        <v>3.57353652323072</v>
+        <v>3.526402341336569</v>
       </c>
       <c r="U73">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V73">
-        <v>0.1636024526468614</v>
+        <v>0.1800217346491816</v>
       </c>
       <c r="W73">
-        <v>0.1127946866926054</v>
+        <v>0.1004946866926054</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8180122632343066</v>
+        <v>0.9001086732459078</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7450,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1446853493906037</v>
+        <v>0.1351383696505328</v>
       </c>
       <c r="C74">
-        <v>-491.2897089904473</v>
+        <v>751.5284234280007</v>
       </c>
       <c r="D74">
-        <v>12517.95829100955</v>
+        <v>13760.776423428</v>
       </c>
       <c r="E74">
         <v>15722.848</v>
@@ -7355,37 +7483,37 @@
         <v>2269.7</v>
       </c>
       <c r="M74">
-        <v>2813.732396300918</v>
+        <v>2557.099685900918</v>
       </c>
       <c r="N74">
-        <v>-544.0323963009178</v>
+        <v>-287.399685900918</v>
       </c>
       <c r="O74">
-        <v>-108.8064792601836</v>
+        <v>-57.47993718018361</v>
       </c>
       <c r="P74">
-        <v>-435.2259170407342</v>
+        <v>-229.9197487207344</v>
       </c>
       <c r="Q74">
-        <v>496.074082959266</v>
+        <v>701.3802512792657</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2259019442658463</v>
+        <v>0.2234341594798788</v>
       </c>
       <c r="T74">
-        <v>3.701162827631817</v>
+        <v>3.65234528209859</v>
       </c>
       <c r="U74">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V74">
-        <v>0.1613301963600994</v>
+        <v>0.1775214327790541</v>
       </c>
       <c r="W74">
-        <v>0.1131011180502316</v>
+        <v>0.1008011180502316</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8066509818004969</v>
+        <v>0.8876071638952702</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7532,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2101133593303373</v>
+        <v>0.1359059470949497</v>
       </c>
       <c r="C75">
-        <v>-5576.065006986639</v>
+        <v>352.4338614187582</v>
       </c>
       <c r="D75">
-        <v>7722.96699301336</v>
+        <v>13651.46586141876</v>
       </c>
       <c r="E75">
         <v>16012.632</v>
@@ -7437,45 +7565,45 @@
         <v>2269.7</v>
       </c>
       <c r="M75">
-        <v>4648.806309716208</v>
+        <v>2592.614959316208</v>
       </c>
       <c r="N75">
-        <v>-2379.106309716209</v>
+        <v>-322.9149593162083</v>
       </c>
       <c r="O75">
-        <v>-475.8212619432418</v>
+        <v>-64.58299186324166</v>
       </c>
       <c r="P75">
-        <v>-1903.285047772967</v>
+        <v>-258.3319674529666</v>
       </c>
       <c r="Q75">
-        <v>-971.9850477729667</v>
+        <v>672.9680325470335</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2420554699620508</v>
+        <v>0.230013202423578</v>
       </c>
       <c r="T75">
-        <v>4.033123868284088</v>
+        <v>3.787617329583722</v>
       </c>
       <c r="U75">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V75">
-        <v>0.09764657199230813</v>
+        <v>0.1750896323300259</v>
       </c>
       <c r="W75">
-        <v>0.1982991540281968</v>
+        <v>0.1010991540281967</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4882328599615405</v>
+        <v>0.8754481616501295</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7614,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2118529367747542</v>
+        <v>0.1366735245393666</v>
       </c>
       <c r="C76">
-        <v>-5943.709636736825</v>
+        <v>-44.93774110518643</v>
       </c>
       <c r="D76">
-        <v>7645.106363263175</v>
+        <v>13543.87825889481</v>
       </c>
       <c r="E76">
         <v>16302.416</v>
@@ -7519,45 +7647,45 @@
         <v>2269.7</v>
       </c>
       <c r="M76">
-        <v>4712.488587931499</v>
+        <v>2628.130232731498</v>
       </c>
       <c r="N76">
-        <v>-2442.788587931499</v>
+        <v>-358.4302327314986</v>
       </c>
       <c r="O76">
-        <v>-488.5577175862998</v>
+        <v>-71.68604654629972</v>
       </c>
       <c r="P76">
-        <v>-1954.230870345199</v>
+        <v>-286.7441861851988</v>
       </c>
       <c r="Q76">
-        <v>-1022.930870345199</v>
+        <v>644.5558138148014</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2496037572682835</v>
+        <v>0.2370983255937157</v>
       </c>
       <c r="T76">
-        <v>4.188244017064245</v>
+        <v>3.933294919183096</v>
       </c>
       <c r="U76">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V76">
-        <v>0.0963270237221418</v>
+        <v>0.172723556217458</v>
       </c>
       <c r="W76">
-        <v>0.1985891349797304</v>
+        <v>0.1013891349797304</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.481635118610709</v>
+        <v>0.86361778108729</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7696,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2135925142191711</v>
+        <v>0.1374411019837835</v>
       </c>
       <c r="C77">
-        <v>-6309.800001232546</v>
+        <v>-440.6268016945141</v>
       </c>
       <c r="D77">
-        <v>7568.799998767458</v>
+        <v>13437.97319830549</v>
       </c>
       <c r="E77">
         <v>16592.2</v>
@@ -7601,45 +7729,45 @@
         <v>2269.7</v>
       </c>
       <c r="M77">
-        <v>4776.17086614679</v>
+        <v>2663.64550614679</v>
       </c>
       <c r="N77">
-        <v>-2506.47086614679</v>
+        <v>-393.9455061467897</v>
       </c>
       <c r="O77">
-        <v>-501.2941732293581</v>
+        <v>-78.78910122935795</v>
       </c>
       <c r="P77">
-        <v>-2005.176692917432</v>
+        <v>-315.1564049174318</v>
       </c>
       <c r="Q77">
-        <v>-1073.876692917432</v>
+        <v>616.1435950825684</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2577559075590149</v>
+        <v>0.2447502586174643</v>
       </c>
       <c r="T77">
-        <v>4.355773777746816</v>
+        <v>4.090626715950421</v>
       </c>
       <c r="U77">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V77">
-        <v>0.09504266340584655</v>
+        <v>0.1704205754678919</v>
       </c>
       <c r="W77">
-        <v>0.1988713831058899</v>
+        <v>0.1016713831058899</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4752133170292328</v>
+        <v>0.8521028773394593</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7778,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.215332091663588</v>
+        <v>0.1382086794282004</v>
       </c>
       <c r="C78">
-        <v>-6674.38218025292</v>
+        <v>-834.6724835435452</v>
       </c>
       <c r="D78">
-        <v>7494.001819747082</v>
+        <v>13333.71151645646</v>
       </c>
       <c r="E78">
         <v>16881.984</v>
@@ -7683,45 +7811,45 @@
         <v>2269.7</v>
       </c>
       <c r="M78">
-        <v>4839.85314436208</v>
+        <v>2699.16077956208</v>
       </c>
       <c r="N78">
-        <v>-2570.153144362081</v>
+        <v>-429.46077956208</v>
       </c>
       <c r="O78">
-        <v>-514.0306288724162</v>
+        <v>-85.892155912416</v>
       </c>
       <c r="P78">
-        <v>-2056.122515489665</v>
+        <v>-343.568623649664</v>
       </c>
       <c r="Q78">
-        <v>-1124.822515489665</v>
+        <v>587.7313763503362</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2665874037073072</v>
+        <v>0.2530398527265253</v>
       </c>
       <c r="T78">
-        <v>4.5372643518196</v>
+        <v>4.261069495781689</v>
       </c>
       <c r="U78">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V78">
-        <v>0.09379210204524331</v>
+        <v>0.1681781994748933</v>
       </c>
       <c r="W78">
-        <v>0.199146203649782</v>
+        <v>0.101946203649782</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4689605102262165</v>
+        <v>0.8408909973744665</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7860,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2170716691080049</v>
+        <v>0.1389762568726172</v>
       </c>
       <c r="C79">
-        <v>-7037.500449880199</v>
+        <v>-1227.112743776688</v>
       </c>
       <c r="D79">
-        <v>7420.667550119803</v>
+        <v>13231.05525622331</v>
       </c>
       <c r="E79">
         <v>17171.768</v>
@@ -7765,45 +7893,45 @@
         <v>2269.7</v>
       </c>
       <c r="M79">
-        <v>4903.535422577371</v>
+        <v>2734.676052977371</v>
       </c>
       <c r="N79">
-        <v>-2633.835422577371</v>
+        <v>-464.9760529773707</v>
       </c>
       <c r="O79">
-        <v>-526.7670845154743</v>
+        <v>-92.99521059547415</v>
       </c>
       <c r="P79">
-        <v>-2107.068338061897</v>
+        <v>-371.9808423818966</v>
       </c>
       <c r="Q79">
-        <v>-1175.768338061896</v>
+        <v>559.3191576181036</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2761868560424074</v>
+        <v>0.2620502811059394</v>
       </c>
       <c r="T79">
-        <v>4.73453671494219</v>
+        <v>4.446333386902631</v>
       </c>
       <c r="U79">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V79">
-        <v>0.0925740227979025</v>
+        <v>0.1659940670141804</v>
       </c>
       <c r="W79">
-        <v>0.1994138859977288</v>
+        <v>0.1022138859977288</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4628701139895125</v>
+        <v>0.8299703350709019</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7942,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2188112465524218</v>
+        <v>0.1397438343170342</v>
       </c>
       <c r="C80">
-        <v>-7399.197369896927</v>
+        <v>-1617.984379521404</v>
       </c>
       <c r="D80">
-        <v>7348.754630103076</v>
+        <v>13129.9676204786</v>
       </c>
       <c r="E80">
         <v>17461.552</v>
@@ -7847,45 +7975,45 @@
         <v>2269.7</v>
       </c>
       <c r="M80">
-        <v>4967.217700792661</v>
+        <v>2770.191326392661</v>
       </c>
       <c r="N80">
-        <v>-2697.517700792661</v>
+        <v>-500.491326392661</v>
       </c>
       <c r="O80">
-        <v>-539.5035401585322</v>
+        <v>-100.0982652785322</v>
       </c>
       <c r="P80">
-        <v>-2158.014160634129</v>
+        <v>-400.3930611141288</v>
       </c>
       <c r="Q80">
-        <v>-1226.714160634129</v>
+        <v>530.9069388858713</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2866589858625169</v>
+        <v>0.2718798393380276</v>
       </c>
       <c r="T80">
-        <v>4.949742929257745</v>
+        <v>4.648439449943661</v>
       </c>
       <c r="U80">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V80">
-        <v>0.09138717635177555</v>
+        <v>0.163865937949896</v>
       </c>
       <c r="W80">
-        <v>0.1996747046957283</v>
+        <v>0.1024747046957283</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4569358817588777</v>
+        <v>0.8193296897494802</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8024,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2205508239968387</v>
+        <v>0.140511411761451</v>
       </c>
       <c r="C81">
-        <v>-7759.51386615019</v>
+        <v>-2007.323071885105</v>
       </c>
       <c r="D81">
-        <v>7278.222133849812</v>
+        <v>13030.4129281149</v>
       </c>
       <c r="E81">
         <v>17751.336</v>
@@ -7929,45 +8057,45 @@
         <v>2269.7</v>
       </c>
       <c r="M81">
-        <v>5030.899979007952</v>
+        <v>2805.706599807952</v>
       </c>
       <c r="N81">
-        <v>-2761.199979007952</v>
+        <v>-536.0065998079517</v>
       </c>
       <c r="O81">
-        <v>-552.2399958015903</v>
+        <v>-107.2013199615903</v>
       </c>
       <c r="P81">
-        <v>-2208.959983206361</v>
+        <v>-428.8052798463614</v>
       </c>
       <c r="Q81">
-        <v>-1277.659983206361</v>
+        <v>502.4947201536388</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2981284613797797</v>
+        <v>0.2826455459731718</v>
       </c>
       <c r="T81">
-        <v>5.185444973508115</v>
+        <v>4.869793709464788</v>
       </c>
       <c r="U81">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V81">
-        <v>0.09023037665112016</v>
+        <v>0.1617916855707834</v>
       </c>
       <c r="W81">
-        <v>0.1999289203887152</v>
+        <v>0.1027289203887152</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4511518832556007</v>
+        <v>0.8089584278539171</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8106,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2222904014412556</v>
+        <v>0.2099651008331541</v>
       </c>
       <c r="C82">
-        <v>-8118.489308217786</v>
+        <v>-7599.264840411259</v>
       </c>
       <c r="D82">
-        <v>7209.030691782215</v>
+        <v>7728.255159588742</v>
       </c>
       <c r="E82">
         <v>18041.12</v>
@@ -8011,37 +8139,37 @@
         <v>2269.7</v>
       </c>
       <c r="M82">
-        <v>5094.582257223242</v>
+        <v>4746.841457223242</v>
       </c>
       <c r="N82">
-        <v>-2824.882257223242</v>
+        <v>-2477.141457223242</v>
       </c>
       <c r="O82">
-        <v>-564.9764514446484</v>
+        <v>-495.4282914446485</v>
       </c>
       <c r="P82">
-        <v>-2259.905805778594</v>
+        <v>-1981.713165778594</v>
       </c>
       <c r="Q82">
-        <v>-1328.605805778594</v>
+        <v>-1050.413165778594</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3107448844487686</v>
+        <v>0.3091183814082611</v>
       </c>
       <c r="T82">
-        <v>5.44471722218352</v>
+        <v>5.414103069152291</v>
       </c>
       <c r="U82">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.08910249694298117</v>
+        <v>0.09562990550468924</v>
       </c>
       <c r="W82">
-        <v>0.2001767806893773</v>
+        <v>0.1851767806893773</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4455124847149058</v>
+        <v>0.4781495275234461</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8188,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2240299788856725</v>
+        <v>0.211554678277571</v>
       </c>
       <c r="C83">
-        <v>-8476.161582686091</v>
+        <v>-7960.356553305597</v>
       </c>
       <c r="D83">
-        <v>7141.142417313915</v>
+        <v>7656.947446694408</v>
       </c>
       <c r="E83">
         <v>18330.904</v>
@@ -8093,37 +8221,37 @@
         <v>2269.7</v>
       </c>
       <c r="M83">
-        <v>5158.264535438533</v>
+        <v>4806.176975438533</v>
       </c>
       <c r="N83">
-        <v>-2888.564535438533</v>
+        <v>-2536.476975438533</v>
       </c>
       <c r="O83">
-        <v>-577.7129070877066</v>
+        <v>-507.2953950877067</v>
       </c>
       <c r="P83">
-        <v>-2310.851628350827</v>
+        <v>-2029.181580350827</v>
       </c>
       <c r="Q83">
-        <v>-1379.551628350826</v>
+        <v>-1097.881580350826</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3246893520513355</v>
+        <v>0.3229772435876433</v>
       </c>
       <c r="T83">
-        <v>5.73128128650897</v>
+        <v>5.69905586226557</v>
       </c>
       <c r="U83">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.0880024661165246</v>
+        <v>0.09444928938734738</v>
       </c>
       <c r="W83">
-        <v>0.2004185209826158</v>
+        <v>0.1854185209826157</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4400123305826229</v>
+        <v>0.4722464469367369</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8270,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2257695563300894</v>
+        <v>0.2131442557219879</v>
       </c>
       <c r="C84">
-        <v>-8832.567162326082</v>
+        <v>-8320.144400842</v>
       </c>
       <c r="D84">
-        <v>7074.520837673922</v>
+        <v>7586.943599158003</v>
       </c>
       <c r="E84">
         <v>18620.688</v>
@@ -8175,37 +8303,37 @@
         <v>2269.7</v>
       </c>
       <c r="M84">
-        <v>5221.946813653823</v>
+        <v>4865.512493653823</v>
       </c>
       <c r="N84">
-        <v>-2952.246813653824</v>
+        <v>-2595.812493653823</v>
       </c>
       <c r="O84">
-        <v>-590.4493627307647</v>
+        <v>-519.1624987307647</v>
       </c>
       <c r="P84">
-        <v>-2361.797450923059</v>
+        <v>-2076.649994923059</v>
       </c>
       <c r="Q84">
-        <v>-1430.497450923059</v>
+        <v>-1145.349994923059</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3401832049430763</v>
+        <v>0.3383759793425123</v>
       </c>
       <c r="T84">
-        <v>6.049685802426135</v>
+        <v>6.015670076835878</v>
       </c>
       <c r="U84">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.08692926531022552</v>
+        <v>0.09329746878506268</v>
       </c>
       <c r="W84">
-        <v>0.2006543651711411</v>
+        <v>0.185654365171141</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4346463265511276</v>
+        <v>0.4664873439253133</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8352,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2275091337745063</v>
+        <v>0.2147338331664048</v>
       </c>
       <c r="C85">
-        <v>-9187.741171433074</v>
+        <v>-8678.663820900791</v>
       </c>
       <c r="D85">
-        <v>7009.130828566929</v>
+        <v>7518.208179099213</v>
       </c>
       <c r="E85">
         <v>18910.472</v>
@@ -8257,37 +8385,37 @@
         <v>2269.7</v>
       </c>
       <c r="M85">
-        <v>5285.629091869115</v>
+        <v>4924.848011869114</v>
       </c>
       <c r="N85">
-        <v>-3015.929091869115</v>
+        <v>-2655.148011869114</v>
       </c>
       <c r="O85">
-        <v>-603.1858183738231</v>
+        <v>-531.0296023738229</v>
       </c>
       <c r="P85">
-        <v>-2412.743273495292</v>
+        <v>-2124.118409495291</v>
       </c>
       <c r="Q85">
-        <v>-1481.443273495292</v>
+        <v>-1192.818409495291</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3574998640573749</v>
+        <v>0.3555863310685425</v>
       </c>
       <c r="T85">
-        <v>6.405549673157084</v>
+        <v>6.369533022532107</v>
       </c>
       <c r="U85">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.08588192476431918</v>
+        <v>0.092173402896086</v>
       </c>
       <c r="W85">
-        <v>0.2008845263671717</v>
+        <v>0.1858845263671718</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4294096238215959</v>
+        <v>0.46086701448043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8434,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2292487112189232</v>
+        <v>0.2163234106108217</v>
       </c>
       <c r="C86">
-        <v>-9541.717447575946</v>
+        <v>-9035.948978666496</v>
       </c>
       <c r="D86">
-        <v>6944.938552424053</v>
+        <v>7450.707021333504</v>
       </c>
       <c r="E86">
         <v>19200.256</v>
@@ -8339,37 +8467,37 @@
         <v>2269.7</v>
       </c>
       <c r="M86">
-        <v>5349.311370084404</v>
+        <v>4984.183530084404</v>
       </c>
       <c r="N86">
-        <v>-3079.611370084404</v>
+        <v>-2714.483530084404</v>
       </c>
       <c r="O86">
-        <v>-615.9222740168809</v>
+        <v>-542.8967060168809</v>
       </c>
       <c r="P86">
-        <v>-2463.689096067524</v>
+        <v>-2171.586824067524</v>
       </c>
       <c r="Q86">
-        <v>-1532.389096067523</v>
+        <v>-1240.286824067523</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3769811055609607</v>
+        <v>0.3749479767603263</v>
       </c>
       <c r="T86">
-        <v>6.805896527729398</v>
+        <v>6.767628836440361</v>
       </c>
       <c r="U86">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.0848595208980773</v>
+        <v>0.09107610048065641</v>
       </c>
       <c r="W86">
-        <v>0.2011092075347255</v>
+        <v>0.1861092075347255</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4242976044903864</v>
+        <v>0.4553805024032821</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8516,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2309882886633401</v>
+        <v>0.2179129880552385</v>
       </c>
       <c r="C87">
-        <v>-9894.528599984082</v>
+        <v>-9392.032823253079</v>
       </c>
       <c r="D87">
-        <v>6881.911400015917</v>
+        <v>7384.40717674692</v>
       </c>
       <c r="E87">
         <v>19490.04</v>
@@ -8421,37 +8549,37 @@
         <v>2269.7</v>
       </c>
       <c r="M87">
-        <v>5412.993648299695</v>
+        <v>5043.519048299694</v>
       </c>
       <c r="N87">
-        <v>-3143.293648299695</v>
+        <v>-2773.819048299694</v>
       </c>
       <c r="O87">
-        <v>-628.658729659939</v>
+        <v>-554.7638096599388</v>
       </c>
       <c r="P87">
-        <v>-2514.634918639756</v>
+        <v>-2219.055238639755</v>
       </c>
       <c r="Q87">
-        <v>-1583.334918639755</v>
+        <v>-1287.755238639755</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3990598459316914</v>
+        <v>0.3968911752110147</v>
       </c>
       <c r="T87">
-        <v>7.259622962911358</v>
+        <v>7.218804092203052</v>
       </c>
       <c r="U87">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.08386117359339404</v>
+        <v>0.09000461694558988</v>
       </c>
       <c r="W87">
-        <v>0.2013286020865722</v>
+        <v>0.1863286020865721</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4193058679669701</v>
+        <v>0.4500230847279494</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8598,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.232727866107757</v>
+        <v>0.2195025654996555</v>
       </c>
       <c r="C88">
-        <v>-10246.20606478358</v>
+        <v>-9746.947141332472</v>
       </c>
       <c r="D88">
-        <v>6820.017935216422</v>
+        <v>7319.276858667527</v>
       </c>
       <c r="E88">
         <v>19779.824</v>
@@ -8503,37 +8631,37 @@
         <v>2269.7</v>
       </c>
       <c r="M88">
-        <v>5476.675926514985</v>
+        <v>5102.854566514985</v>
       </c>
       <c r="N88">
-        <v>-3206.975926514985</v>
+        <v>-2833.154566514985</v>
       </c>
       <c r="O88">
-        <v>-641.3951853029971</v>
+        <v>-566.6309133029971</v>
       </c>
       <c r="P88">
-        <v>-2565.580741211988</v>
+        <v>-2266.523653211988</v>
       </c>
       <c r="Q88">
-        <v>-1634.280741211988</v>
+        <v>-1335.223653211988</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4242926920696694</v>
+        <v>0.4219691162975158</v>
       </c>
       <c r="T88">
-        <v>7.77816746026217</v>
+        <v>7.734432955931842</v>
       </c>
       <c r="U88">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.08288604366788946</v>
+        <v>0.08895805163226905</v>
       </c>
       <c r="W88">
-        <v>0.2015428944395387</v>
+        <v>0.1865428944395386</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4144302183394473</v>
+        <v>0.4447902581613453</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8680,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2344674435521738</v>
+        <v>0.2210921429440723</v>
       </c>
       <c r="C89">
-        <v>-10596.78015727943</v>
+        <v>-10100.72260795</v>
       </c>
       <c r="D89">
-        <v>6759.227842720577</v>
+        <v>7255.285392050005</v>
       </c>
       <c r="E89">
         <v>20069.608</v>
@@ -8585,37 +8713,37 @@
         <v>2269.7</v>
       </c>
       <c r="M89">
-        <v>5540.358204730276</v>
+        <v>5162.190084730276</v>
       </c>
       <c r="N89">
-        <v>-3270.658204730276</v>
+        <v>-2892.490084730276</v>
       </c>
       <c r="O89">
-        <v>-654.1316409460553</v>
+        <v>-578.4980169460553</v>
       </c>
       <c r="P89">
-        <v>-2616.526563784221</v>
+        <v>-2313.992067784221</v>
       </c>
       <c r="Q89">
-        <v>-1685.226563784221</v>
+        <v>-1382.692067784221</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.453407514536567</v>
+        <v>0.4509052021665554</v>
       </c>
       <c r="T89">
-        <v>8.37648803412849</v>
+        <v>8.329389337157368</v>
       </c>
       <c r="U89">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.08193333052228152</v>
+        <v>0.08793554529166826</v>
       </c>
       <c r="W89">
-        <v>0.2017522605315174</v>
+        <v>0.1867522605315174</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4096666526114076</v>
+        <v>0.4396777264583412</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8762,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2362070209965907</v>
+        <v>0.2226817203884892</v>
       </c>
       <c r="C90">
-        <v>-10946.28012146628</v>
+        <v>-10453.38883469719</v>
       </c>
       <c r="D90">
-        <v>6699.511878533724</v>
+        <v>7192.403165302809</v>
       </c>
       <c r="E90">
         <v>20359.392</v>
@@ -8667,37 +8795,37 @@
         <v>2269.7</v>
       </c>
       <c r="M90">
-        <v>5604.040482945567</v>
+        <v>5221.525602945566</v>
       </c>
       <c r="N90">
-        <v>-3334.340482945567</v>
+        <v>-2951.825602945566</v>
       </c>
       <c r="O90">
-        <v>-666.8680965891134</v>
+        <v>-590.3651205891132</v>
       </c>
       <c r="P90">
-        <v>-2667.472386356453</v>
+        <v>-2361.460482356453</v>
       </c>
       <c r="Q90">
-        <v>-1736.172386356453</v>
+        <v>-1430.160482356453</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4873748074146144</v>
+        <v>0.4846639690137683</v>
       </c>
       <c r="T90">
-        <v>9.074528703639199</v>
+        <v>9.023505115253815</v>
       </c>
       <c r="U90">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.08100226994816469</v>
+        <v>0.08693627773153567</v>
       </c>
       <c r="W90">
-        <v>0.2019568683032239</v>
+        <v>0.1869568683032239</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4050113497408234</v>
+        <v>0.4346813886576784</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8844,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2379465984410076</v>
+        <v>0.2242712978329061</v>
       </c>
       <c r="C91">
-        <v>-11294.73417693772</v>
+        <v>-10804.9744154011</v>
       </c>
       <c r="D91">
-        <v>6640.84182306228</v>
+        <v>7130.6015845989</v>
       </c>
       <c r="E91">
         <v>20649.176</v>
@@ -8749,37 +8877,37 @@
         <v>2269.7</v>
       </c>
       <c r="M91">
-        <v>5667.722761160857</v>
+        <v>5280.861121160857</v>
       </c>
       <c r="N91">
-        <v>-3398.022761160857</v>
+        <v>-3011.161121160857</v>
       </c>
       <c r="O91">
-        <v>-679.6045522321715</v>
+        <v>-602.2322242321715</v>
       </c>
       <c r="P91">
-        <v>-2718.418208928686</v>
+        <v>-2408.928896928685</v>
       </c>
       <c r="Q91">
-        <v>-1787.118208928685</v>
+        <v>-1477.628896928685</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5275179717250338</v>
+        <v>0.5245606934695656</v>
       </c>
       <c r="T91">
-        <v>9.89948585851549</v>
+        <v>9.843823762095074</v>
       </c>
       <c r="U91">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.08009213208357857</v>
+        <v>0.08595946562219257</v>
       </c>
       <c r="W91">
-        <v>0.2021568781474763</v>
+        <v>0.1871568781474763</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4004606604178929</v>
+        <v>0.4297973281109628</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8926,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2396861758854245</v>
+        <v>0.225860875277323</v>
       </c>
       <c r="C92">
-        <v>-11642.16956335212</v>
+        <v>-11155.50696947804</v>
       </c>
       <c r="D92">
-        <v>6583.190436647882</v>
+        <v>7069.853030521958</v>
       </c>
       <c r="E92">
         <v>20938.96</v>
@@ -8831,37 +8959,37 @@
         <v>2269.7</v>
       </c>
       <c r="M92">
-        <v>5731.405039376147</v>
+        <v>5340.196639376147</v>
       </c>
       <c r="N92">
-        <v>-3461.705039376147</v>
+        <v>-3070.496639376147</v>
       </c>
       <c r="O92">
-        <v>-692.3410078752295</v>
+        <v>-614.0993278752294</v>
       </c>
       <c r="P92">
-        <v>-2769.364031500918</v>
+        <v>-2456.397311500918</v>
       </c>
       <c r="Q92">
-        <v>-1838.064031500918</v>
+        <v>-1525.097311500917</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5756897688975372</v>
+        <v>0.572436762816522</v>
       </c>
       <c r="T92">
-        <v>10.88943444436704</v>
+        <v>10.82820613830458</v>
       </c>
       <c r="U92">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.07920221950487215</v>
+        <v>0.08500436044861266</v>
       </c>
       <c r="W92">
-        <v>0.2023524433285231</v>
+        <v>0.1873524433285231</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3960110975243607</v>
+        <v>0.4250218022430633</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9008,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2414257533298415</v>
+        <v>0.2274504527217399</v>
       </c>
       <c r="C93">
-        <v>-11988.61258260228</v>
+        <v>-11505.01318309005</v>
       </c>
       <c r="D93">
-        <v>6526.531417397725</v>
+        <v>7010.130816909955</v>
       </c>
       <c r="E93">
         <v>21228.744</v>
@@ -8913,37 +9041,37 @@
         <v>2269.7</v>
       </c>
       <c r="M93">
-        <v>5795.087317591438</v>
+        <v>5399.532157591438</v>
       </c>
       <c r="N93">
-        <v>-3525.387317591438</v>
+        <v>-3129.832157591438</v>
       </c>
       <c r="O93">
-        <v>-705.0774635182876</v>
+        <v>-625.9664315182877</v>
       </c>
       <c r="P93">
-        <v>-2820.30985407315</v>
+        <v>-2503.86572607315</v>
       </c>
       <c r="Q93">
-        <v>-1889.00985407315</v>
+        <v>-1572.56572607315</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6345664098861525</v>
+        <v>0.6309519586850246</v>
       </c>
       <c r="T93">
-        <v>12.09937160485227</v>
+        <v>12.03134015367176</v>
       </c>
       <c r="U93">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.07833186544437905</v>
+        <v>0.084070246597529</v>
       </c>
       <c r="W93">
-        <v>0.2025437103737228</v>
+        <v>0.1875437103737227</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3916593272218952</v>
+        <v>0.420351232987645</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9090,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2431653307742583</v>
+        <v>0.2290400301661568</v>
       </c>
       <c r="C94">
-        <v>-12334.08863882602</v>
+        <v>-11853.51884823273</v>
       </c>
       <c r="D94">
-        <v>6470.83936117398</v>
+        <v>6951.409151767276</v>
       </c>
       <c r="E94">
         <v>21518.52800000001</v>
@@ -8995,37 +9123,37 @@
         <v>2269.7</v>
       </c>
       <c r="M94">
-        <v>5858.769595806729</v>
+        <v>5458.867675806729</v>
       </c>
       <c r="N94">
-        <v>-3589.069595806729</v>
+        <v>-3189.167675806729</v>
       </c>
       <c r="O94">
-        <v>-717.8139191613459</v>
+        <v>-637.8335351613458</v>
       </c>
       <c r="P94">
-        <v>-2871.255676645383</v>
+        <v>-2551.334140645383</v>
       </c>
       <c r="Q94">
-        <v>-1939.955676645383</v>
+        <v>-1620.034140645383</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7081622111219218</v>
+        <v>0.7040959535206529</v>
       </c>
       <c r="T94">
-        <v>13.61179305545881</v>
+        <v>13.53525767288073</v>
       </c>
       <c r="U94">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.07748043212433144</v>
+        <v>0.08315643956929498</v>
       </c>
       <c r="W94">
-        <v>0.2027308194396789</v>
+        <v>0.1877308194396789</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3874021606216572</v>
+        <v>0.4157821978464749</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9172,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2449049082186752</v>
+        <v>0.2306296076105737</v>
       </c>
       <c r="C95">
-        <v>-12678.62227638566</v>
+        <v>-12201.04889987495</v>
       </c>
       <c r="D95">
-        <v>6416.08972361434</v>
+        <v>6893.663100125057</v>
       </c>
       <c r="E95">
         <v>21808.31200000001</v>
@@ -9077,37 +9205,37 @@
         <v>2269.7</v>
       </c>
       <c r="M95">
-        <v>5922.45187402202</v>
+        <v>5518.203194022019</v>
       </c>
       <c r="N95">
-        <v>-3652.75187402202</v>
+        <v>-3248.50319402202</v>
       </c>
       <c r="O95">
-        <v>-730.5503748044041</v>
+        <v>-649.700638804404</v>
       </c>
       <c r="P95">
-        <v>-2922.201499217616</v>
+        <v>-2598.802555217616</v>
       </c>
       <c r="Q95">
-        <v>-1990.901499217616</v>
+        <v>-1667.502555217616</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8027853841393393</v>
+        <v>0.7981382325950319</v>
       </c>
       <c r="T95">
-        <v>15.55633492052435</v>
+        <v>15.46886591186369</v>
       </c>
       <c r="U95">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.07664730919826335</v>
+        <v>0.08226228430510901</v>
       </c>
       <c r="W95">
-        <v>0.2029139046547543</v>
+        <v>0.1879139046547543</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3832365459913167</v>
+        <v>0.411311421525545</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9254,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2466444856630921</v>
+        <v>0.2322191850549906</v>
       </c>
       <c r="C96">
-        <v>-13022.23721593551</v>
+        <v>-12547.62745126258</v>
       </c>
       <c r="D96">
-        <v>6362.25878406449</v>
+        <v>6836.86854873743</v>
       </c>
       <c r="E96">
         <v>22098.09600000001</v>
@@ -9159,37 +9287,37 @@
         <v>2269.7</v>
       </c>
       <c r="M96">
-        <v>5986.13415223731</v>
+        <v>5577.538712237309</v>
       </c>
       <c r="N96">
-        <v>-3716.434152237311</v>
+        <v>-3307.83871223731</v>
       </c>
       <c r="O96">
-        <v>-743.2868304474622</v>
+        <v>-661.567742447462</v>
       </c>
       <c r="P96">
-        <v>-2973.147321789848</v>
+        <v>-2646.270969789848</v>
       </c>
       <c r="Q96">
-        <v>-2041.847321789848</v>
+        <v>-1714.970969789847</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9289496148292296</v>
+        <v>0.9235279380275375</v>
       </c>
       <c r="T96">
-        <v>18.14905740727842</v>
+        <v>18.04701023050765</v>
       </c>
       <c r="U96">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.07583191229189884</v>
+        <v>0.08138715362101212</v>
       </c>
       <c r="W96">
-        <v>0.2030930944397217</v>
+        <v>0.1880930944397217</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3791595614594943</v>
+        <v>0.4069357681050606</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9336,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.248384063107509</v>
+        <v>0.2338087624994075</v>
       </c>
       <c r="C97">
-        <v>-13364.95638868893</v>
+        <v>-12893.27782749137</v>
       </c>
       <c r="D97">
-        <v>6309.323611311072</v>
+        <v>6781.002172508637</v>
       </c>
       <c r="E97">
         <v>22387.88</v>
@@ -9241,37 +9369,37 @@
         <v>2269.7</v>
       </c>
       <c r="M97">
-        <v>6049.816430452601</v>
+        <v>5636.8742304526</v>
       </c>
       <c r="N97">
-        <v>-3780.116430452601</v>
+        <v>-3367.174230452601</v>
       </c>
       <c r="O97">
-        <v>-756.0232860905203</v>
+        <v>-673.4348460905202</v>
       </c>
       <c r="P97">
-        <v>-3024.093144362081</v>
+        <v>-2693.73938436208</v>
       </c>
       <c r="Q97">
-        <v>-2092.793144362081</v>
+        <v>-1762.43938436208</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.105579537795076</v>
+        <v>1.099073525633046</v>
       </c>
       <c r="T97">
-        <v>21.77886888873411</v>
+        <v>21.65641227660919</v>
       </c>
       <c r="U97">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.07503368163619466</v>
+        <v>0.08053044674079093</v>
       </c>
       <c r="W97">
-        <v>0.2032685118081635</v>
+        <v>0.1882685118081635</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3751684081809732</v>
+        <v>0.4026522337039546</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9418,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2501236405519259</v>
+        <v>0.2353983399438244</v>
       </c>
       <c r="C98">
-        <v>-13706.80196898877</v>
+        <v>-13238.0225974472</v>
       </c>
       <c r="D98">
-        <v>6257.262031011229</v>
+        <v>6726.0414025528</v>
       </c>
       <c r="E98">
         <v>22677.664</v>
@@ -9323,37 +9451,37 @@
         <v>2269.7</v>
       </c>
       <c r="M98">
-        <v>6113.49870866789</v>
+        <v>5696.209748667889</v>
       </c>
       <c r="N98">
-        <v>-3843.79870866789</v>
+        <v>-3426.50974866789</v>
       </c>
       <c r="O98">
-        <v>-768.7597417335782</v>
+        <v>-685.301949733578</v>
       </c>
       <c r="P98">
-        <v>-3075.038966934312</v>
+        <v>-2741.207798934312</v>
       </c>
       <c r="Q98">
-        <v>-2143.738966934312</v>
+        <v>-1809.907798934311</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.370524422243842</v>
+        <v>1.362391907041304</v>
       </c>
       <c r="T98">
-        <v>27.22358611091757</v>
+        <v>27.07051534576142</v>
       </c>
       <c r="U98">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.07425208078581763</v>
+        <v>0.07969158792057437</v>
       </c>
       <c r="W98">
-        <v>0.203440274648096</v>
+        <v>0.188440274648096</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3712604039290882</v>
+        <v>0.3984579396028719</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9500,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2518632179963428</v>
+        <v>0.2369879173882413</v>
       </c>
       <c r="C99">
-        <v>-14047.79540527857</v>
+        <v>-13581.8836042055</v>
       </c>
       <c r="D99">
-        <v>6206.052594721431</v>
+        <v>6671.964395794498</v>
       </c>
       <c r="E99">
         <v>22967.448</v>
@@ -9405,37 +9533,37 @@
         <v>2269.7</v>
       </c>
       <c r="M99">
-        <v>6177.180986883181</v>
+        <v>5755.54526688318</v>
       </c>
       <c r="N99">
-        <v>-3907.480986883181</v>
+        <v>-3485.845266883181</v>
       </c>
       <c r="O99">
-        <v>-781.4961973766362</v>
+        <v>-697.1690533766362</v>
       </c>
       <c r="P99">
-        <v>-3125.984789506545</v>
+        <v>-2788.676213506545</v>
       </c>
       <c r="Q99">
-        <v>-2194.684789506544</v>
+        <v>-1857.376213506544</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.812099229658456</v>
+        <v>1.801255876055072</v>
       </c>
       <c r="T99">
-        <v>36.29811481455677</v>
+        <v>36.09402046101523</v>
       </c>
       <c r="U99">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.07348659541689168</v>
+        <v>0.07887002515850659</v>
       </c>
       <c r="W99">
-        <v>0.2036084959861743</v>
+        <v>0.1886084959861743</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3674329770844584</v>
+        <v>0.3943501257925329</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9582,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2536027954407597</v>
+        <v>0.2385774948326581</v>
       </c>
       <c r="C100">
-        <v>-14387.95744956519</v>
+        <v>-13924.8819939759</v>
       </c>
       <c r="D100">
-        <v>6155.674550434817</v>
+        <v>6618.750006024103</v>
       </c>
       <c r="E100">
         <v>23257.232</v>
@@ -9487,37 +9615,37 @@
         <v>2269.7</v>
       </c>
       <c r="M100">
-        <v>6240.863265098472</v>
+        <v>5814.880785098471</v>
       </c>
       <c r="N100">
-        <v>-3971.163265098472</v>
+        <v>-3545.180785098471</v>
       </c>
       <c r="O100">
-        <v>-794.2326530196945</v>
+        <v>-709.0361570196943</v>
       </c>
       <c r="P100">
-        <v>-3176.930612078778</v>
+        <v>-2836.144628078777</v>
       </c>
       <c r="Q100">
-        <v>-2245.630612078778</v>
+        <v>-1904.844628078777</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.695248844487684</v>
+        <v>2.678983814082608</v>
       </c>
       <c r="T100">
-        <v>54.44717222183515</v>
+        <v>54.14103069152284</v>
       </c>
       <c r="U100">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.07273673219835196</v>
+        <v>0.07806522898341979</v>
       </c>
       <c r="W100">
-        <v>0.2037732842357204</v>
+        <v>0.1887732842357203</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9653,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3636836609917597</v>
+        <v>0.3903261449170989</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9664,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2553423728851766</v>
+        <v>0.2401670722770751</v>
       </c>
       <c r="C101">
-        <v>-14727.30818545806</v>
+        <v>-14267.03824367272</v>
       </c>
       <c r="D101">
-        <v>6106.107814541947</v>
+        <v>6566.377756327278</v>
       </c>
       <c r="E101">
         <v>23547.016</v>
@@ -9569,37 +9697,37 @@
         <v>2269.7</v>
       </c>
       <c r="M101">
-        <v>6304.545543313762</v>
+        <v>5874.216303313762</v>
       </c>
       <c r="N101">
-        <v>-4034.845543313762</v>
+        <v>-3604.516303313762</v>
       </c>
       <c r="O101">
-        <v>-806.9691086627525</v>
+        <v>-720.9032606627525</v>
       </c>
       <c r="P101">
-        <v>-3227.87643465101</v>
+        <v>-2883.61304265101</v>
       </c>
       <c r="Q101">
-        <v>-2296.57643465101</v>
+        <v>-1952.31304265101</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.344697688975367</v>
+        <v>5.312167628165216</v>
       </c>
       <c r="T101">
-        <v>108.8943444436703</v>
+        <v>108.2820613830457</v>
       </c>
       <c r="U101">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V101">
-        <v>0.07200201773170194</v>
+        <v>0.0772766913169206</v>
       </c>
       <c r="W101">
-        <v>0.2039347434297201</v>
+        <v>0.1889347434297201</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9735,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3600100886585097</v>
+        <v>0.3863834565846029</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_telecom_equipment.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1028264213062847</v>
+        <v>0.1026884304192056</v>
       </c>
       <c r="C2">
-        <v>28612.7999216799</v>
+        <v>28368.18762236318</v>
       </c>
       <c r="D2">
-        <v>20757.5999216799</v>
+        <v>20802.77162236318</v>
       </c>
       <c r="E2">
-        <v>-5141.6</v>
+        <v>-4851.816000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>289.784</v>
       </c>
       <c r="G2">
         <v>7855.2</v>
@@ -1579,28 +1579,28 @@
         <v>2269.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>15.72302621529052</v>
       </c>
       <c r="N2">
-        <v>2269.7</v>
+        <v>2253.976973784709</v>
       </c>
       <c r="O2">
-        <v>453.94</v>
+        <v>450.7953947569418</v>
       </c>
       <c r="P2">
-        <v>1815.76</v>
+        <v>1803.181579027767</v>
       </c>
       <c r="Q2">
-        <v>2747.06</v>
+        <v>2734.481579027768</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1028264213062847</v>
+        <v>0.1032872408723961</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181998178705849</v>
       </c>
       <c r="U2">
         <v>0.0542577444416894</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.3551622265142</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1026884304192056</v>
+        <v>0.1025504395321266</v>
       </c>
       <c r="C3">
-        <v>28368.18762236318</v>
+        <v>28123.7723528221</v>
       </c>
       <c r="D3">
-        <v>20802.77162236318</v>
+        <v>20848.14035282209</v>
       </c>
       <c r="E3">
-        <v>-4851.816000000001</v>
+        <v>-4562.032</v>
       </c>
       <c r="F3">
-        <v>289.784</v>
+        <v>579.5680000000001</v>
       </c>
       <c r="G3">
         <v>7855.2</v>
@@ -1661,28 +1661,28 @@
         <v>2269.7</v>
       </c>
       <c r="M3">
-        <v>15.72302621529052</v>
+        <v>31.44605243058105</v>
       </c>
       <c r="N3">
-        <v>2253.976973784709</v>
+        <v>2238.253947569419</v>
       </c>
       <c r="O3">
-        <v>450.7953947569418</v>
+        <v>447.6507895138838</v>
       </c>
       <c r="P3">
-        <v>1803.181579027767</v>
+        <v>1790.603158055535</v>
       </c>
       <c r="Q3">
-        <v>2734.481579027768</v>
+        <v>2721.903158055535</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1032872408723961</v>
+        <v>0.1037574649194485</v>
       </c>
       <c r="T3">
-        <v>1.181998178705849</v>
+        <v>1.191666480032632</v>
       </c>
       <c r="U3">
         <v>0.0542577444416894</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.3551622265142</v>
+        <v>72.17758111325712</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1025504395321266</v>
+        <v>0.1024124486450475</v>
       </c>
       <c r="C4">
-        <v>28123.7723528221</v>
+        <v>27879.55540497994</v>
       </c>
       <c r="D4">
-        <v>20848.14035282209</v>
+        <v>20893.70740497993</v>
       </c>
       <c r="E4">
-        <v>-4562.032</v>
+        <v>-4272.248000000001</v>
       </c>
       <c r="F4">
-        <v>579.5680000000001</v>
+        <v>869.352</v>
       </c>
       <c r="G4">
         <v>7855.2</v>
@@ -1743,28 +1743,28 @@
         <v>2269.7</v>
       </c>
       <c r="M4">
-        <v>31.44605243058105</v>
+        <v>47.16907864587156</v>
       </c>
       <c r="N4">
-        <v>2238.253947569419</v>
+        <v>2222.530921354128</v>
       </c>
       <c r="O4">
-        <v>447.6507895138838</v>
+        <v>444.5061842708257</v>
       </c>
       <c r="P4">
-        <v>1790.603158055535</v>
+        <v>1778.024737083303</v>
       </c>
       <c r="Q4">
-        <v>2721.903158055535</v>
+        <v>2709.324737083303</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1037574649194485</v>
+        <v>0.1042373843076773</v>
       </c>
       <c r="T4">
-        <v>1.191666480032632</v>
+        <v>1.201534127778523</v>
       </c>
       <c r="U4">
         <v>0.0542577444416894</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.17758111325712</v>
+        <v>48.11838740883809</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1024124486450475</v>
+        <v>0.1022744577579685</v>
       </c>
       <c r="C5">
-        <v>27879.55540497994</v>
+        <v>27635.53808207958</v>
       </c>
       <c r="D5">
-        <v>20893.70740497993</v>
+        <v>20939.47408207957</v>
       </c>
       <c r="E5">
-        <v>-4272.248000000001</v>
+        <v>-3982.464</v>
       </c>
       <c r="F5">
-        <v>869.352</v>
+        <v>1159.136</v>
       </c>
       <c r="G5">
         <v>7855.2</v>
@@ -1825,28 +1825,28 @@
         <v>2269.7</v>
       </c>
       <c r="M5">
-        <v>47.16907864587156</v>
+        <v>62.8921048611621</v>
       </c>
       <c r="N5">
-        <v>2222.530921354128</v>
+        <v>2206.807895138838</v>
       </c>
       <c r="O5">
-        <v>444.5061842708257</v>
+        <v>441.3615790277676</v>
       </c>
       <c r="P5">
-        <v>1778.024737083303</v>
+        <v>1765.44631611107</v>
       </c>
       <c r="Q5">
-        <v>2709.324737083303</v>
+        <v>2696.74631611107</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1042373843076773</v>
+        <v>0.1047273020164942</v>
       </c>
       <c r="T5">
-        <v>1.201534127778523</v>
+        <v>1.211607351519122</v>
       </c>
       <c r="U5">
         <v>0.0542577444416894</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.11838740883809</v>
+        <v>36.08879055662857</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1022744577579685</v>
+        <v>0.1021364668708894</v>
       </c>
       <c r="C6">
-        <v>27635.53808207958</v>
+        <v>27391.72169880776</v>
       </c>
       <c r="D6">
-        <v>20939.47408207957</v>
+        <v>20985.44169880776</v>
       </c>
       <c r="E6">
-        <v>-3982.464</v>
+        <v>-3692.68</v>
       </c>
       <c r="F6">
-        <v>1159.136</v>
+        <v>1448.92</v>
       </c>
       <c r="G6">
         <v>7855.2</v>
@@ -1907,28 +1907,28 @@
         <v>2269.7</v>
       </c>
       <c r="M6">
-        <v>62.8921048611621</v>
+        <v>78.61513107645261</v>
       </c>
       <c r="N6">
-        <v>2206.807895138838</v>
+        <v>2191.084868923547</v>
       </c>
       <c r="O6">
-        <v>441.3615790277676</v>
+        <v>438.2169737847095</v>
       </c>
       <c r="P6">
-        <v>1765.44631611107</v>
+        <v>1752.867895138838</v>
       </c>
       <c r="Q6">
-        <v>2696.74631611107</v>
+        <v>2684.167895138838</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1047273020164942</v>
+        <v>0.1052275337823388</v>
       </c>
       <c r="T6">
-        <v>1.211607351519122</v>
+        <v>1.221892643127942</v>
       </c>
       <c r="U6">
         <v>0.0542577444416894</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.08879055662857</v>
+        <v>28.87103244530285</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1021364668708894</v>
+        <v>0.1019984759838104</v>
       </c>
       <c r="C7">
-        <v>27391.72169880776</v>
+        <v>27148.10758142091</v>
       </c>
       <c r="D7">
-        <v>20985.44169880776</v>
+        <v>21031.61158142091</v>
       </c>
       <c r="E7">
-        <v>-3692.68</v>
+        <v>-3402.896</v>
       </c>
       <c r="F7">
-        <v>1448.92</v>
+        <v>1738.704</v>
       </c>
       <c r="G7">
         <v>7855.2</v>
@@ -1989,28 +1989,28 @@
         <v>2269.7</v>
       </c>
       <c r="M7">
-        <v>78.61513107645261</v>
+        <v>94.33815729174314</v>
       </c>
       <c r="N7">
-        <v>2191.084868923547</v>
+        <v>2175.361842708257</v>
       </c>
       <c r="O7">
-        <v>438.2169737847095</v>
+        <v>435.0723685416513</v>
       </c>
       <c r="P7">
-        <v>1752.867895138838</v>
+        <v>1740.289474166605</v>
       </c>
       <c r="Q7">
-        <v>2684.167895138838</v>
+        <v>2671.589474166605</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1052275337823388</v>
+        <v>0.1057384087772439</v>
       </c>
       <c r="T7">
-        <v>1.221892643127942</v>
+        <v>1.232396770728441</v>
       </c>
       <c r="U7">
         <v>0.0542577444416894</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.87103244530285</v>
+        <v>24.05919370441904</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1019984759838104</v>
+        <v>0.1018604850967313</v>
       </c>
       <c r="C8">
-        <v>27148.10758142091</v>
+        <v>26904.69706787275</v>
       </c>
       <c r="D8">
-        <v>21031.61158142091</v>
+        <v>21077.98506787275</v>
       </c>
       <c r="E8">
-        <v>-3402.896000000001</v>
+        <v>-3113.112000000001</v>
       </c>
       <c r="F8">
-        <v>1738.704</v>
+        <v>2028.488</v>
       </c>
       <c r="G8">
         <v>7855.2</v>
@@ -2071,28 +2071,28 @@
         <v>2269.7</v>
       </c>
       <c r="M8">
-        <v>94.33815729174313</v>
+        <v>110.0611835070336</v>
       </c>
       <c r="N8">
-        <v>2175.361842708257</v>
+        <v>2159.638816492966</v>
       </c>
       <c r="O8">
-        <v>435.0723685416513</v>
+        <v>431.9277632985933</v>
       </c>
       <c r="P8">
-        <v>1740.289474166605</v>
+        <v>1727.711053194373</v>
       </c>
       <c r="Q8">
-        <v>2671.589474166605</v>
+        <v>2659.011053194373</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1057384087772439</v>
+        <v>0.1062602703311793</v>
       </c>
       <c r="T8">
-        <v>1.232396770728441</v>
+        <v>1.243126793546154</v>
       </c>
       <c r="U8">
         <v>0.0542577444416894</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.05919370441904</v>
+        <v>20.62216603235918</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1018604850967313</v>
+        <v>0.1017224942096523</v>
       </c>
       <c r="C9">
-        <v>26904.69706787275</v>
+        <v>26661.4915079435</v>
       </c>
       <c r="D9">
-        <v>21077.98506787275</v>
+        <v>21124.56350794351</v>
       </c>
       <c r="E9">
-        <v>-3113.112</v>
+        <v>-2823.328</v>
       </c>
       <c r="F9">
-        <v>2028.488</v>
+        <v>2318.272</v>
       </c>
       <c r="G9">
         <v>7855.2</v>
@@ -2153,28 +2153,28 @@
         <v>2269.7</v>
       </c>
       <c r="M9">
-        <v>110.0611835070337</v>
+        <v>125.7842097223242</v>
       </c>
       <c r="N9">
-        <v>2159.638816492966</v>
+        <v>2143.915790277676</v>
       </c>
       <c r="O9">
-        <v>431.9277632985933</v>
+        <v>428.7831580555351</v>
       </c>
       <c r="P9">
-        <v>1727.711053194373</v>
+        <v>1715.132632222141</v>
       </c>
       <c r="Q9">
-        <v>2659.011053194373</v>
+        <v>2646.43263222214</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1062602703311793</v>
+        <v>0.1067934767015045</v>
       </c>
       <c r="T9">
-        <v>1.243126793546154</v>
+        <v>1.254090077729469</v>
       </c>
       <c r="U9">
         <v>0.0542577444416894</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.62216603235918</v>
+        <v>18.04439527831428</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1017224942096523</v>
+        <v>0.1015845033225732</v>
       </c>
       <c r="C10">
-        <v>26661.4915079435</v>
+        <v>26418.49226337089</v>
       </c>
       <c r="D10">
-        <v>21124.56350794351</v>
+        <v>21171.34826337089</v>
       </c>
       <c r="E10">
-        <v>-2823.328</v>
+        <v>-2533.544</v>
       </c>
       <c r="F10">
-        <v>2318.272</v>
+        <v>2608.056</v>
       </c>
       <c r="G10">
         <v>7855.2</v>
@@ -2235,28 +2235,28 @@
         <v>2269.7</v>
       </c>
       <c r="M10">
-        <v>125.7842097223242</v>
+        <v>141.5072359376147</v>
       </c>
       <c r="N10">
-        <v>2143.915790277676</v>
+        <v>2128.192764062385</v>
       </c>
       <c r="O10">
-        <v>428.7831580555351</v>
+        <v>425.6385528124771</v>
       </c>
       <c r="P10">
-        <v>1715.132632222141</v>
+        <v>1702.554211249908</v>
       </c>
       <c r="Q10">
-        <v>2646.43263222214</v>
+        <v>2633.854211249909</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1067934767015045</v>
+        <v>0.1073384018931555</v>
       </c>
       <c r="T10">
-        <v>1.254090077729469</v>
+        <v>1.265294313213517</v>
       </c>
       <c r="U10">
         <v>0.0542577444416894</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.04439527831428</v>
+        <v>16.0394624696127</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1015845033225732</v>
+        <v>0.1014465124354942</v>
       </c>
       <c r="C11">
-        <v>26418.49226337089</v>
+        <v>26175.7007079828</v>
       </c>
       <c r="D11">
-        <v>21171.34826337089</v>
+        <v>21218.3407079828</v>
       </c>
       <c r="E11">
-        <v>-2533.544</v>
+        <v>-2243.760000000001</v>
       </c>
       <c r="F11">
-        <v>2608.056</v>
+        <v>2897.84</v>
       </c>
       <c r="G11">
         <v>7855.2</v>
@@ -2317,28 +2317,28 @@
         <v>2269.7</v>
       </c>
       <c r="M11">
-        <v>141.5072359376147</v>
+        <v>157.2302621529052</v>
       </c>
       <c r="N11">
-        <v>2128.192764062385</v>
+        <v>2112.469737847095</v>
       </c>
       <c r="O11">
-        <v>425.6385528124771</v>
+        <v>422.4939475694189</v>
       </c>
       <c r="P11">
-        <v>1702.554211249908</v>
+        <v>1689.975790277676</v>
       </c>
       <c r="Q11">
-        <v>2633.854211249909</v>
+        <v>2621.275790277676</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1073384018931555</v>
+        <v>0.10789543653351</v>
       </c>
       <c r="T11">
-        <v>1.265294313213517</v>
+        <v>1.276747531708321</v>
       </c>
       <c r="U11">
         <v>0.0542577444416894</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.0394624696127</v>
+        <v>14.43551622265143</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1014465124354942</v>
+        <v>0.1013085215484151</v>
       </c>
       <c r="C12">
-        <v>26175.7007079828</v>
+        <v>25933.1182278318</v>
       </c>
       <c r="D12">
-        <v>21218.3407079828</v>
+        <v>21265.5422278318</v>
       </c>
       <c r="E12">
-        <v>-2243.76</v>
+        <v>-1953.976</v>
       </c>
       <c r="F12">
-        <v>2897.84</v>
+        <v>3187.624</v>
       </c>
       <c r="G12">
         <v>7855.2</v>
@@ -2399,28 +2399,28 @@
         <v>2269.7</v>
       </c>
       <c r="M12">
-        <v>157.2302621529052</v>
+        <v>172.9532883681958</v>
       </c>
       <c r="N12">
-        <v>2112.469737847095</v>
+        <v>2096.746711631804</v>
       </c>
       <c r="O12">
-        <v>422.4939475694189</v>
+        <v>419.3493423263608</v>
       </c>
       <c r="P12">
-        <v>1689.975790277676</v>
+        <v>1677.397369305443</v>
       </c>
       <c r="Q12">
-        <v>2621.275790277676</v>
+        <v>2608.697369305443</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.10789543653351</v>
+        <v>0.1084649888062319</v>
       </c>
       <c r="T12">
-        <v>1.276747531708322</v>
+        <v>1.288458125899638</v>
       </c>
       <c r="U12">
         <v>0.0542577444416894</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.43551622265143</v>
+        <v>13.12319656604675</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1013085215484151</v>
+        <v>0.101170530661336</v>
       </c>
       <c r="C13">
-        <v>25933.1182278318</v>
+        <v>25690.7462213314</v>
       </c>
       <c r="D13">
-        <v>21265.5422278318</v>
+        <v>21312.9542213314</v>
       </c>
       <c r="E13">
-        <v>-1953.976</v>
+        <v>-1664.192</v>
       </c>
       <c r="F13">
-        <v>3187.624</v>
+        <v>3477.408</v>
       </c>
       <c r="G13">
         <v>7855.2</v>
@@ -2481,28 +2481,28 @@
         <v>2269.7</v>
       </c>
       <c r="M13">
-        <v>172.9532883681958</v>
+        <v>188.6763145834863</v>
       </c>
       <c r="N13">
-        <v>2096.746711631804</v>
+        <v>2081.023685416514</v>
       </c>
       <c r="O13">
-        <v>419.3493423263608</v>
+        <v>416.2047370833027</v>
       </c>
       <c r="P13">
-        <v>1677.397369305443</v>
+        <v>1664.818948333211</v>
       </c>
       <c r="Q13">
-        <v>2608.697369305443</v>
+        <v>2596.118948333211</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1084649888062319</v>
+        <v>0.1090474854487885</v>
       </c>
       <c r="T13">
-        <v>1.288458125899638</v>
+        <v>1.30043486995894</v>
       </c>
       <c r="U13">
         <v>0.0542577444416894</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.12319656604675</v>
+        <v>12.02959685220952</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.101170530661336</v>
+        <v>0.101032539774257</v>
       </c>
       <c r="C14">
-        <v>25690.7462213314</v>
+        <v>25448.58609939413</v>
       </c>
       <c r="D14">
-        <v>21312.9542213314</v>
+        <v>21360.57809939413</v>
       </c>
       <c r="E14">
-        <v>-1664.192</v>
+        <v>-1374.408</v>
       </c>
       <c r="F14">
-        <v>3477.408</v>
+        <v>3767.192</v>
       </c>
       <c r="G14">
         <v>7855.2</v>
@@ -2563,28 +2563,28 @@
         <v>2269.7</v>
       </c>
       <c r="M14">
-        <v>188.6763145834863</v>
+        <v>204.3993407987768</v>
       </c>
       <c r="N14">
-        <v>2081.023685416514</v>
+        <v>2065.300659201223</v>
       </c>
       <c r="O14">
-        <v>416.2047370833027</v>
+        <v>413.0601318402446</v>
       </c>
       <c r="P14">
-        <v>1664.818948333211</v>
+        <v>1652.240527360978</v>
       </c>
       <c r="Q14">
-        <v>2596.118948333211</v>
+        <v>2583.540527360979</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1090474854487885</v>
+        <v>0.1096433728187601</v>
       </c>
       <c r="T14">
-        <v>1.30043486995894</v>
+        <v>1.31268694146788</v>
       </c>
       <c r="U14">
         <v>0.0542577444416894</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.02959685220952</v>
+        <v>11.1042432481934</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.101032539774257</v>
+        <v>0.1008945488871779</v>
       </c>
       <c r="C15">
-        <v>25448.58609939413</v>
+        <v>25206.63928557155</v>
       </c>
       <c r="D15">
-        <v>21360.57809939413</v>
+        <v>21408.41528557154</v>
       </c>
       <c r="E15">
-        <v>-1374.408</v>
+        <v>-1084.624</v>
       </c>
       <c r="F15">
-        <v>3767.192</v>
+        <v>4056.976000000001</v>
       </c>
       <c r="G15">
         <v>7855.2</v>
@@ -2645,28 +2645,28 @@
         <v>2269.7</v>
       </c>
       <c r="M15">
-        <v>204.3993407987768</v>
+        <v>220.1223670140674</v>
       </c>
       <c r="N15">
-        <v>2065.300659201223</v>
+        <v>2049.577632985932</v>
       </c>
       <c r="O15">
-        <v>413.0601318402446</v>
+        <v>409.9155265971865</v>
       </c>
       <c r="P15">
-        <v>1652.240527360978</v>
+        <v>1639.662106388746</v>
       </c>
       <c r="Q15">
-        <v>2583.540527360979</v>
+        <v>2570.962106388746</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1096433728187601</v>
+        <v>0.110253118034545</v>
       </c>
       <c r="T15">
-        <v>1.31268694146788</v>
+        <v>1.325223944872377</v>
       </c>
       <c r="U15">
         <v>0.0542577444416894</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.1042432481934</v>
+        <v>10.31108301617959</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1008945488871779</v>
+        <v>0.1007565580000989</v>
       </c>
       <c r="C16">
-        <v>25206.63928557155</v>
+        <v>24964.907216196</v>
       </c>
       <c r="D16">
-        <v>21408.41528557154</v>
+        <v>21456.467216196</v>
       </c>
       <c r="E16">
-        <v>-1084.624</v>
+        <v>-794.8399999999992</v>
       </c>
       <c r="F16">
-        <v>4056.976000000001</v>
+        <v>4346.760000000001</v>
       </c>
       <c r="G16">
         <v>7855.2</v>
@@ -2727,28 +2727,28 @@
         <v>2269.7</v>
       </c>
       <c r="M16">
-        <v>220.1223670140674</v>
+        <v>235.8453932293579</v>
       </c>
       <c r="N16">
-        <v>2049.577632985932</v>
+        <v>2033.854606770642</v>
       </c>
       <c r="O16">
-        <v>409.9155265971865</v>
+        <v>406.7709213541284</v>
       </c>
       <c r="P16">
-        <v>1639.662106388746</v>
+        <v>1627.083685416514</v>
       </c>
       <c r="Q16">
-        <v>2570.962106388746</v>
+        <v>2558.383685416514</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.110253118034545</v>
+        <v>0.1108772101965837</v>
       </c>
       <c r="T16">
-        <v>1.325223944872377</v>
+        <v>1.338055936592275</v>
       </c>
       <c r="U16">
         <v>0.0542577444416894</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.31108301617959</v>
+        <v>9.623677481767615</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1007565580000989</v>
+        <v>0.1006185671130198</v>
       </c>
       <c r="C17">
-        <v>24964.907216196</v>
+        <v>24723.39134052452</v>
       </c>
       <c r="D17">
-        <v>21456.467216196</v>
+        <v>21504.73534052452</v>
       </c>
       <c r="E17">
-        <v>-794.8400000000001</v>
+        <v>-505.0559999999996</v>
       </c>
       <c r="F17">
-        <v>4346.76</v>
+        <v>4636.544000000001</v>
       </c>
       <c r="G17">
         <v>7855.2</v>
@@ -2809,28 +2809,28 @@
         <v>2269.7</v>
       </c>
       <c r="M17">
-        <v>235.8453932293579</v>
+        <v>251.5684194446484</v>
       </c>
       <c r="N17">
-        <v>2033.854606770642</v>
+        <v>2018.131580555351</v>
       </c>
       <c r="O17">
-        <v>406.7709213541284</v>
+        <v>403.6263161110703</v>
       </c>
       <c r="P17">
-        <v>1627.083685416514</v>
+        <v>1614.505264444281</v>
       </c>
       <c r="Q17">
-        <v>2558.383685416514</v>
+        <v>2545.805264444281</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1108772101965837</v>
+        <v>0.1115161616958138</v>
       </c>
       <c r="T17">
-        <v>1.338055936592275</v>
+        <v>1.35119345192455</v>
       </c>
       <c r="U17">
         <v>0.0542577444416894</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.623677481767617</v>
+        <v>9.02219763915714</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1006185671130198</v>
+        <v>0.1006845762259408</v>
       </c>
       <c r="C18">
-        <v>24723.39134052452</v>
+        <v>24410.49080744701</v>
       </c>
       <c r="D18">
-        <v>21504.73534052452</v>
+        <v>21481.61880744701</v>
       </c>
       <c r="E18">
-        <v>-505.0559999999996</v>
+        <v>-215.2719999999999</v>
       </c>
       <c r="F18">
-        <v>4636.544000000001</v>
+        <v>4926.328</v>
       </c>
       <c r="G18">
         <v>7855.2</v>
@@ -2891,45 +2891,45 @@
         <v>2269.7</v>
       </c>
       <c r="M18">
-        <v>251.5684194446484</v>
+        <v>274.6809376599389</v>
       </c>
       <c r="N18">
-        <v>2018.131580555351</v>
+        <v>1995.019062340061</v>
       </c>
       <c r="O18">
-        <v>403.6263161110703</v>
+        <v>399.0038124680122</v>
       </c>
       <c r="P18">
-        <v>1614.505264444281</v>
+        <v>1596.015249872049</v>
       </c>
       <c r="Q18">
-        <v>2545.805264444281</v>
+        <v>2527.315249872049</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1115161616958138</v>
+        <v>0.112170509616712</v>
       </c>
       <c r="T18">
-        <v>1.35119345192455</v>
+        <v>1.364647533891338</v>
       </c>
       <c r="U18">
-        <v>0.0542577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04340619555335153</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.02219763915714</v>
+        <v>8.263041546807077</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1006845762259408</v>
+        <v>0.1005585853388617</v>
       </c>
       <c r="C19">
-        <v>24410.49080744701</v>
+        <v>24164.87227371399</v>
       </c>
       <c r="D19">
-        <v>21481.61880744701</v>
+        <v>21525.78427371399</v>
       </c>
       <c r="E19">
-        <v>-215.2719999999999</v>
+        <v>74.51200000000063</v>
       </c>
       <c r="F19">
-        <v>4926.328</v>
+        <v>5216.112000000001</v>
       </c>
       <c r="G19">
         <v>7855.2</v>
@@ -2973,28 +2973,28 @@
         <v>2269.7</v>
       </c>
       <c r="M19">
-        <v>274.6809376599389</v>
+        <v>290.8386398752294</v>
       </c>
       <c r="N19">
-        <v>1995.019062340061</v>
+        <v>1978.86136012477</v>
       </c>
       <c r="O19">
-        <v>399.0038124680122</v>
+        <v>395.7722720249541</v>
       </c>
       <c r="P19">
-        <v>1596.015249872049</v>
+        <v>1583.089088099816</v>
       </c>
       <c r="Q19">
-        <v>2527.315249872049</v>
+        <v>2514.389088099816</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.112170509616712</v>
+        <v>0.1128408172429981</v>
       </c>
       <c r="T19">
-        <v>1.364647533891338</v>
+        <v>1.37842976419878</v>
       </c>
       <c r="U19">
         <v>0.0557577444416894</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.263041546807077</v>
+        <v>7.803983683095572</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1005585853388617</v>
+        <v>0.1004325944517827</v>
       </c>
       <c r="C20">
-        <v>24164.87227371399</v>
+        <v>23919.43571947074</v>
       </c>
       <c r="D20">
-        <v>21525.78427371399</v>
+        <v>21570.13171947074</v>
       </c>
       <c r="E20">
-        <v>74.51199999999972</v>
+        <v>364.2960000000003</v>
       </c>
       <c r="F20">
-        <v>5216.112</v>
+        <v>5505.896000000001</v>
       </c>
       <c r="G20">
         <v>7855.2</v>
@@ -3055,28 +3055,28 @@
         <v>2269.7</v>
       </c>
       <c r="M20">
-        <v>290.8386398752294</v>
+        <v>306.9963420905199</v>
       </c>
       <c r="N20">
-        <v>1978.86136012477</v>
+        <v>1962.70365790948</v>
       </c>
       <c r="O20">
-        <v>395.7722720249541</v>
+        <v>392.540731581896</v>
       </c>
       <c r="P20">
-        <v>1583.089088099816</v>
+        <v>1570.162926327584</v>
       </c>
       <c r="Q20">
-        <v>2514.389088099816</v>
+        <v>2501.462926327584</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1128408172429981</v>
+        <v>0.1135276756748715</v>
       </c>
       <c r="T20">
-        <v>1.37842976419878</v>
+        <v>1.392552296489122</v>
       </c>
       <c r="U20">
         <v>0.0557577444416894</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.803983683095574</v>
+        <v>7.393247699774753</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1004325944517827</v>
+        <v>0.1003066035647036</v>
       </c>
       <c r="C21">
-        <v>23919.43571947074</v>
+        <v>23674.18227178235</v>
       </c>
       <c r="D21">
-        <v>21570.13171947074</v>
+        <v>21614.66227178235</v>
       </c>
       <c r="E21">
-        <v>364.2960000000003</v>
+        <v>654.0799999999999</v>
       </c>
       <c r="F21">
-        <v>5505.896000000001</v>
+        <v>5795.68</v>
       </c>
       <c r="G21">
         <v>7855.2</v>
@@ -3137,28 +3137,28 @@
         <v>2269.7</v>
       </c>
       <c r="M21">
-        <v>306.9963420905199</v>
+        <v>323.1540443058104</v>
       </c>
       <c r="N21">
-        <v>1962.70365790948</v>
+        <v>1946.545955694189</v>
       </c>
       <c r="O21">
-        <v>392.540731581896</v>
+        <v>389.3091911388379</v>
       </c>
       <c r="P21">
-        <v>1570.162926327584</v>
+        <v>1557.236764555352</v>
       </c>
       <c r="Q21">
-        <v>2501.462926327584</v>
+        <v>2488.536764555352</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1135276756748715</v>
+        <v>0.1142317055675416</v>
       </c>
       <c r="T21">
-        <v>1.392552296489122</v>
+        <v>1.407027892086722</v>
       </c>
       <c r="U21">
         <v>0.0557577444416894</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.393247699774753</v>
+        <v>7.023585314786017</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1003066035647036</v>
+        <v>0.1004662126776246</v>
       </c>
       <c r="C22">
-        <v>23674.18227178235</v>
+        <v>23328.01659922634</v>
       </c>
       <c r="D22">
-        <v>21614.66227178235</v>
+        <v>21558.28059922634</v>
       </c>
       <c r="E22">
-        <v>654.0799999999999</v>
+        <v>943.8640000000005</v>
       </c>
       <c r="F22">
-        <v>5795.68</v>
+        <v>6085.464000000001</v>
       </c>
       <c r="G22">
         <v>7855.2</v>
@@ -3219,45 +3219,45 @@
         <v>2269.7</v>
       </c>
       <c r="M22">
-        <v>323.1540443058104</v>
+        <v>349.657035321101</v>
       </c>
       <c r="N22">
-        <v>1946.545955694189</v>
+        <v>1920.042964678899</v>
       </c>
       <c r="O22">
-        <v>389.3091911388379</v>
+        <v>384.0085929357798</v>
       </c>
       <c r="P22">
-        <v>1557.236764555352</v>
+        <v>1536.034371743119</v>
       </c>
       <c r="Q22">
-        <v>2488.536764555352</v>
+        <v>2467.334371743119</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1142317055675416</v>
+        <v>0.1149535590017984</v>
       </c>
       <c r="T22">
-        <v>1.407027892086722</v>
+        <v>1.421869958458944</v>
       </c>
       <c r="U22">
-        <v>0.0557577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04460619555335152</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.023585314786017</v>
+        <v>6.491217881303785</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1004662126776246</v>
+        <v>0.1003538217905455</v>
       </c>
       <c r="C23">
-        <v>23328.01659922634</v>
+        <v>23077.90381260678</v>
       </c>
       <c r="D23">
-        <v>21558.28059922634</v>
+        <v>21597.95181260678</v>
       </c>
       <c r="E23">
-        <v>943.8639999999996</v>
+        <v>1233.648</v>
       </c>
       <c r="F23">
-        <v>6085.464</v>
+        <v>6375.248000000001</v>
       </c>
       <c r="G23">
         <v>7855.2</v>
@@ -3301,28 +3301,28 @@
         <v>2269.7</v>
       </c>
       <c r="M23">
-        <v>349.6570353211009</v>
+        <v>366.3073703363915</v>
       </c>
       <c r="N23">
-        <v>1920.042964678899</v>
+        <v>1903.392629663608</v>
       </c>
       <c r="O23">
-        <v>384.0085929357798</v>
+        <v>380.6785259327216</v>
       </c>
       <c r="P23">
-        <v>1536.034371743119</v>
+        <v>1522.714103730887</v>
       </c>
       <c r="Q23">
-        <v>2467.334371743119</v>
+        <v>2454.014103730887</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1149535590017984</v>
+        <v>0.115693921498472</v>
       </c>
       <c r="T23">
-        <v>1.421869958458944</v>
+        <v>1.437092590635583</v>
       </c>
       <c r="U23">
         <v>0.0574577444416894</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.491217881303786</v>
+        <v>6.196162523062704</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1003538217905455</v>
+        <v>0.1002414309034664</v>
       </c>
       <c r="C24">
-        <v>23077.90381260678</v>
+        <v>22827.93729986049</v>
       </c>
       <c r="D24">
-        <v>21597.95181260678</v>
+        <v>21637.76929986049</v>
       </c>
       <c r="E24">
-        <v>1233.648</v>
+        <v>1523.432000000001</v>
       </c>
       <c r="F24">
-        <v>6375.248000000001</v>
+        <v>6665.032000000001</v>
       </c>
       <c r="G24">
         <v>7855.2</v>
@@ -3383,28 +3383,28 @@
         <v>2269.7</v>
       </c>
       <c r="M24">
-        <v>366.3073703363915</v>
+        <v>382.957705351682</v>
       </c>
       <c r="N24">
-        <v>1903.392629663608</v>
+        <v>1886.742294648318</v>
       </c>
       <c r="O24">
-        <v>380.6785259327216</v>
+        <v>377.3484589296636</v>
       </c>
       <c r="P24">
-        <v>1522.714103730887</v>
+        <v>1509.393835718654</v>
       </c>
       <c r="Q24">
-        <v>2454.014103730887</v>
+        <v>2440.693835718655</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.115693921498472</v>
+        <v>0.1164535141898644</v>
       </c>
       <c r="T24">
-        <v>1.437092590635583</v>
+        <v>1.452710615855771</v>
       </c>
       <c r="U24">
         <v>0.0574577444416894</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.196162523062704</v>
+        <v>5.92676415249476</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1002414309034664</v>
+        <v>0.1001290400163874</v>
       </c>
       <c r="C25">
-        <v>22827.93729986049</v>
+        <v>22578.11787148312</v>
       </c>
       <c r="D25">
-        <v>21637.76929986049</v>
+        <v>21677.73387148312</v>
       </c>
       <c r="E25">
-        <v>1523.432000000001</v>
+        <v>1813.216</v>
       </c>
       <c r="F25">
-        <v>6665.032000000001</v>
+        <v>6954.816000000001</v>
       </c>
       <c r="G25">
         <v>7855.2</v>
@@ -3465,28 +3465,28 @@
         <v>2269.7</v>
       </c>
       <c r="M25">
-        <v>382.957705351682</v>
+        <v>399.6080403669725</v>
       </c>
       <c r="N25">
-        <v>1886.742294648318</v>
+        <v>1870.091959633027</v>
       </c>
       <c r="O25">
-        <v>377.3484589296636</v>
+        <v>374.0183919266055</v>
       </c>
       <c r="P25">
-        <v>1509.393835718654</v>
+        <v>1496.073567706422</v>
       </c>
       <c r="Q25">
-        <v>2440.693835718655</v>
+        <v>2427.373567706422</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1164535141898644</v>
+        <v>0.1172330961626092</v>
       </c>
       <c r="T25">
-        <v>1.452710615855771</v>
+        <v>1.468739641739648</v>
       </c>
       <c r="U25">
         <v>0.0574577444416894</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.92676415249476</v>
+        <v>5.679815646140812</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1001290400163874</v>
+        <v>0.1001766491293083</v>
       </c>
       <c r="C26">
-        <v>22578.11787148312</v>
+        <v>22271.38675192198</v>
       </c>
       <c r="D26">
-        <v>21677.73387148312</v>
+        <v>21660.78675192198</v>
       </c>
       <c r="E26">
-        <v>1813.215999999999</v>
+        <v>2103</v>
       </c>
       <c r="F26">
-        <v>6954.816</v>
+        <v>7244.6</v>
       </c>
       <c r="G26">
         <v>7855.2</v>
@@ -3547,45 +3547,45 @@
         <v>2269.7</v>
       </c>
       <c r="M26">
-        <v>399.6080403669725</v>
+        <v>422.0540553822631</v>
       </c>
       <c r="N26">
-        <v>1870.091959633027</v>
+        <v>1847.645944617737</v>
       </c>
       <c r="O26">
-        <v>374.0183919266055</v>
+        <v>369.5291889235474</v>
       </c>
       <c r="P26">
-        <v>1496.073567706422</v>
+        <v>1478.11675569419</v>
       </c>
       <c r="Q26">
-        <v>2427.373567706422</v>
+        <v>2409.41675569419</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1172330961626092</v>
+        <v>0.1180334669879606</v>
       </c>
       <c r="T26">
-        <v>1.468739641739648</v>
+        <v>1.485196108313762</v>
       </c>
       <c r="U26">
-        <v>0.0574577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04596619555335152</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.679815646140812</v>
+        <v>5.377747165453216</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1001766491293083</v>
+        <v>0.1000706582422293</v>
       </c>
       <c r="C27">
-        <v>22271.38675192198</v>
+        <v>22019.36790085273</v>
       </c>
       <c r="D27">
-        <v>21660.78675192198</v>
+        <v>21698.55190085273</v>
       </c>
       <c r="E27">
-        <v>2103</v>
+        <v>2392.784000000001</v>
       </c>
       <c r="F27">
-        <v>7244.6</v>
+        <v>7534.384000000001</v>
       </c>
       <c r="G27">
         <v>7855.2</v>
@@ -3629,28 +3629,28 @@
         <v>2269.7</v>
       </c>
       <c r="M27">
-        <v>422.0540553822631</v>
+        <v>438.9362175975536</v>
       </c>
       <c r="N27">
-        <v>1847.645944617737</v>
+        <v>1830.763782402446</v>
       </c>
       <c r="O27">
-        <v>369.5291889235474</v>
+        <v>366.1527564804892</v>
       </c>
       <c r="P27">
-        <v>1478.11675569419</v>
+        <v>1464.611025921957</v>
       </c>
       <c r="Q27">
-        <v>2409.41675569419</v>
+        <v>2395.911025921957</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1180334669879606</v>
+        <v>0.1188554694572404</v>
       </c>
       <c r="T27">
-        <v>1.485196108313762</v>
+        <v>1.502097344254743</v>
       </c>
       <c r="U27">
         <v>0.0582577444416894</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.377747165453216</v>
+        <v>5.170910736012708</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1000706582422293</v>
+        <v>0.09996466735515024</v>
       </c>
       <c r="C28">
-        <v>22019.36790085273</v>
+        <v>21767.48096534086</v>
       </c>
       <c r="D28">
-        <v>21698.55190085273</v>
+        <v>21736.44896534086</v>
       </c>
       <c r="E28">
-        <v>2392.784000000001</v>
+        <v>2682.568</v>
       </c>
       <c r="F28">
-        <v>7534.384000000001</v>
+        <v>7824.168000000001</v>
       </c>
       <c r="G28">
         <v>7855.2</v>
@@ -3711,28 +3711,28 @@
         <v>2269.7</v>
       </c>
       <c r="M28">
-        <v>438.9362175975536</v>
+        <v>455.8183798128441</v>
       </c>
       <c r="N28">
-        <v>1830.763782402446</v>
+        <v>1813.881620187156</v>
       </c>
       <c r="O28">
-        <v>366.1527564804892</v>
+        <v>362.7763240374312</v>
       </c>
       <c r="P28">
-        <v>1464.611025921957</v>
+        <v>1451.105296149725</v>
       </c>
       <c r="Q28">
-        <v>2395.911025921957</v>
+        <v>2382.405296149725</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1188554694572404</v>
+        <v>0.1196999925421169</v>
       </c>
       <c r="T28">
-        <v>1.502097344254743</v>
+        <v>1.519461627755752</v>
       </c>
       <c r="U28">
         <v>0.0582577444416894</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.170910736012708</v>
+        <v>4.979395523567792</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09996466735515024</v>
+        <v>0.09985867646807117</v>
       </c>
       <c r="C29">
-        <v>21767.48096534086</v>
+        <v>21515.72663777717</v>
       </c>
       <c r="D29">
-        <v>21736.44896534086</v>
+        <v>21774.47863777717</v>
       </c>
       <c r="E29">
-        <v>2682.568</v>
+        <v>2972.352000000001</v>
       </c>
       <c r="F29">
-        <v>7824.168000000001</v>
+        <v>8113.952000000001</v>
       </c>
       <c r="G29">
         <v>7855.2</v>
@@ -3793,28 +3793,28 @@
         <v>2269.7</v>
       </c>
       <c r="M29">
-        <v>455.8183798128441</v>
+        <v>472.7005420281346</v>
       </c>
       <c r="N29">
-        <v>1813.881620187156</v>
+        <v>1796.999457971865</v>
       </c>
       <c r="O29">
-        <v>362.7763240374312</v>
+        <v>359.3998915943731</v>
       </c>
       <c r="P29">
-        <v>1451.105296149725</v>
+        <v>1437.599566377492</v>
       </c>
       <c r="Q29">
-        <v>2382.405296149725</v>
+        <v>2368.899566377492</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1196999925421169</v>
+        <v>0.1205679746015733</v>
       </c>
       <c r="T29">
-        <v>1.519461627755752</v>
+        <v>1.537308252465122</v>
       </c>
       <c r="U29">
         <v>0.0582577444416894</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.979395523567792</v>
+        <v>4.801559969154657</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09985867646807117</v>
+        <v>0.09975268558099211</v>
       </c>
       <c r="C30">
-        <v>21515.72663777717</v>
+        <v>21264.10561540646</v>
       </c>
       <c r="D30">
-        <v>21774.47863777717</v>
+        <v>21812.64161540646</v>
       </c>
       <c r="E30">
-        <v>2972.352000000001</v>
+        <v>3262.136</v>
       </c>
       <c r="F30">
-        <v>8113.952000000001</v>
+        <v>8403.736000000001</v>
       </c>
       <c r="G30">
         <v>7855.2</v>
@@ -3875,28 +3875,28 @@
         <v>2269.7</v>
       </c>
       <c r="M30">
-        <v>472.7005420281346</v>
+        <v>489.5827042434252</v>
       </c>
       <c r="N30">
-        <v>1796.999457971865</v>
+        <v>1780.117295756575</v>
       </c>
       <c r="O30">
-        <v>359.3998915943731</v>
+        <v>356.0234591513149</v>
       </c>
       <c r="P30">
-        <v>1437.599566377492</v>
+        <v>1424.09383660526</v>
       </c>
       <c r="Q30">
-        <v>2368.899566377492</v>
+        <v>2355.39383660526</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1205679746015733</v>
+        <v>0.1214604068598876</v>
       </c>
       <c r="T30">
-        <v>1.537308252465122</v>
+        <v>1.555657598997291</v>
       </c>
       <c r="U30">
         <v>0.0582577444416894</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.801559969154657</v>
+        <v>4.635988935735531</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09975268558099211</v>
+        <v>0.09964669469391306</v>
       </c>
       <c r="C31">
-        <v>21264.10561540646</v>
+        <v>21012.61860037023</v>
       </c>
       <c r="D31">
-        <v>21812.64161540646</v>
+        <v>21850.93860037023</v>
       </c>
       <c r="E31">
-        <v>3262.135999999999</v>
+        <v>3551.92</v>
       </c>
       <c r="F31">
-        <v>8403.735999999999</v>
+        <v>8693.52</v>
       </c>
       <c r="G31">
         <v>7855.2</v>
@@ -3957,28 +3957,28 @@
         <v>2269.7</v>
       </c>
       <c r="M31">
-        <v>489.582704243425</v>
+        <v>506.4648664587157</v>
       </c>
       <c r="N31">
-        <v>1780.117295756575</v>
+        <v>1763.235133541284</v>
       </c>
       <c r="O31">
-        <v>356.023459151315</v>
+        <v>352.6470267082568</v>
       </c>
       <c r="P31">
-        <v>1424.09383660526</v>
+        <v>1410.588106833027</v>
       </c>
       <c r="Q31">
-        <v>2355.39383660526</v>
+        <v>2341.888106833027</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1214604068598876</v>
+        <v>0.1223783371827251</v>
       </c>
       <c r="T31">
-        <v>1.555657598997291</v>
+        <v>1.574531212573236</v>
       </c>
       <c r="U31">
         <v>0.0582577444416894</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.635988935735532</v>
+        <v>4.481455971211013</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09964669469391306</v>
+        <v>0.09954070380683401</v>
       </c>
       <c r="C32">
-        <v>21012.61860037023</v>
+        <v>20761.26629974971</v>
       </c>
       <c r="D32">
-        <v>21850.93860037023</v>
+        <v>21889.37029974971</v>
       </c>
       <c r="E32">
-        <v>3551.92</v>
+        <v>3841.704</v>
       </c>
       <c r="F32">
-        <v>8693.52</v>
+        <v>8983.304</v>
       </c>
       <c r="G32">
         <v>7855.2</v>
@@ -4039,28 +4039,28 @@
         <v>2269.7</v>
       </c>
       <c r="M32">
-        <v>506.4648664587157</v>
+        <v>523.3470286740062</v>
       </c>
       <c r="N32">
-        <v>1763.235133541284</v>
+        <v>1746.352971325994</v>
       </c>
       <c r="O32">
-        <v>352.6470267082568</v>
+        <v>349.2705942651987</v>
       </c>
       <c r="P32">
-        <v>1410.588106833027</v>
+        <v>1397.082377060795</v>
       </c>
       <c r="Q32">
-        <v>2341.888106833027</v>
+        <v>2328.382377060795</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1223783371827251</v>
+        <v>0.123322874181587</v>
       </c>
       <c r="T32">
-        <v>1.574531212573236</v>
+        <v>1.593951887412252</v>
       </c>
       <c r="U32">
         <v>0.0582577444416894</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.481455971211013</v>
+        <v>4.336892875365496</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09954070380683401</v>
+        <v>0.09969071291975494</v>
       </c>
       <c r="C33">
-        <v>20761.26629974971</v>
+        <v>20417.129470994</v>
       </c>
       <c r="D33">
-        <v>21889.37029974971</v>
+        <v>21835.017470994</v>
       </c>
       <c r="E33">
-        <v>3841.704</v>
+        <v>4131.488000000001</v>
       </c>
       <c r="F33">
-        <v>8983.304</v>
+        <v>9273.088000000002</v>
       </c>
       <c r="G33">
         <v>7855.2</v>
@@ -4121,45 +4121,45 @@
         <v>2269.7</v>
       </c>
       <c r="M33">
-        <v>523.3470286740062</v>
+        <v>549.5022788892968</v>
       </c>
       <c r="N33">
-        <v>1746.352971325994</v>
+        <v>1720.197721110703</v>
       </c>
       <c r="O33">
-        <v>349.2705942651987</v>
+        <v>344.0395442221406</v>
       </c>
       <c r="P33">
-        <v>1397.082377060795</v>
+        <v>1376.158176888562</v>
       </c>
       <c r="Q33">
-        <v>2328.382377060795</v>
+        <v>2307.458176888563</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.123322874181587</v>
+        <v>0.1242951916804154</v>
       </c>
       <c r="T33">
-        <v>1.593951887412252</v>
+        <v>1.613943758570063</v>
       </c>
       <c r="U33">
-        <v>0.0582577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04660619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.336892875365496</v>
+        <v>4.130465126710158</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09969071291975494</v>
+        <v>0.09959272203267591</v>
       </c>
       <c r="C34">
-        <v>20417.129470994</v>
+        <v>20162.81990547823</v>
       </c>
       <c r="D34">
-        <v>21835.017470994</v>
+        <v>21870.49190547823</v>
       </c>
       <c r="E34">
-        <v>4131.488000000001</v>
+        <v>4421.272000000001</v>
       </c>
       <c r="F34">
-        <v>9273.088000000002</v>
+        <v>9562.872000000001</v>
       </c>
       <c r="G34">
         <v>7855.2</v>
@@ -4203,28 +4203,28 @@
         <v>2269.7</v>
       </c>
       <c r="M34">
-        <v>549.5022788892968</v>
+        <v>566.6742251045873</v>
       </c>
       <c r="N34">
-        <v>1720.197721110703</v>
+        <v>1703.025774895412</v>
       </c>
       <c r="O34">
-        <v>344.0395442221406</v>
+        <v>340.6051549790825</v>
       </c>
       <c r="P34">
-        <v>1376.158176888562</v>
+        <v>1362.42061991633</v>
       </c>
       <c r="Q34">
-        <v>2307.458176888563</v>
+        <v>2293.72061991633</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1242951916804154</v>
+        <v>0.1252965335821939</v>
       </c>
       <c r="T34">
-        <v>1.613943758570063</v>
+        <v>1.634532402001242</v>
       </c>
       <c r="U34">
         <v>0.0592577444416894</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.130465126710158</v>
+        <v>4.00529951680985</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09959272203267591</v>
+        <v>0.09949473114559684</v>
       </c>
       <c r="C35">
-        <v>20162.81990547823</v>
+        <v>19908.62579518095</v>
       </c>
       <c r="D35">
-        <v>21870.49190547823</v>
+        <v>21906.08179518095</v>
       </c>
       <c r="E35">
-        <v>4421.272000000001</v>
+        <v>4711.056</v>
       </c>
       <c r="F35">
-        <v>9562.872000000001</v>
+        <v>9852.656000000001</v>
       </c>
       <c r="G35">
         <v>7855.2</v>
@@ -4285,28 +4285,28 @@
         <v>2269.7</v>
       </c>
       <c r="M35">
-        <v>566.6742251045873</v>
+        <v>583.8461713198777</v>
       </c>
       <c r="N35">
-        <v>1703.025774895412</v>
+        <v>1685.853828680122</v>
       </c>
       <c r="O35">
-        <v>340.6051549790825</v>
+        <v>337.1707657360245</v>
       </c>
       <c r="P35">
-        <v>1362.42061991633</v>
+        <v>1348.683062944098</v>
       </c>
       <c r="Q35">
-        <v>2293.72061991633</v>
+        <v>2279.983062944098</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1252965335821939</v>
+        <v>0.1263282191779657</v>
       </c>
       <c r="T35">
-        <v>1.634532402001242</v>
+        <v>1.655744943718213</v>
       </c>
       <c r="U35">
         <v>0.0592577444416894</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.00529951680985</v>
+        <v>3.887496589844856</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09949473114559684</v>
+        <v>0.09939674025851777</v>
       </c>
       <c r="C36">
-        <v>19908.62579518095</v>
+        <v>19654.5477046623</v>
       </c>
       <c r="D36">
-        <v>21906.08179518095</v>
+        <v>21941.7877046623</v>
       </c>
       <c r="E36">
-        <v>4711.056</v>
+        <v>5000.840000000002</v>
       </c>
       <c r="F36">
-        <v>9852.656000000001</v>
+        <v>10142.44</v>
       </c>
       <c r="G36">
         <v>7855.2</v>
@@ -4367,28 +4367,28 @@
         <v>2269.7</v>
       </c>
       <c r="M36">
-        <v>583.8461713198777</v>
+        <v>601.0181175351684</v>
       </c>
       <c r="N36">
-        <v>1685.853828680122</v>
+        <v>1668.681882464831</v>
       </c>
       <c r="O36">
-        <v>337.1707657360245</v>
+        <v>333.7363764929663</v>
       </c>
       <c r="P36">
-        <v>1348.683062944098</v>
+        <v>1334.945505971865</v>
       </c>
       <c r="Q36">
-        <v>2279.983062944098</v>
+        <v>2266.245505971865</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1263282191779657</v>
+        <v>0.127391648945915</v>
       </c>
       <c r="T36">
-        <v>1.655744943718213</v>
+        <v>1.677610179026476</v>
       </c>
       <c r="U36">
         <v>0.0592577444416894</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.887496589844856</v>
+        <v>3.77642525870643</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09939674025851777</v>
+        <v>0.09929874937143873</v>
       </c>
       <c r="C37">
-        <v>19654.5477046623</v>
+        <v>19400.58620216924</v>
       </c>
       <c r="D37">
-        <v>21941.7877046623</v>
+        <v>21977.61020216924</v>
       </c>
       <c r="E37">
-        <v>5000.840000000002</v>
+        <v>5290.624000000002</v>
       </c>
       <c r="F37">
-        <v>10142.44</v>
+        <v>10432.224</v>
       </c>
       <c r="G37">
         <v>7855.2</v>
@@ -4449,28 +4449,28 @@
         <v>2269.7</v>
       </c>
       <c r="M37">
-        <v>601.0181175351684</v>
+        <v>618.1900637504589</v>
       </c>
       <c r="N37">
-        <v>1668.681882464831</v>
+        <v>1651.509936249541</v>
       </c>
       <c r="O37">
-        <v>333.7363764929663</v>
+        <v>330.3019872499082</v>
       </c>
       <c r="P37">
-        <v>1334.945505971865</v>
+        <v>1321.207948999633</v>
       </c>
       <c r="Q37">
-        <v>2266.245505971865</v>
+        <v>2252.507948999633</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.127391648945915</v>
+        <v>0.1284883108941128</v>
       </c>
       <c r="T37">
-        <v>1.677610179026476</v>
+        <v>1.700158702938122</v>
       </c>
       <c r="U37">
         <v>0.0592577444416894</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.77642525870643</v>
+        <v>3.671524557075696</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09929874937143875</v>
+        <v>0.09920075848435969</v>
       </c>
       <c r="C38">
-        <v>19400.58620216923</v>
+        <v>19146.74185966575</v>
       </c>
       <c r="D38">
-        <v>21977.61020216923</v>
+        <v>22013.54985966575</v>
       </c>
       <c r="E38">
-        <v>5290.624</v>
+        <v>5580.407999999999</v>
       </c>
       <c r="F38">
-        <v>10432.224</v>
+        <v>10722.008</v>
       </c>
       <c r="G38">
         <v>7855.2</v>
@@ -4531,28 +4531,28 @@
         <v>2269.7</v>
       </c>
       <c r="M38">
-        <v>618.1900637504588</v>
+        <v>635.3620099657493</v>
       </c>
       <c r="N38">
-        <v>1651.509936249541</v>
+        <v>1634.337990034251</v>
       </c>
       <c r="O38">
-        <v>330.3019872499083</v>
+        <v>326.8675980068501</v>
       </c>
       <c r="P38">
-        <v>1321.207948999633</v>
+        <v>1307.470392027401</v>
       </c>
       <c r="Q38">
-        <v>2252.507948999633</v>
+        <v>2238.770392027401</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1284883108941128</v>
+        <v>0.1296197875073327</v>
       </c>
       <c r="T38">
-        <v>1.700158702938122</v>
+        <v>1.723423053005694</v>
       </c>
       <c r="U38">
         <v>0.0592577444416894</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.671524557075697</v>
+        <v>3.572294163641219</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09920075848435969</v>
+        <v>0.09910276759728062</v>
       </c>
       <c r="C39">
-        <v>19146.74185966575</v>
+        <v>18893.01525286324</v>
       </c>
       <c r="D39">
-        <v>22013.54985966575</v>
+        <v>22049.60725286324</v>
       </c>
       <c r="E39">
-        <v>5580.407999999999</v>
+        <v>5870.192000000001</v>
       </c>
       <c r="F39">
-        <v>10722.008</v>
+        <v>11011.792</v>
       </c>
       <c r="G39">
         <v>7855.2</v>
@@ -4613,28 +4613,28 @@
         <v>2269.7</v>
       </c>
       <c r="M39">
-        <v>635.3620099657493</v>
+        <v>652.5339561810399</v>
       </c>
       <c r="N39">
-        <v>1634.337990034251</v>
+        <v>1617.16604381896</v>
       </c>
       <c r="O39">
-        <v>326.8675980068501</v>
+        <v>323.433208763792</v>
       </c>
       <c r="P39">
-        <v>1307.470392027401</v>
+        <v>1293.732835055168</v>
       </c>
       <c r="Q39">
-        <v>2238.770392027401</v>
+        <v>2225.032835055168</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1296197875073327</v>
+        <v>0.1307877633661404</v>
       </c>
       <c r="T39">
-        <v>1.723423053005694</v>
+        <v>1.74743786597867</v>
       </c>
       <c r="U39">
         <v>0.0592577444416894</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.572294163641219</v>
+        <v>3.478286422492765</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09910276759728062</v>
+        <v>0.09900477671020157</v>
       </c>
       <c r="C40">
-        <v>18893.01525286324</v>
+        <v>18639.40696125125</v>
       </c>
       <c r="D40">
-        <v>22049.60725286324</v>
+        <v>22085.78296125125</v>
       </c>
       <c r="E40">
-        <v>5870.192000000001</v>
+        <v>6159.976000000001</v>
       </c>
       <c r="F40">
-        <v>11011.792</v>
+        <v>11301.576</v>
       </c>
       <c r="G40">
         <v>7855.2</v>
@@ -4695,28 +4695,28 @@
         <v>2269.7</v>
       </c>
       <c r="M40">
-        <v>652.5339561810399</v>
+        <v>669.7059023963304</v>
       </c>
       <c r="N40">
-        <v>1617.16604381896</v>
+        <v>1599.994097603669</v>
       </c>
       <c r="O40">
-        <v>323.433208763792</v>
+        <v>319.9988195207339</v>
       </c>
       <c r="P40">
-        <v>1293.732835055168</v>
+        <v>1279.995278082936</v>
       </c>
       <c r="Q40">
-        <v>2225.032835055168</v>
+        <v>2211.295278082936</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1307877633661404</v>
+        <v>0.1319940335154008</v>
       </c>
       <c r="T40">
-        <v>1.74743786597867</v>
+        <v>1.772240049868794</v>
       </c>
       <c r="U40">
         <v>0.0592577444416894</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.478286422492765</v>
+        <v>3.389099591146796</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09900477671020157</v>
+        <v>0.09890678582312251</v>
       </c>
       <c r="C41">
-        <v>18639.40696125125</v>
+        <v>18385.91756812855</v>
       </c>
       <c r="D41">
-        <v>22085.78296125125</v>
+        <v>22122.07756812854</v>
       </c>
       <c r="E41">
-        <v>6159.976000000001</v>
+        <v>6449.76</v>
       </c>
       <c r="F41">
-        <v>11301.576</v>
+        <v>11591.36</v>
       </c>
       <c r="G41">
         <v>7855.2</v>
@@ -4777,28 +4777,28 @@
         <v>2269.7</v>
       </c>
       <c r="M41">
-        <v>669.7059023963304</v>
+        <v>686.8778486116209</v>
       </c>
       <c r="N41">
-        <v>1599.994097603669</v>
+        <v>1582.822151388379</v>
       </c>
       <c r="O41">
-        <v>319.9988195207339</v>
+        <v>316.5644302776758</v>
       </c>
       <c r="P41">
-        <v>1279.995278082936</v>
+        <v>1266.257721110703</v>
       </c>
       <c r="Q41">
-        <v>2211.295278082936</v>
+        <v>2197.557721110703</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1319940335154008</v>
+        <v>0.1332405126696365</v>
       </c>
       <c r="T41">
-        <v>1.772240049868794</v>
+        <v>1.797868973221922</v>
       </c>
       <c r="U41">
         <v>0.0592577444416894</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.389099591146796</v>
+        <v>3.304372101368127</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09890678582312251</v>
+        <v>0.09880879493604347</v>
       </c>
       <c r="C42">
-        <v>18385.91756812855</v>
+        <v>18132.54766063445</v>
       </c>
       <c r="D42">
-        <v>22122.07756812854</v>
+        <v>22158.49166063446</v>
       </c>
       <c r="E42">
-        <v>6449.76</v>
+        <v>6739.544000000002</v>
       </c>
       <c r="F42">
-        <v>11591.36</v>
+        <v>11881.144</v>
       </c>
       <c r="G42">
         <v>7855.2</v>
@@ -4859,28 +4859,28 @@
         <v>2269.7</v>
       </c>
       <c r="M42">
-        <v>686.8778486116209</v>
+        <v>704.0497948269115</v>
       </c>
       <c r="N42">
-        <v>1582.822151388379</v>
+        <v>1565.650205173088</v>
       </c>
       <c r="O42">
-        <v>316.5644302776758</v>
+        <v>313.1300410346177</v>
       </c>
       <c r="P42">
-        <v>1266.257721110703</v>
+        <v>1252.520164138471</v>
       </c>
       <c r="Q42">
-        <v>2197.557721110703</v>
+        <v>2183.820164138471</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1332405126696365</v>
+        <v>0.1345292453545243</v>
       </c>
       <c r="T42">
-        <v>1.797868973221922</v>
+        <v>1.824366673637868</v>
       </c>
       <c r="U42">
         <v>0.0592577444416894</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.304372101368127</v>
+        <v>3.223777659871343</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09880879493604347</v>
+        <v>0.0987108040489644</v>
       </c>
       <c r="C43">
-        <v>18132.54766063445</v>
+        <v>17879.29782978055</v>
       </c>
       <c r="D43">
-        <v>22158.49166063446</v>
+        <v>22195.02582978054</v>
       </c>
       <c r="E43">
-        <v>6739.544000000002</v>
+        <v>7029.328000000001</v>
       </c>
       <c r="F43">
-        <v>11881.144</v>
+        <v>12170.928</v>
       </c>
       <c r="G43">
         <v>7855.2</v>
@@ -4941,28 +4941,28 @@
         <v>2269.7</v>
       </c>
       <c r="M43">
-        <v>704.0497948269115</v>
+        <v>721.221741042202</v>
       </c>
       <c r="N43">
-        <v>1565.650205173088</v>
+        <v>1548.478258957798</v>
       </c>
       <c r="O43">
-        <v>313.1300410346177</v>
+        <v>309.6956517915596</v>
       </c>
       <c r="P43">
-        <v>1252.520164138471</v>
+        <v>1238.782607166238</v>
       </c>
       <c r="Q43">
-        <v>2183.820164138471</v>
+        <v>2170.082607166239</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1345292453545243</v>
+        <v>0.1358624170975117</v>
       </c>
       <c r="T43">
-        <v>1.824366673637868</v>
+        <v>1.85177808786126</v>
       </c>
       <c r="U43">
         <v>0.0592577444416894</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.223777659871343</v>
+        <v>3.147021048922025</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09871080404896443</v>
+        <v>0.09861281316188536</v>
       </c>
       <c r="C44">
-        <v>17879.29782978054</v>
+        <v>17626.16867048254</v>
       </c>
       <c r="D44">
-        <v>22195.02582978054</v>
+        <v>22231.68067048254</v>
       </c>
       <c r="E44">
-        <v>7029.328</v>
+        <v>7319.111999999999</v>
       </c>
       <c r="F44">
-        <v>12170.928</v>
+        <v>12460.712</v>
       </c>
       <c r="G44">
         <v>7855.2</v>
@@ -5023,28 +5023,28 @@
         <v>2269.7</v>
       </c>
       <c r="M44">
-        <v>721.2217410422019</v>
+        <v>738.3936872574924</v>
       </c>
       <c r="N44">
-        <v>1548.478258957798</v>
+        <v>1531.306312742508</v>
       </c>
       <c r="O44">
-        <v>309.6956517915596</v>
+        <v>306.2612625485015</v>
       </c>
       <c r="P44">
-        <v>1238.782607166238</v>
+        <v>1225.045050194006</v>
       </c>
       <c r="Q44">
-        <v>2170.082607166239</v>
+        <v>2156.345050194006</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1358624170975117</v>
+        <v>0.1372423667963933</v>
       </c>
       <c r="T44">
-        <v>1.85177808786126</v>
+        <v>1.880151306092491</v>
       </c>
       <c r="U44">
         <v>0.0592577444416894</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.147021048922026</v>
+        <v>3.073834512900584</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09861281316188536</v>
+        <v>0.09851482227480632</v>
       </c>
       <c r="C45">
-        <v>17626.16867048254</v>
+        <v>17373.16078159269</v>
       </c>
       <c r="D45">
-        <v>22231.68067048254</v>
+        <v>22268.45678159269</v>
       </c>
       <c r="E45">
-        <v>7319.111999999999</v>
+        <v>7608.896000000001</v>
       </c>
       <c r="F45">
-        <v>12460.712</v>
+        <v>12750.496</v>
       </c>
       <c r="G45">
         <v>7855.2</v>
@@ -5105,28 +5105,28 @@
         <v>2269.7</v>
       </c>
       <c r="M45">
-        <v>738.3936872574924</v>
+        <v>755.565633472783</v>
       </c>
       <c r="N45">
-        <v>1531.306312742508</v>
+        <v>1514.134366527217</v>
       </c>
       <c r="O45">
-        <v>306.2612625485015</v>
+        <v>302.8268733054434</v>
       </c>
       <c r="P45">
-        <v>1225.045050194006</v>
+        <v>1211.307493221773</v>
       </c>
       <c r="Q45">
-        <v>2156.345050194006</v>
+        <v>2142.607493221773</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1372423667963933</v>
+        <v>0.1386716004130922</v>
       </c>
       <c r="T45">
-        <v>1.880151306092491</v>
+        <v>1.909537853546265</v>
       </c>
       <c r="U45">
         <v>0.0592577444416894</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.073834512900584</v>
+        <v>3.003974637607388</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09851482227480632</v>
+        <v>0.09931683138772725</v>
       </c>
       <c r="C46">
-        <v>17373.16078159269</v>
+        <v>16785.91116730321</v>
       </c>
       <c r="D46">
-        <v>22268.45678159269</v>
+        <v>21970.99116730321</v>
       </c>
       <c r="E46">
-        <v>7608.896000000001</v>
+        <v>7898.68</v>
       </c>
       <c r="F46">
-        <v>12750.496</v>
+        <v>13040.28</v>
       </c>
       <c r="G46">
         <v>7855.2</v>
@@ -5187,45 +5187,45 @@
         <v>2269.7</v>
       </c>
       <c r="M46">
-        <v>755.565633472783</v>
+        <v>805.3382796880735</v>
       </c>
       <c r="N46">
-        <v>1514.134366527217</v>
+        <v>1464.361720311926</v>
       </c>
       <c r="O46">
-        <v>302.8268733054434</v>
+        <v>292.8723440623853</v>
       </c>
       <c r="P46">
-        <v>1211.307493221773</v>
+        <v>1171.489376249541</v>
       </c>
       <c r="Q46">
-        <v>2142.607493221773</v>
+        <v>2102.789376249541</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1386716004130922</v>
+        <v>0.1401528061613074</v>
       </c>
       <c r="T46">
-        <v>1.909537853546265</v>
+        <v>1.939993002725631</v>
       </c>
       <c r="U46">
-        <v>0.0592577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.04740619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.003974637607388</v>
+        <v>2.818318782610344</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09931683138772725</v>
+        <v>0.09923884050064821</v>
       </c>
       <c r="C47">
-        <v>16785.91116730321</v>
+        <v>16524.70474233881</v>
       </c>
       <c r="D47">
-        <v>21970.99116730321</v>
+        <v>21999.56874233881</v>
       </c>
       <c r="E47">
-        <v>7898.68</v>
+        <v>8188.464000000002</v>
       </c>
       <c r="F47">
-        <v>13040.28</v>
+        <v>13330.064</v>
       </c>
       <c r="G47">
         <v>7855.2</v>
@@ -5269,28 +5269,28 @@
         <v>2269.7</v>
       </c>
       <c r="M47">
-        <v>805.3382796880735</v>
+        <v>823.234685903364</v>
       </c>
       <c r="N47">
-        <v>1464.361720311926</v>
+        <v>1446.465314096636</v>
       </c>
       <c r="O47">
-        <v>292.8723440623853</v>
+        <v>289.2930628193271</v>
       </c>
       <c r="P47">
-        <v>1171.489376249541</v>
+        <v>1157.172251277309</v>
       </c>
       <c r="Q47">
-        <v>2102.789376249541</v>
+        <v>2088.472251277309</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1401528061613074</v>
+        <v>0.1416888713816787</v>
       </c>
       <c r="T47">
-        <v>1.939993002725631</v>
+        <v>1.971576120393123</v>
       </c>
       <c r="U47">
         <v>0.0617577444416894</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.818318782610344</v>
+        <v>2.75705098298838</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09923884050064821</v>
+        <v>0.09916084961356914</v>
       </c>
       <c r="C48">
-        <v>16524.70474233881</v>
+        <v>16263.5727556573</v>
       </c>
       <c r="D48">
-        <v>21999.56874233881</v>
+        <v>22028.2207556573</v>
       </c>
       <c r="E48">
-        <v>8188.464000000002</v>
+        <v>8478.248000000001</v>
       </c>
       <c r="F48">
-        <v>13330.064</v>
+        <v>13619.848</v>
       </c>
       <c r="G48">
         <v>7855.2</v>
@@ -5351,28 +5351,28 @@
         <v>2269.7</v>
       </c>
       <c r="M48">
-        <v>823.234685903364</v>
+        <v>841.1310921186546</v>
       </c>
       <c r="N48">
-        <v>1446.465314096636</v>
+        <v>1428.568907881345</v>
       </c>
       <c r="O48">
-        <v>289.2930628193271</v>
+        <v>285.7137815762691</v>
       </c>
       <c r="P48">
-        <v>1157.172251277309</v>
+        <v>1142.855126305076</v>
       </c>
       <c r="Q48">
-        <v>2088.472251277309</v>
+        <v>2074.155126305076</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1416888713816787</v>
+        <v>0.143282901327347</v>
       </c>
       <c r="T48">
-        <v>1.971576120393123</v>
+        <v>2.004351053821651</v>
       </c>
       <c r="U48">
         <v>0.0617577444416894</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.75705098298838</v>
+        <v>2.698390323775861</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09916084961356914</v>
+        <v>0.09908285872649009</v>
       </c>
       <c r="C49">
-        <v>16263.5727556573</v>
+        <v>16002.5154984809</v>
       </c>
       <c r="D49">
-        <v>22028.2207556573</v>
+        <v>22056.9474984809</v>
       </c>
       <c r="E49">
-        <v>8478.248000000001</v>
+        <v>8768.032000000001</v>
       </c>
       <c r="F49">
-        <v>13619.848</v>
+        <v>13909.632</v>
       </c>
       <c r="G49">
         <v>7855.2</v>
@@ -5433,28 +5433,28 @@
         <v>2269.7</v>
       </c>
       <c r="M49">
-        <v>841.1310921186546</v>
+        <v>859.027498333945</v>
       </c>
       <c r="N49">
-        <v>1428.568907881345</v>
+        <v>1410.672501666055</v>
       </c>
       <c r="O49">
-        <v>285.7137815762691</v>
+        <v>282.134500333211</v>
       </c>
       <c r="P49">
-        <v>1142.855126305076</v>
+        <v>1128.538001332844</v>
       </c>
       <c r="Q49">
-        <v>2074.155126305076</v>
+        <v>2059.838001332844</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.143282901327347</v>
+        <v>0.1449382401170795</v>
       </c>
       <c r="T49">
-        <v>2.004351053821651</v>
+        <v>2.038386561612815</v>
       </c>
       <c r="U49">
         <v>0.0617577444416894</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.698390323775861</v>
+        <v>2.642173858697197</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09908285872649009</v>
+        <v>0.09900486783941102</v>
       </c>
       <c r="C50">
-        <v>16002.5154984809</v>
+        <v>15741.533263553</v>
       </c>
       <c r="D50">
-        <v>22056.9474984809</v>
+        <v>22085.749263553</v>
       </c>
       <c r="E50">
-        <v>8768.031999999999</v>
+        <v>9057.816000000001</v>
       </c>
       <c r="F50">
-        <v>13909.632</v>
+        <v>14199.416</v>
       </c>
       <c r="G50">
         <v>7855.2</v>
@@ -5515,28 +5515,28 @@
         <v>2269.7</v>
       </c>
       <c r="M50">
-        <v>859.0274983339449</v>
+        <v>876.9239045492355</v>
       </c>
       <c r="N50">
-        <v>1410.672501666055</v>
+        <v>1392.776095450764</v>
       </c>
       <c r="O50">
-        <v>282.134500333211</v>
+        <v>278.5552190901529</v>
       </c>
       <c r="P50">
-        <v>1128.538001332844</v>
+        <v>1114.220876360612</v>
       </c>
       <c r="Q50">
-        <v>2059.838001332844</v>
+        <v>2045.520876360612</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1449382401170795</v>
+        <v>0.1466584941534682</v>
       </c>
       <c r="T50">
-        <v>2.038386561612815</v>
+        <v>2.073756795199711</v>
       </c>
       <c r="U50">
         <v>0.0617577444416894</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.642173858697197</v>
+        <v>2.588251943213582</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09900486783941102</v>
+        <v>0.09892687695233197</v>
       </c>
       <c r="C51">
-        <v>15741.533263553</v>
+        <v>15480.626345148</v>
       </c>
       <c r="D51">
-        <v>22085.749263553</v>
+        <v>22114.626345148</v>
       </c>
       <c r="E51">
-        <v>9057.816000000001</v>
+        <v>9347.6</v>
       </c>
       <c r="F51">
-        <v>14199.416</v>
+        <v>14489.2</v>
       </c>
       <c r="G51">
         <v>7855.2</v>
@@ -5597,28 +5597,28 @@
         <v>2269.7</v>
       </c>
       <c r="M51">
-        <v>876.9239045492355</v>
+        <v>894.8203107645261</v>
       </c>
       <c r="N51">
-        <v>1392.776095450764</v>
+        <v>1374.879689235474</v>
       </c>
       <c r="O51">
-        <v>278.5552190901529</v>
+        <v>274.9759378470948</v>
       </c>
       <c r="P51">
-        <v>1114.220876360612</v>
+        <v>1099.903751388379</v>
       </c>
       <c r="Q51">
-        <v>2045.520876360612</v>
+        <v>2031.203751388379</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1466584941534682</v>
+        <v>0.1484475583513124</v>
       </c>
       <c r="T51">
-        <v>2.073756795199711</v>
+        <v>2.110541838130083</v>
       </c>
       <c r="U51">
         <v>0.0617577444416894</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.588251943213582</v>
+        <v>2.536486904349309</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09892687695233197</v>
+        <v>0.1002768860652529</v>
       </c>
       <c r="C52">
-        <v>15480.626345148</v>
+        <v>14701.40851486261</v>
       </c>
       <c r="D52">
-        <v>22114.626345148</v>
+        <v>21625.19251486261</v>
       </c>
       <c r="E52">
-        <v>9347.6</v>
+        <v>9637.384</v>
       </c>
       <c r="F52">
-        <v>14489.2</v>
+        <v>14778.984</v>
       </c>
       <c r="G52">
         <v>7855.2</v>
@@ -5679,45 +5679,45 @@
         <v>2269.7</v>
       </c>
       <c r="M52">
-        <v>894.8203107645261</v>
+        <v>964.4431609798166</v>
       </c>
       <c r="N52">
-        <v>1374.879689235474</v>
+        <v>1305.256839020183</v>
       </c>
       <c r="O52">
-        <v>274.9759378470948</v>
+        <v>261.0513678040367</v>
       </c>
       <c r="P52">
-        <v>1099.903751388379</v>
+        <v>1044.205471216147</v>
       </c>
       <c r="Q52">
-        <v>2031.203751388379</v>
+        <v>1975.505471216147</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1484475583513124</v>
+        <v>0.1503096455776401</v>
       </c>
       <c r="T52">
-        <v>2.110541838130083</v>
+        <v>2.148828311384143</v>
       </c>
       <c r="U52">
-        <v>0.0617577444416894</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.04940619555335152</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.536486904349309</v>
+        <v>2.353378707869233</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1002768860652529</v>
+        <v>0.1002268951781739</v>
       </c>
       <c r="C53">
-        <v>14701.40851486261</v>
+        <v>14429.36169477083</v>
       </c>
       <c r="D53">
-        <v>21625.19251486261</v>
+        <v>21642.92969477083</v>
       </c>
       <c r="E53">
-        <v>9637.384</v>
+        <v>9927.168000000001</v>
       </c>
       <c r="F53">
-        <v>14778.984</v>
+        <v>15068.768</v>
       </c>
       <c r="G53">
         <v>7855.2</v>
@@ -5761,28 +5761,28 @@
         <v>2269.7</v>
       </c>
       <c r="M53">
-        <v>964.4431609798166</v>
+        <v>983.3538111951073</v>
       </c>
       <c r="N53">
-        <v>1305.256839020183</v>
+        <v>1286.346188804893</v>
       </c>
       <c r="O53">
-        <v>261.0513678040367</v>
+        <v>257.2692377609785</v>
       </c>
       <c r="P53">
-        <v>1044.205471216147</v>
+        <v>1029.076951043914</v>
       </c>
       <c r="Q53">
-        <v>1975.505471216147</v>
+        <v>1960.376951043914</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1503096455776401</v>
+        <v>0.1522493197717314</v>
       </c>
       <c r="T53">
-        <v>2.148828311384143</v>
+        <v>2.188710054357123</v>
       </c>
       <c r="U53">
         <v>0.0652577444416894</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.353378707869233</v>
+        <v>2.308121425025594</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1002268951781739</v>
+        <v>0.1001769042910948</v>
       </c>
       <c r="C54">
-        <v>14429.36169477083</v>
+        <v>14157.34399495687</v>
       </c>
       <c r="D54">
-        <v>21642.92969477083</v>
+        <v>21660.69599495687</v>
       </c>
       <c r="E54">
-        <v>9927.168000000001</v>
+        <v>10216.952</v>
       </c>
       <c r="F54">
-        <v>15068.768</v>
+        <v>15358.552</v>
       </c>
       <c r="G54">
         <v>7855.2</v>
@@ -5843,28 +5843,28 @@
         <v>2269.7</v>
       </c>
       <c r="M54">
-        <v>983.3538111951073</v>
+        <v>1002.264461410398</v>
       </c>
       <c r="N54">
-        <v>1286.346188804893</v>
+        <v>1267.435538589602</v>
       </c>
       <c r="O54">
-        <v>257.2692377609785</v>
+        <v>253.4871077179204</v>
       </c>
       <c r="P54">
-        <v>1029.076951043914</v>
+        <v>1013.948430871682</v>
       </c>
       <c r="Q54">
-        <v>1960.376951043914</v>
+        <v>1945.248430871682</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1522493197717314</v>
+        <v>0.1542715332932309</v>
       </c>
       <c r="T54">
-        <v>2.188710054357123</v>
+        <v>2.230288892775761</v>
       </c>
       <c r="U54">
         <v>0.0652577444416894</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.308121425025594</v>
+        <v>2.264571964176055</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1001769042910948</v>
+        <v>0.1013365134040158</v>
       </c>
       <c r="C55">
-        <v>14157.34399495687</v>
+        <v>13462.81428962252</v>
       </c>
       <c r="D55">
-        <v>21660.69599495687</v>
+        <v>21255.95028962252</v>
       </c>
       <c r="E55">
-        <v>10216.952</v>
+        <v>10506.736</v>
       </c>
       <c r="F55">
-        <v>15358.552</v>
+        <v>15648.336</v>
       </c>
       <c r="G55">
         <v>7855.2</v>
@@ -5925,45 +5925,45 @@
         <v>2269.7</v>
       </c>
       <c r="M55">
-        <v>1002.264461410398</v>
+        <v>1064.990452425688</v>
       </c>
       <c r="N55">
-        <v>1267.435538589602</v>
+        <v>1204.709547574312</v>
       </c>
       <c r="O55">
-        <v>253.4871077179204</v>
+        <v>240.9419095148623</v>
       </c>
       <c r="P55">
-        <v>1013.948430871682</v>
+        <v>963.7676380594494</v>
       </c>
       <c r="Q55">
-        <v>1945.248430871682</v>
+        <v>1895.06763805945</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1542715332932309</v>
+        <v>0.1563816691417521</v>
       </c>
       <c r="T55">
-        <v>2.230288892775761</v>
+        <v>2.273675506777819</v>
       </c>
       <c r="U55">
-        <v>0.0652577444416894</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05220619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.264571964176055</v>
+        <v>2.131192814762227</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1013365134040158</v>
+        <v>0.1013089225169367</v>
       </c>
       <c r="C56">
-        <v>13462.81428962252</v>
+        <v>13182.48476727766</v>
       </c>
       <c r="D56">
-        <v>21255.95028962252</v>
+        <v>21265.40476727766</v>
       </c>
       <c r="E56">
-        <v>10506.736</v>
+        <v>10796.52</v>
       </c>
       <c r="F56">
-        <v>15648.336</v>
+        <v>15938.12</v>
       </c>
       <c r="G56">
         <v>7855.2</v>
@@ -6007,28 +6007,28 @@
         <v>2269.7</v>
       </c>
       <c r="M56">
-        <v>1064.990452425688</v>
+        <v>1084.712497840979</v>
       </c>
       <c r="N56">
-        <v>1204.709547574312</v>
+        <v>1184.987502159021</v>
       </c>
       <c r="O56">
-        <v>240.9419095148623</v>
+        <v>236.9975004318042</v>
       </c>
       <c r="P56">
-        <v>963.7676380594494</v>
+        <v>947.9900017272168</v>
       </c>
       <c r="Q56">
-        <v>1895.06763805945</v>
+        <v>1879.290001727217</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1563816691417521</v>
+        <v>0.1585855888057631</v>
       </c>
       <c r="T56">
-        <v>2.273675506777819</v>
+        <v>2.318990414735523</v>
       </c>
       <c r="U56">
         <v>0.0680577444416894</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.131192814762227</v>
+        <v>2.092443854493823</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1013089225169367</v>
+        <v>0.1012813316298577</v>
       </c>
       <c r="C57">
-        <v>13182.48476727766</v>
+        <v>12902.16365922835</v>
       </c>
       <c r="D57">
-        <v>21265.40476727766</v>
+        <v>21274.86765922836</v>
       </c>
       <c r="E57">
-        <v>10796.52</v>
+        <v>11086.304</v>
       </c>
       <c r="F57">
-        <v>15938.12</v>
+        <v>16227.904</v>
       </c>
       <c r="G57">
         <v>7855.2</v>
@@ -6089,28 +6089,28 @@
         <v>2269.7</v>
       </c>
       <c r="M57">
-        <v>1084.712497840979</v>
+        <v>1104.434543256269</v>
       </c>
       <c r="N57">
-        <v>1184.987502159021</v>
+        <v>1165.265456743731</v>
       </c>
       <c r="O57">
-        <v>236.9975004318042</v>
+        <v>233.0530913487461</v>
       </c>
       <c r="P57">
-        <v>947.9900017272168</v>
+        <v>932.2123653949844</v>
       </c>
       <c r="Q57">
-        <v>1879.290001727217</v>
+        <v>1863.512365394984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1585855888057631</v>
+        <v>0.16088968663632</v>
       </c>
       <c r="T57">
-        <v>2.318990414735523</v>
+        <v>2.36636509123676</v>
       </c>
       <c r="U57">
         <v>0.0680577444416894</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.092443854493823</v>
+        <v>2.055078785663576</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1012813316298577</v>
+        <v>0.1012537407427786</v>
       </c>
       <c r="C58">
-        <v>12902.16365922835</v>
+        <v>12621.85097671245</v>
       </c>
       <c r="D58">
-        <v>21274.86765922836</v>
+        <v>21284.33897671245</v>
       </c>
       <c r="E58">
-        <v>11086.304</v>
+        <v>11376.088</v>
       </c>
       <c r="F58">
-        <v>16227.904</v>
+        <v>16517.688</v>
       </c>
       <c r="G58">
         <v>7855.2</v>
@@ -6171,28 +6171,28 @@
         <v>2269.7</v>
       </c>
       <c r="M58">
-        <v>1104.434543256269</v>
+        <v>1124.15658867156</v>
       </c>
       <c r="N58">
-        <v>1165.265456743731</v>
+        <v>1145.54341132844</v>
       </c>
       <c r="O58">
-        <v>233.0530913487461</v>
+        <v>229.108682265688</v>
       </c>
       <c r="P58">
-        <v>932.2123653949844</v>
+        <v>916.434729062752</v>
       </c>
       <c r="Q58">
-        <v>1863.512365394984</v>
+        <v>1847.734729062752</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.16088968663632</v>
+        <v>0.1633009518078331</v>
       </c>
       <c r="T58">
-        <v>2.36636509123676</v>
+        <v>2.415943241063635</v>
       </c>
       <c r="U58">
         <v>0.0680577444416894</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.055078785663576</v>
+        <v>2.019024771880004</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1012537407427786</v>
+        <v>0.1048453498556996</v>
       </c>
       <c r="C59">
-        <v>12621.85097671245</v>
+        <v>11166.16721465491</v>
       </c>
       <c r="D59">
-        <v>21284.33897671245</v>
+        <v>20118.43921465491</v>
       </c>
       <c r="E59">
-        <v>11376.088</v>
+        <v>11665.872</v>
       </c>
       <c r="F59">
-        <v>16517.688</v>
+        <v>16807.472</v>
       </c>
       <c r="G59">
         <v>7855.2</v>
@@ -6253,45 +6253,45 @@
         <v>2269.7</v>
       </c>
       <c r="M59">
-        <v>1124.15658867156</v>
+        <v>1274.97691568685</v>
       </c>
       <c r="N59">
-        <v>1145.54341132844</v>
+        <v>994.7230843131495</v>
       </c>
       <c r="O59">
-        <v>229.108682265688</v>
+        <v>198.9446168626299</v>
       </c>
       <c r="P59">
-        <v>916.434729062752</v>
+        <v>795.7784674505195</v>
       </c>
       <c r="Q59">
-        <v>1847.734729062752</v>
+        <v>1727.07846745052</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1633009518078331</v>
+        <v>0.1658270391303707</v>
       </c>
       <c r="T59">
-        <v>2.415943241063635</v>
+        <v>2.467882255167981</v>
       </c>
       <c r="U59">
-        <v>0.0680577444416894</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.05444619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.019024771880004</v>
+        <v>1.780189093680395</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1048453498556995</v>
+        <v>0.1048801589686205</v>
       </c>
       <c r="C60">
-        <v>11166.16721465491</v>
+        <v>10865.7081940663</v>
       </c>
       <c r="D60">
-        <v>20118.43921465491</v>
+        <v>20107.76419406631</v>
       </c>
       <c r="E60">
-        <v>11665.872</v>
+        <v>11955.656</v>
       </c>
       <c r="F60">
-        <v>16807.472</v>
+        <v>17097.256</v>
       </c>
       <c r="G60">
         <v>7855.2</v>
@@ -6335,28 +6335,28 @@
         <v>2269.7</v>
       </c>
       <c r="M60">
-        <v>1274.97691568685</v>
+        <v>1296.959276302141</v>
       </c>
       <c r="N60">
-        <v>994.7230843131497</v>
+        <v>972.740723697859</v>
       </c>
       <c r="O60">
-        <v>198.9446168626299</v>
+        <v>194.5481447395718</v>
       </c>
       <c r="P60">
-        <v>795.7784674505198</v>
+        <v>778.1925789582872</v>
       </c>
       <c r="Q60">
-        <v>1727.07846745052</v>
+        <v>1709.492578958287</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1658270391303706</v>
+        <v>0.1684763502247393</v>
       </c>
       <c r="T60">
-        <v>2.46788225516798</v>
+        <v>2.52235487971644</v>
       </c>
       <c r="U60">
         <v>0.0758577444416894</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.780189093680395</v>
+        <v>1.750016397177338</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1048801589686205</v>
+        <v>0.1067869680815415</v>
       </c>
       <c r="C61">
-        <v>10865.7081940663</v>
+        <v>10007.97543325157</v>
       </c>
       <c r="D61">
-        <v>20107.76419406631</v>
+        <v>19539.81543325157</v>
       </c>
       <c r="E61">
-        <v>11955.656</v>
+        <v>12245.44</v>
       </c>
       <c r="F61">
-        <v>17097.256</v>
+        <v>17387.04</v>
       </c>
       <c r="G61">
         <v>7855.2</v>
@@ -6417,45 +6417,45 @@
         <v>2269.7</v>
       </c>
       <c r="M61">
-        <v>1296.959276302141</v>
+        <v>1386.751092917431</v>
       </c>
       <c r="N61">
-        <v>972.740723697859</v>
+        <v>882.9489070825684</v>
       </c>
       <c r="O61">
-        <v>194.5481447395718</v>
+        <v>176.5897814165137</v>
       </c>
       <c r="P61">
-        <v>778.1925789582872</v>
+        <v>706.3591256660548</v>
       </c>
       <c r="Q61">
-        <v>1709.492578958287</v>
+        <v>1637.659125666055</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1684763502247393</v>
+        <v>0.1712581268738263</v>
       </c>
       <c r="T61">
-        <v>2.52235487971644</v>
+        <v>2.579551135492324</v>
       </c>
       <c r="U61">
-        <v>0.0758577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.06068619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.750016397177338</v>
+        <v>1.636703235059314</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1067869680815415</v>
+        <v>0.1068529771944624</v>
       </c>
       <c r="C62">
-        <v>10007.97543325157</v>
+        <v>9699.104415840018</v>
       </c>
       <c r="D62">
-        <v>19539.81543325157</v>
+        <v>19520.72841584002</v>
       </c>
       <c r="E62">
-        <v>12245.44</v>
+        <v>12535.224</v>
       </c>
       <c r="F62">
-        <v>17387.04</v>
+        <v>17676.824</v>
       </c>
       <c r="G62">
         <v>7855.2</v>
@@ -6499,28 +6499,28 @@
         <v>2269.7</v>
       </c>
       <c r="M62">
-        <v>1386.751092917431</v>
+        <v>1409.863611132722</v>
       </c>
       <c r="N62">
-        <v>882.9489070825684</v>
+        <v>859.8363888672779</v>
       </c>
       <c r="O62">
-        <v>176.5897814165137</v>
+        <v>171.9672777734556</v>
       </c>
       <c r="P62">
-        <v>706.3591256660548</v>
+        <v>687.8691110938223</v>
       </c>
       <c r="Q62">
-        <v>1637.659125666055</v>
+        <v>1619.169111093822</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1712581268738263</v>
+        <v>0.1741825587356871</v>
       </c>
       <c r="T62">
-        <v>2.579551135492324</v>
+        <v>2.639680532590046</v>
       </c>
       <c r="U62">
         <v>0.0797577444416894</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.636703235059314</v>
+        <v>1.609872034484572</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1068529771944624</v>
+        <v>0.1069189863073833</v>
       </c>
       <c r="C63">
-        <v>9699.104415840018</v>
+        <v>9390.270651462935</v>
       </c>
       <c r="D63">
-        <v>19520.72841584002</v>
+        <v>19501.67865146293</v>
       </c>
       <c r="E63">
-        <v>12535.224</v>
+        <v>12825.008</v>
       </c>
       <c r="F63">
-        <v>17676.824</v>
+        <v>17966.608</v>
       </c>
       <c r="G63">
         <v>7855.2</v>
@@ -6581,28 +6581,28 @@
         <v>2269.7</v>
       </c>
       <c r="M63">
-        <v>1409.863611132722</v>
+        <v>1432.976129348012</v>
       </c>
       <c r="N63">
-        <v>859.8363888672779</v>
+        <v>836.7238706519875</v>
       </c>
       <c r="O63">
-        <v>171.9672777734556</v>
+        <v>167.3447741303975</v>
       </c>
       <c r="P63">
-        <v>687.8691110938223</v>
+        <v>669.37909652159</v>
       </c>
       <c r="Q63">
-        <v>1619.169111093822</v>
+        <v>1600.67909652159</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1741825587356871</v>
+        <v>0.1772609080639616</v>
       </c>
       <c r="T63">
-        <v>2.639680532590046</v>
+        <v>2.702974634798176</v>
       </c>
       <c r="U63">
         <v>0.0797577444416894</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.609872034484572</v>
+        <v>1.583906356509014</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1069189863073833</v>
+        <v>0.1069849954203043</v>
       </c>
       <c r="C64">
-        <v>9390.270651462935</v>
+        <v>9081.4740311639</v>
       </c>
       <c r="D64">
-        <v>19501.67865146293</v>
+        <v>19482.6660311639</v>
       </c>
       <c r="E64">
-        <v>12825.008</v>
+        <v>13114.792</v>
       </c>
       <c r="F64">
-        <v>17966.608</v>
+        <v>18256.392</v>
       </c>
       <c r="G64">
         <v>7855.2</v>
@@ -6663,28 +6663,28 @@
         <v>2269.7</v>
       </c>
       <c r="M64">
-        <v>1432.976129348012</v>
+        <v>1456.088647563303</v>
       </c>
       <c r="N64">
-        <v>836.7238706519875</v>
+        <v>813.611352436697</v>
       </c>
       <c r="O64">
-        <v>167.3447741303975</v>
+        <v>162.7222704873394</v>
       </c>
       <c r="P64">
-        <v>669.37909652159</v>
+        <v>650.8890819493575</v>
       </c>
       <c r="Q64">
-        <v>1600.67909652159</v>
+        <v>1582.189081949358</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1772609080639616</v>
+        <v>0.1805056546532239</v>
       </c>
       <c r="T64">
-        <v>2.702974634798176</v>
+        <v>2.769690039828367</v>
       </c>
       <c r="U64">
         <v>0.0797577444416894</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.583906356509014</v>
+        <v>1.558764985770776</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1069849954203043</v>
+        <v>0.1070510045332252</v>
       </c>
       <c r="C65">
-        <v>9081.4740311639</v>
+        <v>8772.714446410948</v>
       </c>
       <c r="D65">
-        <v>19482.6660311639</v>
+        <v>19463.69044641095</v>
       </c>
       <c r="E65">
-        <v>13114.792</v>
+        <v>13404.576</v>
       </c>
       <c r="F65">
-        <v>18256.392</v>
+        <v>18546.176</v>
       </c>
       <c r="G65">
         <v>7855.2</v>
@@ -6745,28 +6745,28 @@
         <v>2269.7</v>
       </c>
       <c r="M65">
-        <v>1456.088647563303</v>
+        <v>1479.201165778594</v>
       </c>
       <c r="N65">
-        <v>813.611352436697</v>
+        <v>790.4988342214062</v>
       </c>
       <c r="O65">
-        <v>162.7222704873394</v>
+        <v>158.0997668442812</v>
       </c>
       <c r="P65">
-        <v>650.8890819493575</v>
+        <v>632.399067377125</v>
       </c>
       <c r="Q65">
-        <v>1582.189081949358</v>
+        <v>1563.699067377125</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1805056546532239</v>
+        <v>0.1839306649418896</v>
       </c>
       <c r="T65">
-        <v>2.769690039828367</v>
+        <v>2.840111856249124</v>
       </c>
       <c r="U65">
         <v>0.0797577444416894</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.558764985770776</v>
+        <v>1.534409282868107</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1070510045332252</v>
+        <v>0.1071170136461462</v>
       </c>
       <c r="C66">
-        <v>8772.714446410948</v>
+        <v>8463.991789094554</v>
       </c>
       <c r="D66">
-        <v>19463.69044641095</v>
+        <v>19444.75178909456</v>
       </c>
       <c r="E66">
-        <v>13404.576</v>
+        <v>13694.36</v>
       </c>
       <c r="F66">
-        <v>18546.176</v>
+        <v>18835.96</v>
       </c>
       <c r="G66">
         <v>7855.2</v>
@@ -6827,28 +6827,28 @@
         <v>2269.7</v>
       </c>
       <c r="M66">
-        <v>1479.201165778594</v>
+        <v>1502.313683993884</v>
       </c>
       <c r="N66">
-        <v>790.4988342214062</v>
+        <v>767.3863160061157</v>
       </c>
       <c r="O66">
-        <v>158.0997668442812</v>
+        <v>153.4772632012232</v>
       </c>
       <c r="P66">
-        <v>632.399067377125</v>
+        <v>613.9090528048926</v>
       </c>
       <c r="Q66">
-        <v>1563.699067377125</v>
+        <v>1545.209052804893</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1839306649418896</v>
+        <v>0.1875513901041934</v>
       </c>
       <c r="T66">
-        <v>2.840111856249124</v>
+        <v>2.914557776465352</v>
       </c>
       <c r="U66">
         <v>0.0797577444416894</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.534409282868107</v>
+        <v>1.510802986208598</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1071170136461462</v>
+        <v>0.1146806227590671</v>
       </c>
       <c r="C67">
-        <v>8463.991789094554</v>
+        <v>6223.713465504814</v>
       </c>
       <c r="D67">
-        <v>19444.75178909456</v>
+        <v>17494.25746550482</v>
       </c>
       <c r="E67">
-        <v>13694.36</v>
+        <v>13984.144</v>
       </c>
       <c r="F67">
-        <v>18835.96</v>
+        <v>19125.744</v>
       </c>
       <c r="G67">
         <v>7855.2</v>
@@ -6909,45 +6909,45 @@
         <v>2269.7</v>
       </c>
       <c r="M67">
-        <v>1502.313683993884</v>
+        <v>1797.011767009175</v>
       </c>
       <c r="N67">
-        <v>767.3863160061157</v>
+        <v>472.6882329908251</v>
       </c>
       <c r="O67">
-        <v>153.4772632012232</v>
+        <v>94.53764659816503</v>
       </c>
       <c r="P67">
-        <v>613.9090528048926</v>
+        <v>378.1505863926601</v>
       </c>
       <c r="Q67">
-        <v>1545.209052804893</v>
+        <v>1309.45058639266</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1875513901041934</v>
+        <v>0.1913850990995739</v>
       </c>
       <c r="T67">
-        <v>2.914557776465352</v>
+        <v>2.993382868459006</v>
       </c>
       <c r="U67">
-        <v>0.0797577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.06380619555335153</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.510802986208598</v>
+        <v>1.263041256417333</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1146806227590671</v>
+        <v>0.1313004824284483</v>
       </c>
       <c r="C68">
-        <v>6223.713465504814</v>
+        <v>2774.354636552747</v>
       </c>
       <c r="D68">
-        <v>17494.25746550482</v>
+        <v>14334.68263655275</v>
       </c>
       <c r="E68">
-        <v>13984.144</v>
+        <v>14273.928</v>
       </c>
       <c r="F68">
-        <v>19125.744</v>
+        <v>19415.528</v>
       </c>
       <c r="G68">
         <v>7855.2</v>
@@ -6991,45 +6991,45 @@
         <v>2269.7</v>
       </c>
       <c r="M68">
-        <v>1797.011767009175</v>
+        <v>2379.523318824465</v>
       </c>
       <c r="N68">
-        <v>472.6882329908251</v>
+        <v>-109.8233188244653</v>
       </c>
       <c r="O68">
-        <v>94.53764659816503</v>
+        <v>-21.96466376489307</v>
       </c>
       <c r="P68">
-        <v>378.1505863926601</v>
+        <v>-87.85865505957227</v>
       </c>
       <c r="Q68">
-        <v>1309.45058639266</v>
+        <v>843.4413449404279</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1913850990995739</v>
+        <v>0.1965198928920184</v>
       </c>
       <c r="T68">
-        <v>2.993382868459006</v>
+        <v>3.098959633295773</v>
       </c>
       <c r="U68">
-        <v>0.0939577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V68">
-        <v>0.2</v>
+        <v>0.1907693008968939</v>
       </c>
       <c r="W68">
-        <v>0.07516619555335152</v>
+        <v>0.09917748921504813</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.263041256417333</v>
+        <v>0.9538465044844695</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1313004824284483</v>
+        <v>0.1320680598728652</v>
       </c>
       <c r="C69">
-        <v>2774.354636552747</v>
+        <v>2365.991425161246</v>
       </c>
       <c r="D69">
-        <v>14334.68263655275</v>
+        <v>14216.10342516125</v>
       </c>
       <c r="E69">
-        <v>14273.928</v>
+        <v>14563.712</v>
       </c>
       <c r="F69">
-        <v>19415.528</v>
+        <v>19705.312</v>
       </c>
       <c r="G69">
         <v>7855.2</v>
@@ -7073,37 +7073,37 @@
         <v>2269.7</v>
       </c>
       <c r="M69">
-        <v>2379.523318824465</v>
+        <v>2415.038592239756</v>
       </c>
       <c r="N69">
-        <v>-109.8233188244653</v>
+        <v>-145.3385922397561</v>
       </c>
       <c r="O69">
-        <v>-21.96466376489307</v>
+        <v>-29.06771844795121</v>
       </c>
       <c r="P69">
-        <v>-87.85865505957227</v>
+        <v>-116.2708737918048</v>
       </c>
       <c r="Q69">
-        <v>843.4413449404279</v>
+        <v>815.0291262081953</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1965198928920184</v>
+        <v>0.201229889544894</v>
       </c>
       <c r="T69">
-        <v>3.098959633295773</v>
+        <v>3.195802121836267</v>
       </c>
       <c r="U69">
         <v>0.1225577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1907693008968939</v>
+        <v>0.1879638700013513</v>
       </c>
       <c r="W69">
-        <v>0.09917748921504813</v>
+        <v>0.09952131649779286</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9538465044844695</v>
+        <v>0.9398193500067565</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1320680598728652</v>
+        <v>0.1328356373172821</v>
       </c>
       <c r="C70">
-        <v>2365.991425161246</v>
+        <v>1959.573937789999</v>
       </c>
       <c r="D70">
-        <v>14216.10342516125</v>
+        <v>14099.46993779</v>
       </c>
       <c r="E70">
-        <v>14563.712</v>
+        <v>14853.496</v>
       </c>
       <c r="F70">
-        <v>19705.312</v>
+        <v>19995.096</v>
       </c>
       <c r="G70">
         <v>7855.2</v>
@@ -7155,37 +7155,37 @@
         <v>2269.7</v>
       </c>
       <c r="M70">
-        <v>2415.038592239756</v>
+        <v>2450.553865655046</v>
       </c>
       <c r="N70">
-        <v>-145.3385922397561</v>
+        <v>-180.8538656550463</v>
       </c>
       <c r="O70">
-        <v>-29.06771844795121</v>
+        <v>-36.17077313100926</v>
       </c>
       <c r="P70">
-        <v>-116.2708737918048</v>
+        <v>-144.6830925240371</v>
       </c>
       <c r="Q70">
-        <v>815.0291262081953</v>
+        <v>786.6169074759631</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.201229889544894</v>
+        <v>0.206243756949568</v>
       </c>
       <c r="T70">
-        <v>3.195802121836267</v>
+        <v>3.298892512863243</v>
       </c>
       <c r="U70">
         <v>0.1225577444416894</v>
       </c>
       <c r="V70">
-        <v>0.1879638700013513</v>
+        <v>0.1852397559433607</v>
       </c>
       <c r="W70">
-        <v>0.09952131649779286</v>
+        <v>0.09985517777234208</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9398193500067565</v>
+        <v>0.9261987797168036</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1328356373172821</v>
+        <v>0.133603214761699</v>
       </c>
       <c r="C71">
-        <v>1959.573937789999</v>
+        <v>1555.054674108942</v>
       </c>
       <c r="D71">
-        <v>14099.46993779</v>
+        <v>13984.73467410895</v>
       </c>
       <c r="E71">
-        <v>14853.496</v>
+        <v>15143.28</v>
       </c>
       <c r="F71">
-        <v>19995.096</v>
+        <v>20284.88</v>
       </c>
       <c r="G71">
         <v>7855.2</v>
@@ -7237,37 +7237,37 @@
         <v>2269.7</v>
       </c>
       <c r="M71">
-        <v>2450.553865655046</v>
+        <v>2486.069139070337</v>
       </c>
       <c r="N71">
-        <v>-180.8538656550463</v>
+        <v>-216.3691390703375</v>
       </c>
       <c r="O71">
-        <v>-36.17077313100926</v>
+        <v>-43.2738278140675</v>
       </c>
       <c r="P71">
-        <v>-144.6830925240371</v>
+        <v>-173.09531125627</v>
       </c>
       <c r="Q71">
-        <v>786.6169074759631</v>
+        <v>758.2046887437302</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.206243756949568</v>
+        <v>0.2115918821812203</v>
       </c>
       <c r="T71">
-        <v>3.298892512863243</v>
+        <v>3.408855596625351</v>
       </c>
       <c r="U71">
         <v>0.1225577444416894</v>
       </c>
       <c r="V71">
-        <v>0.1852397559433607</v>
+        <v>0.1825934737155984</v>
       </c>
       <c r="W71">
-        <v>0.09985517777234208</v>
+        <v>0.1001795001533328</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9261987797168036</v>
+        <v>0.912967368577992</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.133603214761699</v>
+        <v>0.1343707922061159</v>
       </c>
       <c r="C72">
-        <v>1555.054674108942</v>
+        <v>1152.387667454623</v>
       </c>
       <c r="D72">
-        <v>13984.73467410895</v>
+        <v>13871.85166745463</v>
       </c>
       <c r="E72">
-        <v>15143.28</v>
+        <v>15433.064</v>
       </c>
       <c r="F72">
-        <v>20284.88</v>
+        <v>20574.664</v>
       </c>
       <c r="G72">
         <v>7855.2</v>
@@ -7319,37 +7319,37 @@
         <v>2269.7</v>
       </c>
       <c r="M72">
-        <v>2486.069139070337</v>
+        <v>2521.584412485628</v>
       </c>
       <c r="N72">
-        <v>-216.3691390703375</v>
+        <v>-251.8844124856278</v>
       </c>
       <c r="O72">
-        <v>-43.2738278140675</v>
+        <v>-50.37688249712556</v>
       </c>
       <c r="P72">
-        <v>-173.09531125627</v>
+        <v>-201.5075299885022</v>
       </c>
       <c r="Q72">
-        <v>758.2046887437302</v>
+        <v>729.7924700114979</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2115918821812203</v>
+        <v>0.2173088436357452</v>
       </c>
       <c r="T72">
-        <v>3.408855596625351</v>
+        <v>3.526402341336571</v>
       </c>
       <c r="U72">
         <v>0.1225577444416894</v>
       </c>
       <c r="V72">
-        <v>0.1825934737155984</v>
+        <v>0.1800217346491816</v>
       </c>
       <c r="W72">
-        <v>0.1001795001533328</v>
+        <v>0.1004946866926054</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.912967368577992</v>
+        <v>0.9001086732459077</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1343707922061159</v>
+        <v>0.1351383696505328</v>
       </c>
       <c r="C73">
-        <v>1152.387667454626</v>
+        <v>751.5284234280007</v>
       </c>
       <c r="D73">
-        <v>13871.85166745463</v>
+        <v>13760.776423428</v>
       </c>
       <c r="E73">
-        <v>15433.064</v>
+        <v>15722.848</v>
       </c>
       <c r="F73">
-        <v>20574.664</v>
+        <v>20864.448</v>
       </c>
       <c r="G73">
         <v>7855.2</v>
@@ -7401,37 +7401,37 @@
         <v>2269.7</v>
       </c>
       <c r="M73">
-        <v>2521.584412485627</v>
+        <v>2557.099685900918</v>
       </c>
       <c r="N73">
-        <v>-251.8844124856273</v>
+        <v>-287.399685900918</v>
       </c>
       <c r="O73">
-        <v>-50.37688249712546</v>
+        <v>-57.47993718018361</v>
       </c>
       <c r="P73">
-        <v>-201.5075299885019</v>
+        <v>-229.9197487207344</v>
       </c>
       <c r="Q73">
-        <v>729.7924700114984</v>
+        <v>701.3802512792657</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2173088436357451</v>
+        <v>0.2234341594798788</v>
       </c>
       <c r="T73">
-        <v>3.526402341336569</v>
+        <v>3.65234528209859</v>
       </c>
       <c r="U73">
         <v>0.1225577444416894</v>
       </c>
       <c r="V73">
-        <v>0.1800217346491816</v>
+        <v>0.1775214327790541</v>
       </c>
       <c r="W73">
-        <v>0.1004946866926054</v>
+        <v>0.1008011180502316</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9001086732459078</v>
+        <v>0.8876071638952702</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1351383696505328</v>
+        <v>0.1359059470949497</v>
       </c>
       <c r="C74">
-        <v>751.5284234280007</v>
+        <v>352.4338614187582</v>
       </c>
       <c r="D74">
-        <v>13760.776423428</v>
+        <v>13651.46586141876</v>
       </c>
       <c r="E74">
-        <v>15722.848</v>
+        <v>16012.632</v>
       </c>
       <c r="F74">
-        <v>20864.448</v>
+        <v>21154.232</v>
       </c>
       <c r="G74">
         <v>7855.2</v>
@@ -7483,37 +7483,37 @@
         <v>2269.7</v>
       </c>
       <c r="M74">
-        <v>2557.099685900918</v>
+        <v>2592.614959316208</v>
       </c>
       <c r="N74">
-        <v>-287.399685900918</v>
+        <v>-322.9149593162083</v>
       </c>
       <c r="O74">
-        <v>-57.47993718018361</v>
+        <v>-64.58299186324166</v>
       </c>
       <c r="P74">
-        <v>-229.9197487207344</v>
+        <v>-258.3319674529666</v>
       </c>
       <c r="Q74">
-        <v>701.3802512792657</v>
+        <v>672.9680325470335</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2234341594798788</v>
+        <v>0.230013202423578</v>
       </c>
       <c r="T74">
-        <v>3.65234528209859</v>
+        <v>3.787617329583722</v>
       </c>
       <c r="U74">
         <v>0.1225577444416894</v>
       </c>
       <c r="V74">
-        <v>0.1775214327790541</v>
+        <v>0.1750896323300259</v>
       </c>
       <c r="W74">
-        <v>0.1008011180502316</v>
+        <v>0.1010991540281967</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8876071638952702</v>
+        <v>0.8754481616501295</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1359059470949497</v>
+        <v>0.1366735245393666</v>
       </c>
       <c r="C75">
-        <v>352.4338614187582</v>
+        <v>-44.93774110518643</v>
       </c>
       <c r="D75">
-        <v>13651.46586141876</v>
+        <v>13543.87825889481</v>
       </c>
       <c r="E75">
-        <v>16012.632</v>
+        <v>16302.416</v>
       </c>
       <c r="F75">
-        <v>21154.232</v>
+        <v>21444.016</v>
       </c>
       <c r="G75">
         <v>7855.2</v>
@@ -7565,37 +7565,37 @@
         <v>2269.7</v>
       </c>
       <c r="M75">
-        <v>2592.614959316208</v>
+        <v>2628.130232731498</v>
       </c>
       <c r="N75">
-        <v>-322.9149593162083</v>
+        <v>-358.4302327314986</v>
       </c>
       <c r="O75">
-        <v>-64.58299186324166</v>
+        <v>-71.68604654629972</v>
       </c>
       <c r="P75">
-        <v>-258.3319674529666</v>
+        <v>-286.7441861851988</v>
       </c>
       <c r="Q75">
-        <v>672.9680325470335</v>
+        <v>644.5558138148014</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.230013202423578</v>
+        <v>0.2370983255937157</v>
       </c>
       <c r="T75">
-        <v>3.787617329583722</v>
+        <v>3.933294919183096</v>
       </c>
       <c r="U75">
         <v>0.1225577444416894</v>
       </c>
       <c r="V75">
-        <v>0.1750896323300259</v>
+        <v>0.172723556217458</v>
       </c>
       <c r="W75">
-        <v>0.1010991540281967</v>
+        <v>0.1013891349797304</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8754481616501295</v>
+        <v>0.86361778108729</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1366735245393666</v>
+        <v>0.1374411019837835</v>
       </c>
       <c r="C76">
-        <v>-44.93774110518643</v>
+        <v>-440.6268016945141</v>
       </c>
       <c r="D76">
-        <v>13543.87825889481</v>
+        <v>13437.97319830549</v>
       </c>
       <c r="E76">
-        <v>16302.416</v>
+        <v>16592.2</v>
       </c>
       <c r="F76">
-        <v>21444.016</v>
+        <v>21733.8</v>
       </c>
       <c r="G76">
         <v>7855.2</v>
@@ -7647,37 +7647,37 @@
         <v>2269.7</v>
       </c>
       <c r="M76">
-        <v>2628.130232731498</v>
+        <v>2663.64550614679</v>
       </c>
       <c r="N76">
-        <v>-358.4302327314986</v>
+        <v>-393.9455061467897</v>
       </c>
       <c r="O76">
-        <v>-71.68604654629972</v>
+        <v>-78.78910122935795</v>
       </c>
       <c r="P76">
-        <v>-286.7441861851988</v>
+        <v>-315.1564049174318</v>
       </c>
       <c r="Q76">
-        <v>644.5558138148014</v>
+        <v>616.1435950825684</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2370983255937157</v>
+        <v>0.2447502586174643</v>
       </c>
       <c r="T76">
-        <v>3.933294919183096</v>
+        <v>4.090626715950421</v>
       </c>
       <c r="U76">
         <v>0.1225577444416894</v>
       </c>
       <c r="V76">
-        <v>0.172723556217458</v>
+        <v>0.1704205754678919</v>
       </c>
       <c r="W76">
-        <v>0.1013891349797304</v>
+        <v>0.1016713831058899</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.86361778108729</v>
+        <v>0.8521028773394593</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1374411019837835</v>
+        <v>0.1382086794282004</v>
       </c>
       <c r="C77">
-        <v>-440.6268016945141</v>
+        <v>-834.6724835435452</v>
       </c>
       <c r="D77">
-        <v>13437.97319830549</v>
+        <v>13333.71151645646</v>
       </c>
       <c r="E77">
-        <v>16592.2</v>
+        <v>16881.984</v>
       </c>
       <c r="F77">
-        <v>21733.8</v>
+        <v>22023.584</v>
       </c>
       <c r="G77">
         <v>7855.2</v>
@@ -7729,37 +7729,37 @@
         <v>2269.7</v>
       </c>
       <c r="M77">
-        <v>2663.64550614679</v>
+        <v>2699.16077956208</v>
       </c>
       <c r="N77">
-        <v>-393.9455061467897</v>
+        <v>-429.46077956208</v>
       </c>
       <c r="O77">
-        <v>-78.78910122935795</v>
+        <v>-85.892155912416</v>
       </c>
       <c r="P77">
-        <v>-315.1564049174318</v>
+        <v>-343.568623649664</v>
       </c>
       <c r="Q77">
-        <v>616.1435950825684</v>
+        <v>587.7313763503362</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2447502586174643</v>
+        <v>0.2530398527265253</v>
       </c>
       <c r="T77">
-        <v>4.090626715950421</v>
+        <v>4.261069495781689</v>
       </c>
       <c r="U77">
         <v>0.1225577444416894</v>
       </c>
       <c r="V77">
-        <v>0.1704205754678919</v>
+        <v>0.1681781994748933</v>
       </c>
       <c r="W77">
-        <v>0.1016713831058899</v>
+        <v>0.101946203649782</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8521028773394593</v>
+        <v>0.8408909973744665</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1382086794282004</v>
+        <v>0.1389762568726172</v>
       </c>
       <c r="C78">
-        <v>-834.6724835435452</v>
+        <v>-1227.112743776688</v>
       </c>
       <c r="D78">
-        <v>13333.71151645646</v>
+        <v>13231.05525622331</v>
       </c>
       <c r="E78">
-        <v>16881.984</v>
+        <v>17171.768</v>
       </c>
       <c r="F78">
-        <v>22023.584</v>
+        <v>22313.368</v>
       </c>
       <c r="G78">
         <v>7855.2</v>
@@ -7811,37 +7811,37 @@
         <v>2269.7</v>
       </c>
       <c r="M78">
-        <v>2699.16077956208</v>
+        <v>2734.676052977371</v>
       </c>
       <c r="N78">
-        <v>-429.46077956208</v>
+        <v>-464.9760529773707</v>
       </c>
       <c r="O78">
-        <v>-85.892155912416</v>
+        <v>-92.99521059547415</v>
       </c>
       <c r="P78">
-        <v>-343.568623649664</v>
+        <v>-371.9808423818966</v>
       </c>
       <c r="Q78">
-        <v>587.7313763503362</v>
+        <v>559.3191576181036</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2530398527265253</v>
+        <v>0.2620502811059394</v>
       </c>
       <c r="T78">
-        <v>4.261069495781689</v>
+        <v>4.446333386902631</v>
       </c>
       <c r="U78">
         <v>0.1225577444416894</v>
       </c>
       <c r="V78">
-        <v>0.1681781994748933</v>
+        <v>0.1659940670141804</v>
       </c>
       <c r="W78">
-        <v>0.101946203649782</v>
+        <v>0.1022138859977288</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8408909973744665</v>
+        <v>0.8299703350709019</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1389762568726172</v>
+        <v>0.1397438343170342</v>
       </c>
       <c r="C79">
-        <v>-1227.112743776688</v>
+        <v>-1617.984379521404</v>
       </c>
       <c r="D79">
-        <v>13231.05525622331</v>
+        <v>13129.9676204786</v>
       </c>
       <c r="E79">
-        <v>17171.768</v>
+        <v>17461.552</v>
       </c>
       <c r="F79">
-        <v>22313.368</v>
+        <v>22603.152</v>
       </c>
       <c r="G79">
         <v>7855.2</v>
@@ -7893,37 +7893,37 @@
         <v>2269.7</v>
       </c>
       <c r="M79">
-        <v>2734.676052977371</v>
+        <v>2770.191326392661</v>
       </c>
       <c r="N79">
-        <v>-464.9760529773707</v>
+        <v>-500.491326392661</v>
       </c>
       <c r="O79">
-        <v>-92.99521059547415</v>
+        <v>-100.0982652785322</v>
       </c>
       <c r="P79">
-        <v>-371.9808423818966</v>
+        <v>-400.3930611141288</v>
       </c>
       <c r="Q79">
-        <v>559.3191576181036</v>
+        <v>530.9069388858713</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2620502811059394</v>
+        <v>0.2718798393380276</v>
       </c>
       <c r="T79">
-        <v>4.446333386902631</v>
+        <v>4.648439449943661</v>
       </c>
       <c r="U79">
         <v>0.1225577444416894</v>
       </c>
       <c r="V79">
-        <v>0.1659940670141804</v>
+        <v>0.163865937949896</v>
       </c>
       <c r="W79">
-        <v>0.1022138859977288</v>
+        <v>0.1024747046957283</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8299703350709019</v>
+        <v>0.8193296897494802</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1397438343170342</v>
+        <v>0.140511411761451</v>
       </c>
       <c r="C80">
-        <v>-1617.984379521404</v>
+        <v>-2007.323071885105</v>
       </c>
       <c r="D80">
-        <v>13129.9676204786</v>
+        <v>13030.4129281149</v>
       </c>
       <c r="E80">
-        <v>17461.552</v>
+        <v>17751.336</v>
       </c>
       <c r="F80">
-        <v>22603.152</v>
+        <v>22892.936</v>
       </c>
       <c r="G80">
         <v>7855.2</v>
@@ -7975,37 +7975,37 @@
         <v>2269.7</v>
       </c>
       <c r="M80">
-        <v>2770.191326392661</v>
+        <v>2805.706599807952</v>
       </c>
       <c r="N80">
-        <v>-500.491326392661</v>
+        <v>-536.0065998079517</v>
       </c>
       <c r="O80">
-        <v>-100.0982652785322</v>
+        <v>-107.2013199615903</v>
       </c>
       <c r="P80">
-        <v>-400.3930611141288</v>
+        <v>-428.8052798463614</v>
       </c>
       <c r="Q80">
-        <v>530.9069388858713</v>
+        <v>502.4947201536388</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2718798393380276</v>
+        <v>0.2826455459731718</v>
       </c>
       <c r="T80">
-        <v>4.648439449943661</v>
+        <v>4.869793709464788</v>
       </c>
       <c r="U80">
         <v>0.1225577444416894</v>
       </c>
       <c r="V80">
-        <v>0.163865937949896</v>
+        <v>0.1617916855707834</v>
       </c>
       <c r="W80">
-        <v>0.1024747046957283</v>
+        <v>0.1027289203887152</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8193296897494802</v>
+        <v>0.8089584278539171</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.140511411761451</v>
+        <v>0.2099651008331541</v>
       </c>
       <c r="C81">
-        <v>-2007.323071885105</v>
+        <v>-7599.264840411259</v>
       </c>
       <c r="D81">
-        <v>13030.4129281149</v>
+        <v>7728.255159588742</v>
       </c>
       <c r="E81">
-        <v>17751.336</v>
+        <v>18041.12</v>
       </c>
       <c r="F81">
-        <v>22892.936</v>
+        <v>23182.72</v>
       </c>
       <c r="G81">
         <v>7855.2</v>
@@ -8057,45 +8057,45 @@
         <v>2269.7</v>
       </c>
       <c r="M81">
-        <v>2805.706599807952</v>
+        <v>4746.841457223242</v>
       </c>
       <c r="N81">
-        <v>-536.0065998079517</v>
+        <v>-2477.141457223242</v>
       </c>
       <c r="O81">
-        <v>-107.2013199615903</v>
+        <v>-495.4282914446485</v>
       </c>
       <c r="P81">
-        <v>-428.8052798463614</v>
+        <v>-1981.713165778594</v>
       </c>
       <c r="Q81">
-        <v>502.4947201536388</v>
+        <v>-1050.413165778594</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2826455459731718</v>
+        <v>0.3091183814082611</v>
       </c>
       <c r="T81">
-        <v>4.869793709464788</v>
+        <v>5.414103069152291</v>
       </c>
       <c r="U81">
-        <v>0.1225577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V81">
-        <v>0.1617916855707834</v>
+        <v>0.09562990550468924</v>
       </c>
       <c r="W81">
-        <v>0.1027289203887152</v>
+        <v>0.1851767806893773</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8089584278539171</v>
+        <v>0.4781495275234461</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2099651008331541</v>
+        <v>0.211554678277571</v>
       </c>
       <c r="C82">
-        <v>-7599.264840411259</v>
+        <v>-7960.356553305597</v>
       </c>
       <c r="D82">
-        <v>7728.255159588742</v>
+        <v>7656.947446694408</v>
       </c>
       <c r="E82">
-        <v>18041.12</v>
+        <v>18330.904</v>
       </c>
       <c r="F82">
-        <v>23182.72</v>
+        <v>23472.504</v>
       </c>
       <c r="G82">
         <v>7855.2</v>
@@ -8139,37 +8139,37 @@
         <v>2269.7</v>
       </c>
       <c r="M82">
-        <v>4746.841457223242</v>
+        <v>4806.176975438533</v>
       </c>
       <c r="N82">
-        <v>-2477.141457223242</v>
+        <v>-2536.476975438533</v>
       </c>
       <c r="O82">
-        <v>-495.4282914446485</v>
+        <v>-507.2953950877067</v>
       </c>
       <c r="P82">
-        <v>-1981.713165778594</v>
+        <v>-2029.181580350827</v>
       </c>
       <c r="Q82">
-        <v>-1050.413165778594</v>
+        <v>-1097.881580350826</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3091183814082611</v>
+        <v>0.3229772435876433</v>
       </c>
       <c r="T82">
-        <v>5.414103069152291</v>
+        <v>5.69905586226557</v>
       </c>
       <c r="U82">
         <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.09562990550468924</v>
+        <v>0.09444928938734738</v>
       </c>
       <c r="W82">
-        <v>0.1851767806893773</v>
+        <v>0.1854185209826157</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4781495275234461</v>
+        <v>0.4722464469367369</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.211554678277571</v>
+        <v>0.2131442557219879</v>
       </c>
       <c r="C83">
-        <v>-7960.356553305597</v>
+        <v>-8320.144400842</v>
       </c>
       <c r="D83">
-        <v>7656.947446694408</v>
+        <v>7586.943599158003</v>
       </c>
       <c r="E83">
-        <v>18330.904</v>
+        <v>18620.688</v>
       </c>
       <c r="F83">
-        <v>23472.504</v>
+        <v>23762.288</v>
       </c>
       <c r="G83">
         <v>7855.2</v>
@@ -8221,37 +8221,37 @@
         <v>2269.7</v>
       </c>
       <c r="M83">
-        <v>4806.176975438533</v>
+        <v>4865.512493653823</v>
       </c>
       <c r="N83">
-        <v>-2536.476975438533</v>
+        <v>-2595.812493653823</v>
       </c>
       <c r="O83">
-        <v>-507.2953950877067</v>
+        <v>-519.1624987307647</v>
       </c>
       <c r="P83">
-        <v>-2029.181580350827</v>
+        <v>-2076.649994923059</v>
       </c>
       <c r="Q83">
-        <v>-1097.881580350826</v>
+        <v>-1145.349994923059</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3229772435876433</v>
+        <v>0.3383759793425123</v>
       </c>
       <c r="T83">
-        <v>5.69905586226557</v>
+        <v>6.015670076835878</v>
       </c>
       <c r="U83">
         <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.09444928938734738</v>
+        <v>0.09329746878506268</v>
       </c>
       <c r="W83">
-        <v>0.1854185209826157</v>
+        <v>0.185654365171141</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4722464469367369</v>
+        <v>0.4664873439253133</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2131442557219879</v>
+        <v>0.2147338331664048</v>
       </c>
       <c r="C84">
-        <v>-8320.144400842</v>
+        <v>-8678.663820900791</v>
       </c>
       <c r="D84">
-        <v>7586.943599158003</v>
+        <v>7518.208179099213</v>
       </c>
       <c r="E84">
-        <v>18620.688</v>
+        <v>18910.472</v>
       </c>
       <c r="F84">
-        <v>23762.288</v>
+        <v>24052.072</v>
       </c>
       <c r="G84">
         <v>7855.2</v>
@@ -8303,37 +8303,37 @@
         <v>2269.7</v>
       </c>
       <c r="M84">
-        <v>4865.512493653823</v>
+        <v>4924.848011869114</v>
       </c>
       <c r="N84">
-        <v>-2595.812493653823</v>
+        <v>-2655.148011869114</v>
       </c>
       <c r="O84">
-        <v>-519.1624987307647</v>
+        <v>-531.0296023738229</v>
       </c>
       <c r="P84">
-        <v>-2076.649994923059</v>
+        <v>-2124.118409495291</v>
       </c>
       <c r="Q84">
-        <v>-1145.349994923059</v>
+        <v>-1192.818409495291</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3383759793425123</v>
+        <v>0.3555863310685425</v>
       </c>
       <c r="T84">
-        <v>6.015670076835878</v>
+        <v>6.369533022532107</v>
       </c>
       <c r="U84">
         <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.09329746878506268</v>
+        <v>0.092173402896086</v>
       </c>
       <c r="W84">
-        <v>0.185654365171141</v>
+        <v>0.1858845263671718</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4664873439253133</v>
+        <v>0.46086701448043</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2147338331664048</v>
+        <v>0.2163234106108217</v>
       </c>
       <c r="C85">
-        <v>-8678.663820900791</v>
+        <v>-9035.9489786665</v>
       </c>
       <c r="D85">
-        <v>7518.208179099213</v>
+        <v>7450.707021333504</v>
       </c>
       <c r="E85">
-        <v>18910.472</v>
+        <v>19200.256</v>
       </c>
       <c r="F85">
-        <v>24052.072</v>
+        <v>24341.856</v>
       </c>
       <c r="G85">
         <v>7855.2</v>
@@ -8385,37 +8385,37 @@
         <v>2269.7</v>
       </c>
       <c r="M85">
-        <v>4924.848011869114</v>
+        <v>4984.183530084404</v>
       </c>
       <c r="N85">
-        <v>-2655.148011869114</v>
+        <v>-2714.483530084404</v>
       </c>
       <c r="O85">
-        <v>-531.0296023738229</v>
+        <v>-542.8967060168809</v>
       </c>
       <c r="P85">
-        <v>-2124.118409495291</v>
+        <v>-2171.586824067524</v>
       </c>
       <c r="Q85">
-        <v>-1192.818409495291</v>
+        <v>-1240.286824067523</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3555863310685425</v>
+        <v>0.3749479767603265</v>
       </c>
       <c r="T85">
-        <v>6.369533022532107</v>
+        <v>6.767628836440366</v>
       </c>
       <c r="U85">
         <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.092173402896086</v>
+        <v>0.09107610048065641</v>
       </c>
       <c r="W85">
-        <v>0.1858845263671718</v>
+        <v>0.1861092075347255</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.46086701448043</v>
+        <v>0.4553805024032821</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2163234106108217</v>
+        <v>0.2179129880552385</v>
       </c>
       <c r="C86">
-        <v>-9035.948978666496</v>
+        <v>-9392.032823253079</v>
       </c>
       <c r="D86">
-        <v>7450.707021333504</v>
+        <v>7384.40717674692</v>
       </c>
       <c r="E86">
-        <v>19200.256</v>
+        <v>19490.04</v>
       </c>
       <c r="F86">
-        <v>24341.856</v>
+        <v>24631.64</v>
       </c>
       <c r="G86">
         <v>7855.2</v>
@@ -8467,37 +8467,37 @@
         <v>2269.7</v>
       </c>
       <c r="M86">
-        <v>4984.183530084404</v>
+        <v>5043.519048299694</v>
       </c>
       <c r="N86">
-        <v>-2714.483530084404</v>
+        <v>-2773.819048299694</v>
       </c>
       <c r="O86">
-        <v>-542.8967060168809</v>
+        <v>-554.7638096599388</v>
       </c>
       <c r="P86">
-        <v>-2171.586824067524</v>
+        <v>-2219.055238639755</v>
       </c>
       <c r="Q86">
-        <v>-1240.286824067523</v>
+        <v>-1287.755238639755</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3749479767603263</v>
+        <v>0.3968911752110147</v>
       </c>
       <c r="T86">
-        <v>6.767628836440361</v>
+        <v>7.218804092203052</v>
       </c>
       <c r="U86">
         <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.09107610048065641</v>
+        <v>0.09000461694558988</v>
       </c>
       <c r="W86">
-        <v>0.1861092075347255</v>
+        <v>0.1863286020865721</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4553805024032821</v>
+        <v>0.4500230847279494</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2179129880552385</v>
+        <v>0.2195025654996555</v>
       </c>
       <c r="C87">
-        <v>-9392.032823253079</v>
+        <v>-9746.947141332472</v>
       </c>
       <c r="D87">
-        <v>7384.40717674692</v>
+        <v>7319.276858667527</v>
       </c>
       <c r="E87">
-        <v>19490.04</v>
+        <v>19779.824</v>
       </c>
       <c r="F87">
-        <v>24631.64</v>
+        <v>24921.424</v>
       </c>
       <c r="G87">
         <v>7855.2</v>
@@ -8549,37 +8549,37 @@
         <v>2269.7</v>
       </c>
       <c r="M87">
-        <v>5043.519048299694</v>
+        <v>5102.854566514985</v>
       </c>
       <c r="N87">
-        <v>-2773.819048299694</v>
+        <v>-2833.154566514985</v>
       </c>
       <c r="O87">
-        <v>-554.7638096599388</v>
+        <v>-566.6309133029971</v>
       </c>
       <c r="P87">
-        <v>-2219.055238639755</v>
+        <v>-2266.523653211988</v>
       </c>
       <c r="Q87">
-        <v>-1287.755238639755</v>
+        <v>-1335.223653211988</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3968911752110147</v>
+        <v>0.4219691162975158</v>
       </c>
       <c r="T87">
-        <v>7.218804092203052</v>
+        <v>7.734432955931842</v>
       </c>
       <c r="U87">
         <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.09000461694558988</v>
+        <v>0.08895805163226905</v>
       </c>
       <c r="W87">
-        <v>0.1863286020865721</v>
+        <v>0.1865428944395386</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4500230847279494</v>
+        <v>0.4447902581613453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2195025654996555</v>
+        <v>0.2210921429440723</v>
       </c>
       <c r="C88">
-        <v>-9746.947141332472</v>
+        <v>-10100.72260795</v>
       </c>
       <c r="D88">
-        <v>7319.276858667527</v>
+        <v>7255.285392050005</v>
       </c>
       <c r="E88">
-        <v>19779.824</v>
+        <v>20069.608</v>
       </c>
       <c r="F88">
-        <v>24921.424</v>
+        <v>25211.208</v>
       </c>
       <c r="G88">
         <v>7855.2</v>
@@ -8631,37 +8631,37 @@
         <v>2269.7</v>
       </c>
       <c r="M88">
-        <v>5102.854566514985</v>
+        <v>5162.190084730276</v>
       </c>
       <c r="N88">
-        <v>-2833.154566514985</v>
+        <v>-2892.490084730276</v>
       </c>
       <c r="O88">
-        <v>-566.6309133029971</v>
+        <v>-578.4980169460553</v>
       </c>
       <c r="P88">
-        <v>-2266.523653211988</v>
+        <v>-2313.992067784221</v>
       </c>
       <c r="Q88">
-        <v>-1335.223653211988</v>
+        <v>-1382.692067784221</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4219691162975158</v>
+        <v>0.4509052021665554</v>
       </c>
       <c r="T88">
-        <v>7.734432955931842</v>
+        <v>8.329389337157368</v>
       </c>
       <c r="U88">
         <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.08895805163226905</v>
+        <v>0.08793554529166826</v>
       </c>
       <c r="W88">
-        <v>0.1865428944395386</v>
+        <v>0.1867522605315174</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4447902581613453</v>
+        <v>0.4396777264583412</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2210921429440723</v>
+        <v>0.2226817203884892</v>
       </c>
       <c r="C89">
-        <v>-10100.72260795</v>
+        <v>-10453.38883469719</v>
       </c>
       <c r="D89">
-        <v>7255.285392050005</v>
+        <v>7192.403165302809</v>
       </c>
       <c r="E89">
-        <v>20069.608</v>
+        <v>20359.392</v>
       </c>
       <c r="F89">
-        <v>25211.208</v>
+        <v>25500.992</v>
       </c>
       <c r="G89">
         <v>7855.2</v>
@@ -8713,37 +8713,37 @@
         <v>2269.7</v>
       </c>
       <c r="M89">
-        <v>5162.190084730276</v>
+        <v>5221.525602945566</v>
       </c>
       <c r="N89">
-        <v>-2892.490084730276</v>
+        <v>-2951.825602945566</v>
       </c>
       <c r="O89">
-        <v>-578.4980169460553</v>
+        <v>-590.3651205891132</v>
       </c>
       <c r="P89">
-        <v>-2313.992067784221</v>
+        <v>-2361.460482356453</v>
       </c>
       <c r="Q89">
-        <v>-1382.692067784221</v>
+        <v>-1430.160482356453</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4509052021665554</v>
+        <v>0.4846639690137683</v>
       </c>
       <c r="T89">
-        <v>8.329389337157368</v>
+        <v>9.023505115253815</v>
       </c>
       <c r="U89">
         <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.08793554529166826</v>
+        <v>0.08693627773153567</v>
       </c>
       <c r="W89">
-        <v>0.1867522605315174</v>
+        <v>0.1869568683032239</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4396777264583412</v>
+        <v>0.4346813886576784</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2226817203884892</v>
+        <v>0.2242712978329061</v>
       </c>
       <c r="C90">
-        <v>-10453.38883469719</v>
+        <v>-10804.9744154011</v>
       </c>
       <c r="D90">
-        <v>7192.403165302809</v>
+        <v>7130.6015845989</v>
       </c>
       <c r="E90">
-        <v>20359.392</v>
+        <v>20649.176</v>
       </c>
       <c r="F90">
-        <v>25500.992</v>
+        <v>25790.776</v>
       </c>
       <c r="G90">
         <v>7855.2</v>
@@ -8795,37 +8795,37 @@
         <v>2269.7</v>
       </c>
       <c r="M90">
-        <v>5221.525602945566</v>
+        <v>5280.861121160857</v>
       </c>
       <c r="N90">
-        <v>-2951.825602945566</v>
+        <v>-3011.161121160857</v>
       </c>
       <c r="O90">
-        <v>-590.3651205891132</v>
+        <v>-602.2322242321715</v>
       </c>
       <c r="P90">
-        <v>-2361.460482356453</v>
+        <v>-2408.928896928685</v>
       </c>
       <c r="Q90">
-        <v>-1430.160482356453</v>
+        <v>-1477.628896928685</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4846639690137683</v>
+        <v>0.5245606934695656</v>
       </c>
       <c r="T90">
-        <v>9.023505115253815</v>
+        <v>9.843823762095074</v>
       </c>
       <c r="U90">
         <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.08693627773153567</v>
+        <v>0.08595946562219257</v>
       </c>
       <c r="W90">
-        <v>0.1869568683032239</v>
+        <v>0.1871568781474763</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4346813886576784</v>
+        <v>0.4297973281109628</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2242712978329061</v>
+        <v>0.225860875277323</v>
       </c>
       <c r="C91">
-        <v>-10804.9744154011</v>
+        <v>-11155.50696947804</v>
       </c>
       <c r="D91">
-        <v>7130.6015845989</v>
+        <v>7069.853030521958</v>
       </c>
       <c r="E91">
-        <v>20649.176</v>
+        <v>20938.96</v>
       </c>
       <c r="F91">
-        <v>25790.776</v>
+        <v>26080.56</v>
       </c>
       <c r="G91">
         <v>7855.2</v>
@@ -8877,37 +8877,37 @@
         <v>2269.7</v>
       </c>
       <c r="M91">
-        <v>5280.861121160857</v>
+        <v>5340.196639376147</v>
       </c>
       <c r="N91">
-        <v>-3011.161121160857</v>
+        <v>-3070.496639376147</v>
       </c>
       <c r="O91">
-        <v>-602.2322242321715</v>
+        <v>-614.0993278752294</v>
       </c>
       <c r="P91">
-        <v>-2408.928896928685</v>
+        <v>-2456.397311500918</v>
       </c>
       <c r="Q91">
-        <v>-1477.628896928685</v>
+        <v>-1525.097311500917</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5245606934695656</v>
+        <v>0.572436762816522</v>
       </c>
       <c r="T91">
-        <v>9.843823762095074</v>
+        <v>10.82820613830458</v>
       </c>
       <c r="U91">
         <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.08595946562219257</v>
+        <v>0.08500436044861266</v>
       </c>
       <c r="W91">
-        <v>0.1871568781474763</v>
+        <v>0.1873524433285231</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4297973281109628</v>
+        <v>0.4250218022430633</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.225860875277323</v>
+        <v>0.2274504527217399</v>
       </c>
       <c r="C92">
-        <v>-11155.50696947804</v>
+        <v>-11505.01318309005</v>
       </c>
       <c r="D92">
-        <v>7069.853030521958</v>
+        <v>7010.130816909955</v>
       </c>
       <c r="E92">
-        <v>20938.96</v>
+        <v>21228.744</v>
       </c>
       <c r="F92">
-        <v>26080.56</v>
+        <v>26370.344</v>
       </c>
       <c r="G92">
         <v>7855.2</v>
@@ -8959,37 +8959,37 @@
         <v>2269.7</v>
       </c>
       <c r="M92">
-        <v>5340.196639376147</v>
+        <v>5399.532157591438</v>
       </c>
       <c r="N92">
-        <v>-3070.496639376147</v>
+        <v>-3129.832157591438</v>
       </c>
       <c r="O92">
-        <v>-614.0993278752294</v>
+        <v>-625.9664315182877</v>
       </c>
       <c r="P92">
-        <v>-2456.397311500918</v>
+        <v>-2503.86572607315</v>
       </c>
       <c r="Q92">
-        <v>-1525.097311500917</v>
+        <v>-1572.56572607315</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.572436762816522</v>
+        <v>0.6309519586850246</v>
       </c>
       <c r="T92">
-        <v>10.82820613830458</v>
+        <v>12.03134015367176</v>
       </c>
       <c r="U92">
         <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.08500436044861266</v>
+        <v>0.084070246597529</v>
       </c>
       <c r="W92">
-        <v>0.1873524433285231</v>
+        <v>0.1875437103737227</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4250218022430633</v>
+        <v>0.420351232987645</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2274504527217399</v>
+        <v>0.2290400301661568</v>
       </c>
       <c r="C93">
-        <v>-11505.01318309005</v>
+        <v>-11853.51884823273</v>
       </c>
       <c r="D93">
-        <v>7010.130816909955</v>
+        <v>6951.409151767276</v>
       </c>
       <c r="E93">
-        <v>21228.744</v>
+        <v>21518.52800000001</v>
       </c>
       <c r="F93">
-        <v>26370.344</v>
+        <v>26660.128</v>
       </c>
       <c r="G93">
         <v>7855.2</v>
@@ -9041,37 +9041,37 @@
         <v>2269.7</v>
       </c>
       <c r="M93">
-        <v>5399.532157591438</v>
+        <v>5458.867675806729</v>
       </c>
       <c r="N93">
-        <v>-3129.832157591438</v>
+        <v>-3189.167675806729</v>
       </c>
       <c r="O93">
-        <v>-625.9664315182877</v>
+        <v>-637.8335351613458</v>
       </c>
       <c r="P93">
-        <v>-2503.86572607315</v>
+        <v>-2551.334140645383</v>
       </c>
       <c r="Q93">
-        <v>-1572.56572607315</v>
+        <v>-1620.034140645383</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6309519586850246</v>
+        <v>0.7040959535206529</v>
       </c>
       <c r="T93">
-        <v>12.03134015367176</v>
+        <v>13.53525767288073</v>
       </c>
       <c r="U93">
         <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.084070246597529</v>
+        <v>0.08315643956929498</v>
       </c>
       <c r="W93">
-        <v>0.1875437103737227</v>
+        <v>0.1877308194396789</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.420351232987645</v>
+        <v>0.4157821978464749</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2290400301661568</v>
+        <v>0.2306296076105737</v>
       </c>
       <c r="C94">
-        <v>-11853.51884823273</v>
+        <v>-12201.04889987495</v>
       </c>
       <c r="D94">
-        <v>6951.409151767276</v>
+        <v>6893.663100125057</v>
       </c>
       <c r="E94">
-        <v>21518.52800000001</v>
+        <v>21808.31200000001</v>
       </c>
       <c r="F94">
-        <v>26660.128</v>
+        <v>26949.912</v>
       </c>
       <c r="G94">
         <v>7855.2</v>
@@ -9123,37 +9123,37 @@
         <v>2269.7</v>
       </c>
       <c r="M94">
-        <v>5458.867675806729</v>
+        <v>5518.203194022019</v>
       </c>
       <c r="N94">
-        <v>-3189.167675806729</v>
+        <v>-3248.50319402202</v>
       </c>
       <c r="O94">
-        <v>-637.8335351613458</v>
+        <v>-649.700638804404</v>
       </c>
       <c r="P94">
-        <v>-2551.334140645383</v>
+        <v>-2598.802555217616</v>
       </c>
       <c r="Q94">
-        <v>-1620.034140645383</v>
+        <v>-1667.502555217616</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7040959535206529</v>
+        <v>0.7981382325950319</v>
       </c>
       <c r="T94">
-        <v>13.53525767288073</v>
+        <v>15.46886591186369</v>
       </c>
       <c r="U94">
         <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.08315643956929498</v>
+        <v>0.08226228430510901</v>
       </c>
       <c r="W94">
-        <v>0.1877308194396789</v>
+        <v>0.1879139046547543</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4157821978464749</v>
+        <v>0.411311421525545</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2306296076105737</v>
+        <v>0.2322191850549906</v>
       </c>
       <c r="C95">
-        <v>-12201.04889987495</v>
+        <v>-12547.62745126258</v>
       </c>
       <c r="D95">
-        <v>6893.663100125057</v>
+        <v>6836.86854873743</v>
       </c>
       <c r="E95">
-        <v>21808.31200000001</v>
+        <v>22098.09600000001</v>
       </c>
       <c r="F95">
-        <v>26949.912</v>
+        <v>27239.696</v>
       </c>
       <c r="G95">
         <v>7855.2</v>
@@ -9205,37 +9205,37 @@
         <v>2269.7</v>
       </c>
       <c r="M95">
-        <v>5518.203194022019</v>
+        <v>5577.538712237309</v>
       </c>
       <c r="N95">
-        <v>-3248.50319402202</v>
+        <v>-3307.83871223731</v>
       </c>
       <c r="O95">
-        <v>-649.700638804404</v>
+        <v>-661.567742447462</v>
       </c>
       <c r="P95">
-        <v>-2598.802555217616</v>
+        <v>-2646.270969789848</v>
       </c>
       <c r="Q95">
-        <v>-1667.502555217616</v>
+        <v>-1714.970969789847</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7981382325950319</v>
+        <v>0.9235279380275375</v>
       </c>
       <c r="T95">
-        <v>15.46886591186369</v>
+        <v>18.04701023050765</v>
       </c>
       <c r="U95">
         <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.08226228430510901</v>
+        <v>0.08138715362101212</v>
       </c>
       <c r="W95">
-        <v>0.1879139046547543</v>
+        <v>0.1880930944397217</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.411311421525545</v>
+        <v>0.4069357681050606</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2322191850549906</v>
+        <v>0.2338087624994075</v>
       </c>
       <c r="C96">
-        <v>-12547.62745126258</v>
+        <v>-12893.27782749137</v>
       </c>
       <c r="D96">
-        <v>6836.86854873743</v>
+        <v>6781.002172508637</v>
       </c>
       <c r="E96">
-        <v>22098.09600000001</v>
+        <v>22387.88</v>
       </c>
       <c r="F96">
-        <v>27239.696</v>
+        <v>27529.48</v>
       </c>
       <c r="G96">
         <v>7855.2</v>
@@ -9287,37 +9287,37 @@
         <v>2269.7</v>
       </c>
       <c r="M96">
-        <v>5577.538712237309</v>
+        <v>5636.8742304526</v>
       </c>
       <c r="N96">
-        <v>-3307.83871223731</v>
+        <v>-3367.174230452601</v>
       </c>
       <c r="O96">
-        <v>-661.567742447462</v>
+        <v>-673.4348460905202</v>
       </c>
       <c r="P96">
-        <v>-2646.270969789848</v>
+        <v>-2693.73938436208</v>
       </c>
       <c r="Q96">
-        <v>-1714.970969789847</v>
+        <v>-1762.43938436208</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9235279380275375</v>
+        <v>1.099073525633046</v>
       </c>
       <c r="T96">
-        <v>18.04701023050765</v>
+        <v>21.65641227660919</v>
       </c>
       <c r="U96">
         <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.08138715362101212</v>
+        <v>0.08053044674079093</v>
       </c>
       <c r="W96">
-        <v>0.1880930944397217</v>
+        <v>0.1882685118081635</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4069357681050606</v>
+        <v>0.4026522337039546</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2338087624994075</v>
+        <v>0.2353983399438244</v>
       </c>
       <c r="C97">
-        <v>-12893.27782749137</v>
+        <v>-13238.02259744721</v>
       </c>
       <c r="D97">
-        <v>6781.002172508637</v>
+        <v>6726.041402552797</v>
       </c>
       <c r="E97">
-        <v>22387.88</v>
+        <v>22677.664</v>
       </c>
       <c r="F97">
-        <v>27529.48</v>
+        <v>27819.264</v>
       </c>
       <c r="G97">
         <v>7855.2</v>
@@ -9369,37 +9369,37 @@
         <v>2269.7</v>
       </c>
       <c r="M97">
-        <v>5636.8742304526</v>
+        <v>5696.20974866789</v>
       </c>
       <c r="N97">
-        <v>-3367.174230452601</v>
+        <v>-3426.509748667891</v>
       </c>
       <c r="O97">
-        <v>-673.4348460905202</v>
+        <v>-685.3019497335781</v>
       </c>
       <c r="P97">
-        <v>-2693.73938436208</v>
+        <v>-2741.207798934312</v>
       </c>
       <c r="Q97">
-        <v>-1762.43938436208</v>
+        <v>-1809.907798934312</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.099073525633046</v>
+        <v>1.362391907041308</v>
       </c>
       <c r="T97">
-        <v>21.65641227660919</v>
+        <v>27.0705153457615</v>
       </c>
       <c r="U97">
         <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.08053044674079093</v>
+        <v>0.07969158792057436</v>
       </c>
       <c r="W97">
-        <v>0.1882685118081635</v>
+        <v>0.188440274648096</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4026522337039546</v>
+        <v>0.3984579396028718</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2353983399438244</v>
+        <v>0.2369879173882413</v>
       </c>
       <c r="C98">
-        <v>-13238.0225974472</v>
+        <v>-13581.8836042055</v>
       </c>
       <c r="D98">
-        <v>6726.0414025528</v>
+        <v>6671.964395794498</v>
       </c>
       <c r="E98">
-        <v>22677.664</v>
+        <v>22967.448</v>
       </c>
       <c r="F98">
-        <v>27819.264</v>
+        <v>28109.048</v>
       </c>
       <c r="G98">
         <v>7855.2</v>
@@ -9451,37 +9451,37 @@
         <v>2269.7</v>
       </c>
       <c r="M98">
-        <v>5696.209748667889</v>
+        <v>5755.54526688318</v>
       </c>
       <c r="N98">
-        <v>-3426.50974866789</v>
+        <v>-3485.845266883181</v>
       </c>
       <c r="O98">
-        <v>-685.301949733578</v>
+        <v>-697.1690533766362</v>
       </c>
       <c r="P98">
-        <v>-2741.207798934312</v>
+        <v>-2788.676213506545</v>
       </c>
       <c r="Q98">
-        <v>-1809.907798934311</v>
+        <v>-1857.376213506544</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.362391907041304</v>
+        <v>1.801255876055072</v>
       </c>
       <c r="T98">
-        <v>27.07051534576142</v>
+        <v>36.09402046101523</v>
       </c>
       <c r="U98">
         <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.07969158792057437</v>
+        <v>0.07887002515850659</v>
       </c>
       <c r="W98">
-        <v>0.188440274648096</v>
+        <v>0.1886084959861743</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3984579396028719</v>
+        <v>0.3943501257925329</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2369879173882413</v>
+        <v>0.2385774948326581</v>
       </c>
       <c r="C99">
-        <v>-13581.8836042055</v>
+        <v>-13924.8819939759</v>
       </c>
       <c r="D99">
-        <v>6671.964395794498</v>
+        <v>6618.750006024103</v>
       </c>
       <c r="E99">
-        <v>22967.448</v>
+        <v>23257.232</v>
       </c>
       <c r="F99">
-        <v>28109.048</v>
+        <v>28398.832</v>
       </c>
       <c r="G99">
         <v>7855.2</v>
@@ -9533,37 +9533,37 @@
         <v>2269.7</v>
       </c>
       <c r="M99">
-        <v>5755.54526688318</v>
+        <v>5814.880785098471</v>
       </c>
       <c r="N99">
-        <v>-3485.845266883181</v>
+        <v>-3545.180785098471</v>
       </c>
       <c r="O99">
-        <v>-697.1690533766362</v>
+        <v>-709.0361570196943</v>
       </c>
       <c r="P99">
-        <v>-2788.676213506545</v>
+        <v>-2836.144628078777</v>
       </c>
       <c r="Q99">
-        <v>-1857.376213506544</v>
+        <v>-1904.844628078777</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.801255876055072</v>
+        <v>2.678983814082608</v>
       </c>
       <c r="T99">
-        <v>36.09402046101523</v>
+        <v>54.14103069152284</v>
       </c>
       <c r="U99">
         <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.07887002515850659</v>
+        <v>0.07806522898341979</v>
       </c>
       <c r="W99">
-        <v>0.1886084959861743</v>
+        <v>0.1887732842357203</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3943501257925329</v>
+        <v>0.3903261449170989</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2385774948326581</v>
+        <v>0.2401670722770751</v>
       </c>
       <c r="C100">
-        <v>-13924.8819939759</v>
+        <v>-14267.03824367272</v>
       </c>
       <c r="D100">
-        <v>6618.750006024103</v>
+        <v>6566.377756327278</v>
       </c>
       <c r="E100">
-        <v>23257.232</v>
+        <v>23547.016</v>
       </c>
       <c r="F100">
-        <v>28398.832</v>
+        <v>28688.616</v>
       </c>
       <c r="G100">
         <v>7855.2</v>
@@ -9615,37 +9615,37 @@
         <v>2269.7</v>
       </c>
       <c r="M100">
-        <v>5814.880785098471</v>
+        <v>5874.216303313762</v>
       </c>
       <c r="N100">
-        <v>-3545.180785098471</v>
+        <v>-3604.516303313762</v>
       </c>
       <c r="O100">
-        <v>-709.0361570196943</v>
+        <v>-720.9032606627525</v>
       </c>
       <c r="P100">
-        <v>-2836.144628078777</v>
+        <v>-2883.61304265101</v>
       </c>
       <c r="Q100">
-        <v>-1904.844628078777</v>
+        <v>-1952.31304265101</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.678983814082608</v>
+        <v>5.312167628165216</v>
       </c>
       <c r="T100">
-        <v>54.14103069152284</v>
+        <v>108.2820613830457</v>
       </c>
       <c r="U100">
         <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.07806522898341979</v>
+        <v>0.0772766913169206</v>
       </c>
       <c r="W100">
-        <v>0.1887732842357203</v>
+        <v>0.1889347434297201</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3903261449170989</v>
+        <v>0.3863834565846029</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2401670722770751</v>
-      </c>
-      <c r="C101">
-        <v>-14267.03824367272</v>
-      </c>
-      <c r="D101">
-        <v>6566.377756327278</v>
-      </c>
-      <c r="E101">
-        <v>23547.016</v>
-      </c>
-      <c r="F101">
-        <v>28688.616</v>
-      </c>
-      <c r="G101">
-        <v>7855.2</v>
-      </c>
-      <c r="H101">
-        <v>23836.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3201</v>
-      </c>
-      <c r="K101">
-        <v>931.3000000000002</v>
-      </c>
-      <c r="L101">
-        <v>2269.7</v>
-      </c>
-      <c r="M101">
-        <v>5874.216303313762</v>
-      </c>
-      <c r="N101">
-        <v>-3604.516303313762</v>
-      </c>
-      <c r="O101">
-        <v>-720.9032606627525</v>
-      </c>
-      <c r="P101">
-        <v>-2883.61304265101</v>
-      </c>
-      <c r="Q101">
-        <v>-1952.31304265101</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.312167628165216</v>
-      </c>
-      <c r="T101">
-        <v>108.2820613830457</v>
-      </c>
-      <c r="U101">
-        <v>0.2047577444416894</v>
-      </c>
-      <c r="V101">
-        <v>0.0772766913169206</v>
-      </c>
-      <c r="W101">
-        <v>0.1889347434297201</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3863834565846029</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
